--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-301.671</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.01573e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.004</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1973444488350379</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7450374900498935</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.630163528485135</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.004800302825428</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30.15869574676302</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.32876199545412</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 21.434x + -11454.311</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>396.7494757253389</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9476.531367599982</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.882106739746401e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9998892794082589</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-274.621</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.01753e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.39700000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2669793922304137</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.996773199233175</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.9093100171525</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.356563851811438</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33.34009071916551</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.58173862750681</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 23.679x + -11972.298</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>444.3248684806564</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>124542088.0869367</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.872969470109779e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9455210549081215</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-269.188</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.01569e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2008975940625089</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.142305461833156</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.743142955932948</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.169077616921518</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.25341463845149</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.68526055021523</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 24.739x + -12293.225</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>438.6912072937703</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>180002047.1834024</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.833385558037288e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9475143334988627</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-265.18</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.01135e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2214127413421912</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9873065204646287</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.714687729024932</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.169189576661888</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.0357884436017</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.70455818397799</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 24.947x + -12220.466</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>417.8418410683744</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5838.71159234117</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.397371370064106e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9529945128565545</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-253.147</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.00886e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.70699999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.538483946385534</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.337492807460235</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.316388193132781</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.050052934375221</v>
+      </c>
+      <c r="J6" t="n">
+        <v>36.42125127999422</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.85913255689807</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 26.750x + -13032.513</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>407.3648962783021</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3541.201247124014</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.883231697752806e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8258834609808883</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-256.03</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.00712e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.732</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4768385044457272</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.236902936544507</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.888587925159335</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.432730300854617</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.88413502844951</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.83021175901268</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 26.394x + -12696.378</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>409.4310658951832</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3513.279001399675</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.832195786694801e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7498059072504979</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-249.344</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.00704e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.816</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3555475116455878</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.156112556268354</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.180534955360806</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.294954640284571</v>
+      </c>
+      <c r="J8" t="n">
+        <v>36.00464037839883</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.87954763265597</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 27.008x + -12867.182</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>410.3922897139009</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3480.175744170541</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.436075765014825e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7459538723595734</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-253.11</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.00308e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.82599999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6815285601655351</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.369749149690351</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.291140218530405</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.654963697958912</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.82657295016472</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.89616406398055</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 27.222x + -12859.536</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>401.8272138803461</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3451.573212426066</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.042168233436052e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7916368027510712</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-251.138</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.00132e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.895</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3220914925148843</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.018200756246153</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.212228721164762</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.634529431393978</v>
+      </c>
+      <c r="J10" t="n">
+        <v>36.50354400646423</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.85680783890082</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 26.721x + -12442.841</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>398.0725959979554</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3420.699389341019</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.163559562718493e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7869633325249612</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-246.883</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.00153e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.94799999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4140890652588683</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.048196960216098</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.178056140698877</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.768079421076786</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36.96248592113697</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.92552157173371</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 27.607x + -12767.128</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>394.9177349925651</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3391.415712651376</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.207869693961968e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7810813294218094</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-243.092</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.00104e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-85.002</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3818977973897687</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.285837919843958</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.131334312531441</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.571764856366669</v>
+      </c>
+      <c r="J12" t="n">
+        <v>36.89826129426142</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.97173264315612</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 28.237x + -12949.649</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>392.6016724387123</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3360.517903602971</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.052067875112602e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.795707823975795</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-244.6220000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.0007e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-85.023</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5719288948432788</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.226464275904343</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.180517210987698</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.117896929490184</v>
+      </c>
+      <c r="J13" t="n">
+        <v>37.32525620129778</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.96799672088163</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 28.185x + -12800.423</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>396.7291897181614</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5447.895109564663</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.086245210894876e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8461773584740592</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-245.7910000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.00008e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-85.05500000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1671338949635031</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.109456345501684</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.854168367762323</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.587545724580339</v>
+      </c>
+      <c r="J14" t="n">
+        <v>36.41396014280187</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.94510256937021</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 27.871x + -12513.055</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>392.4449466826355</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6664.223827601112</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.80176729512535e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9994292745609792</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-239.637</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.99847e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-85.129</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5522716539548969</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8756803119590779</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.822040944279355</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.267424899597334</v>
+      </c>
+      <c r="J15" t="n">
+        <v>37.40476728743956</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.98725928861322</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 28.455x + -12665.157</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>399.7722451537153</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>109184778.3241984</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.641568219533586e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9569485877414382</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-239.664</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.99828e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-85.151</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5821713873484994</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.515801907208131</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.608937138086306</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.254066757998615</v>
+      </c>
+      <c r="J16" t="n">
+        <v>38.0757470789155</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.03368550909551</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 29.127x + -12882.958</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>396.4967727724966</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>433539134.4037449</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.636242338467464e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9572436146272094</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-243.848</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.99709e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.16800000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1331185763013006</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9276342485835093</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.875408226955208</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.28334969042427</v>
+      </c>
+      <c r="J17" t="n">
+        <v>36.66507694654916</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.95778491032624</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 28.044x + -12228.123</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>393.2524944883046</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>214709801.261642</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.629495894298315e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9575580020846242</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-237.5960000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.99687e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.238</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2704190300572111</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9399521303582564</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.989830441980188</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.742935163026497</v>
+      </c>
+      <c r="J18" t="n">
+        <v>38.08565181491034</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.01332091202561</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 28.828x + -12471.714</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>389.9716284979895</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>213081000.0809783</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.615101207613322e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9583742811641953</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-231.955</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.99669e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.29900000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4606534340731671</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.14839136197544</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.179031513525538</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.692117001731308</v>
+      </c>
+      <c r="J19" t="n">
+        <v>38.8640899585908</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.08313119401684</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 29.879x + -12841.971</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>386.7074171342449</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>421719329.5008657</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.602481999857752e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9590930828932677</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-231.742</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.99708e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.328</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4698725138888062</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.281375745596727</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.009875500980757</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.651785864586149</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38.65888997638589</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.08689395371252</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 29.938x + -12743.901</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>383.4161594966821</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>156971907.8893668</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.596409672831079e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9594810691287596</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-237.4179999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.9952e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.331</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1379497959015523</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9096311074646574</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.024270725708462</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.886034037267473</v>
+      </c>
+      <c r="J21" t="n">
+        <v>38.25152479647706</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.02856032291847</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 29.051x + -12207.673</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>380.0833278472551</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>417669598.8100793</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.59198318755664e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9596183020566957</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-233.336</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.99644e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.38200000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2874436474306723</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9406848639163014</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.930238840130045</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.456310670646253</v>
+      </c>
+      <c r="J22" t="n">
+        <v>38.46050775793957</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.07628340723382</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 29.773x + -12408.931</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>376.7321260772224</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>821698538.8496218</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.583546293951973e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9602034087251805</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-810.442</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.15998e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-78.503</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08820852647624562</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4447991162463117</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.083302873472932</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.998489834818301</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.308809082899344</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.18999817840536</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.374x + -5401.071</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>514.5894486391926</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>285869104.6976956</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.772404767762741e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8510905746400552</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-619.3349999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.20096e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.515</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2506897046118307</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.009559198020658</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.767060631246263</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.93472413806754</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.14854864781429</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.75512454019101</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 10.894x + -6178.568</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>483.0142044814073</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>268188951.6084123</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.537211082018327e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8899330000803782</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-529.5049999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.17127e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-81.535</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4111860165552653</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9574295637088668</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.935069670580428</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.019215330571425</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.56391866251832</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.55562048662085</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.866x + -7064.024</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>473.6879955288285</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>390715133.1608049</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.025617682073349e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9058043978599836</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-472.145</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.13877e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3738743717002503</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.014589615539844</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.863434745368294</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.116373997595697</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16.80525315108842</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.07531142267271</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.576x + -7877.713</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>468.1671033032571</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>193121447.887839</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.716303751517951e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9155322562876601</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-424.6659999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.1135e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.736</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2336104066420534</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9233871023952122</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.858458949076669</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.128576849150017</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.19423925094863</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.44645856337118</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.103x + -8563.418</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>463.1888459470676</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>412945724.0501981</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.493779008537029e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9230168367433877</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-402.571</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.09211e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.044</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1938119586115925</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.035348009225888</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.777688336615365</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.216446664981048</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.62872153529186</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.65975374096946</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.134x + -8990.945</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>458.0781117823967</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>251336372.6764174</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.355757330395731e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.927569774174188</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-372.673</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.07505e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.383</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3418183045411953</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9616112785318057</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.824613700204597</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.187439072835225</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22.5414674043494</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.89567991017859</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.439x + -9548.569</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>453.1056739293182</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>248391625.5926813</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.227873529410139e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9321849308159753</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-362.136</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.06022e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.565</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1324248945431294</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.824904243736298</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.787086570243024</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.046825535055615</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23.16851832929142</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.9898135424009</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.016x + -9704.214</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>448.1286515640717</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>321752148.2150379</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.147105274599211e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9349488997125096</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-345.299</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.04932e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.788</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7128775371894374</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.664314256101519</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.933470792565861</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.69259515562757</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.10116706600029</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.748x + -9930.241</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>443.3643763277236</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>364039937.4832708</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.068180290307751e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9379835186312472</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-330.157</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.03996e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-83.959</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4217644677324958</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.1500071958039</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.977231890651065</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.306780985718539</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26.21705563390539</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.27482393024709</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 21.009x + -10483.117</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>438.8792344827597</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>241205774.9745677</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.006781957533359e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9403546345120315</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-517.6370000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.17316e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.855</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1589966308973626</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7434827609713527</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.320545325742608</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.413564379349952</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.93351470251674</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.57652688229666</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.927x + -6760.276</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>450.8678769253131</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>123242275.114243</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.884791817255893e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9113499642088377</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-410.001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.11682e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.08</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.498058424431033</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.073370072916201</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.999711834595777</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.224685542264359</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.91439950070653</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.57243820920476</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.696x + -8375.073</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>439.6563681340648</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>180977512.9080008</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.366011558935878e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9289216952549978</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-360.9400000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.08477e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.61799999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5966808199647685</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.263355329852837</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.132102546152328</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.726067132447885</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.3641140244456</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.99561876236625</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 19.053x + -9418.214</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>395.293628619102</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5395.605148669591</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8.798345134825952e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8725147479809059</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-331.812</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.06316e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.946</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7239329115084142</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.113850167464755</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.134214831744694</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.367362543963505</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.57292010750326</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.26124801782844</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 20.904x + -10235.100</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>431.024296780722</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>241022262.4156938</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.036202999131847e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9406032166263536</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-315.943</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.04785e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.15900000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6428711357087948</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.198950865638251</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.941786706364579</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.364240143112697</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.32234471910459</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.37059469986423</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 21.775x + -10519.781</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>402.2937102302833</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3512.599583949087</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.287681571068858e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8166519810821551</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-306.8489999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.03659e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.30500000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.378797995590998</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.229075498406854</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.10620337349713</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.722142668458165</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.65074771852751</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.4355951855562</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 22.328x + -10653.125</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>405.4904995387254</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3480.233216384322</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.353391950136328e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7818828453287834</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-296.956</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.03039e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.443</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03551805697344007</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8114860434439487</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.764605855598119</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.248625269654075</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29.65195526046964</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.46913154353524</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 22.624x + -10653.923</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>402.3831554181585</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3451.586194284745</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.05675726637929e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7842147816995064</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-295.492</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.02408e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.47799999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4933019676876122</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.041986659014513</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.933331973496651</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.25470898901645</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.3619081403828</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.55871172853033</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 23.455x + -11004.725</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>403.8965751825108</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3427.772219435024</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.826980749065107e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7954648330292199</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-284.792</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.01857e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.60899999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3223141101112555</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.079258077155339</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.383442456148816</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.539786123313053</v>
+      </c>
+      <c r="J10" t="n">
+        <v>30.9768642462386</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.62033215672666</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 24.063x + -11176.696</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>394.3707398400769</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3400.063772847948</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.130406602422708e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7519618202728146</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-282.722</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.01567e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.667</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1646341102990112</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9852257548693608</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.088078650336183</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.630599303399414</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.54235066895993</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.62493867185771</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 24.110x + -11078.258</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>392.2629985923898</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3373.167806019072</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.190957564552214e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7844817338121756</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-277.197</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.01191e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.742</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5219617829552574</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.294852257055502</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.195780574330948</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.863008443147893</v>
+      </c>
+      <c r="J12" t="n">
+        <v>32.19529497151549</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.7093320023989</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 24.999x + -11416.585</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>389.4832884581104</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3345.463254356214</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>9.44109590473631e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8688694029003797</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-271.838</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.00889e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.819</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2985675904808944</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.044034907042573</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.892519021102931</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.431893267174817</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32.54823124320753</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.73285262931817</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 25.259x + -11422.213</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>387.1864115939476</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3315.766509785056</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.085072054046103e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.7928592603596168</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-265.651</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.00738e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.889</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5328275766590981</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.239571189727722</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.039948581961155</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.582801945579332</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33.25845623528761</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.81481647224859</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 26.207x + -11779.848</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>391.6978607263177</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5379.752486957718</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.064923145243585e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8489207620657759</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-263.128</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.00478e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.946</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4708361237466108</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.110551760203663</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.249121355828976</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.72959508313734</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.92776259497656</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.82043187161247</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 26.275x + -11687.953</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>387.3264559726508</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6582.322267194906</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.872510354953958e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9999185374315883</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-273.386</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0028e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.92700000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.649537018670474</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.754989562205785</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.218025233904749</v>
+      </c>
+      <c r="J16" t="n">
+        <v>32.35154057688209</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.69925981326088</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 24.890x + -10906.624</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>395.0548991229824</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>215610645.3962327</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.698851289753131e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9540178891906357</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-267.936</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.0016e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.007690041579432116</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7131577743502023</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.657799295980089</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.30135869497418</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33.54431255461084</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.72580019033398</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 25.181x + -10929.057</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>391.9623220307058</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>110429064.5540533</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.681525107923475e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9548998996271583</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-259.605</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.00064e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.077</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1152193708537342</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7321369995612019</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.737919833372013</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.464162833720077</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.50981367059094</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.81287807470544</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 26.184x + -11299.127</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>388.9329620833877</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>424417102.6382215</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.664634351187337e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9557804722578245</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-257.252</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.99927e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.11499999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3361162372660874</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.227217626908485</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.137206772453854</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.789174652368978</v>
+      </c>
+      <c r="J19" t="n">
+        <v>35.11635834637911</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.8797697509733</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 27.011x + -11597.276</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>385.8920534170926</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>421248590.2657109</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.654126478313937e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9562841296332386</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-256.595</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.99843e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.152</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2464762090725707</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9327381618058768</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.971681954600668</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.407453100247873</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.67821897109189</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.88074814245793</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 27.024x + -11485.191</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>382.817670241769</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>208983998.0971246</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.644063102284988e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9568018018580203</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-256.1849999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.99763e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.202</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.02158508760614425</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5589134083189419</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.761634177686389</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.145065181151164</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.72287068301465</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.82758369754721</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 26.362x + -11047.969</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>379.7669731489552</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>414165340.4579787</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.632497046580194e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9574126781426855</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-247.955</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.99554e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.268</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5065454221942527</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.124589816198246</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.482540566158105</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.203496687758305</v>
+      </c>
+      <c r="J22" t="n">
+        <v>36.48069246148265</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.9701621601189</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 28.215x + -11809.651</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>376.7423984880032</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>308630477.7942852</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.615821687966625e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9582188621066603</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-762.902</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.21037e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-78.718</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2419395143513107</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6836433619823946</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.329890620662158</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.385374777245058</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.723177956082333</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.45949046664951</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.722x + -5528.900</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>510.0230643160938</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>280240702.0054348</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.747730760022037e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8551690128015379</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-578.886</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.21752e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.791</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3157981966496224</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9202807094299617</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.792409966999563</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.211635879690772</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.03648345404301</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.03443553300878</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.510x + -6517.298</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>482.4254909750563</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>805207626.7345194</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.462534064680492e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8934832853792555</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-488.2439999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.17976e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-81.836</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4109089579599934</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9807436062473478</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.041498666356232</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.328932665533806</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.01497847855696</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.86524912306481</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.833x + -7611.660</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>473.7800385816096</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>260510951.643348</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.942887961099986e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9094445245033568</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-430.6420000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.14361e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.515</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4043895921112611</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.03263452902021</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.950760047316217</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.124689142862113</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.59341116313811</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.3631281959031</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.733x + -8509.877</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>468.275077592011</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>128529960.5918365</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.631311019853731e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9192954304947233</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-393.077</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.11582e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-82.96299999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4643559296173638</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.192479608931269</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.962206514137083</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.235150946503587</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.82564279223162</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.68943968421829</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.288x + -9225.698</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>463.1657707101388</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>190577286.1824888</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.433202917606022e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9257882025619144</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-365.943</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.09581e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.319</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1560719221421459</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8657298223159873</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.716597799563078</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.940095731310978</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.68008642215301</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.87646964071794</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.325x + -9608.469</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>458.1120111061471</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>754170482.2608846</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.28840568000323e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9308548232196515</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-341.428</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.08005e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.598</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3858259278993429</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.216262341469251</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.0510112522173</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.503781115179806</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25.0616407410469</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.10560889338865</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 19.779x + -10257.965</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>453.0741271720851</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>496407696.4325032</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.179195488138277e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9348194406595822</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-328.872</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.06787e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.797</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1384403634363479</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9420539905199823</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.831289267100855</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.050148985471261</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.89498778952024</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.20011358068641</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 20.447x + -10444.717</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>403.7724355794147</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9304.183362649805</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.894594238925443e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9998268003986831</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-315.638</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.05925e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.973</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1916562175136638</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8817201168580782</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.70637415092634</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.082879569868378</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26.99901495575602</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.30416266343487</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 21.238x + -10705.669</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>443.4328412523989</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>485106620.7304722</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.037941546175563e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9401836813729093</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-305.871</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.05354e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.09699999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3929808702485166</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.104028109150762</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.968645657111501</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.269549942202687</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.30706506193646</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.40591634175149</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 22.072x + -11014.710</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>438.9773628255097</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>720381305.7444178</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.994258849657866e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9419561149497139</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-528.6270000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.2279e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.51600000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.344064277659561</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.02116908200836</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.778107205017853</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.985254314816214</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.39163777440432</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.40007102497242</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.429x + -6545.016</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>452.3508453541294</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>248183263.2253623</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.112824161963975e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9065260216129608</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-409.328</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.1518e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.953</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.211868110274113</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.101027905648077</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.827916444428982</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.216523030193073</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.61485873387916</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.51054109016846</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.399x + -8261.792</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>441.1915900308161</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>241859846.0119839</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.463548461689567e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.927080734629527</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-352.181</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.11094e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.589</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4952333540888252</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.26303849146077</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.149772610038327</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.610655360771308</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.71250639878987</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.00645554276082</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 19.122x + -9490.960</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>436.3548310285325</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>119278596.0502252</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.208848820771064e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9356944585156446</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-325.645</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.08667e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.91800000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3338274566290925</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9828530062674787</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.084929809776971</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.297804502401517</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.92299983848542</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.22812280110165</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 20.654x + -10121.659</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>432.4205249758801</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>118581029.3885973</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.079512572913859e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9401622021827061</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-309.522</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.07064e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.155</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6597874039103194</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.704472177847332</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.990697747128618</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.61741906852401</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.2890872318856</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 21.119x + -10176.591</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>408.3964641392536</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7101.422942289118</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.6379726903005e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9947722685128367</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-299.2690000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.0586e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.26600000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6666288403196496</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.37938242697057</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.049298768923853</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.541369847774445</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.71533160815539</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.50462129892919</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 22.946x + -11045.048</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>401.966931862572</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3492.649307771641</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6.058865907241843e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9756267818283836</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-295.419</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.05e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.366</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5433696039329577</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.377852189678077</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.287103175132971</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.470470990304249</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29.42901704662881</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.52145584907113</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 23.102x + -10977.462</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>398.597674306599</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3459.703656614961</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.541397465901892e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8219042449566987</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-285.576</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.04506e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.505</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2371795159159547</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8594941183048749</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.735001738608295</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.94183993455372</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.20135175259545</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.54544948096554</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 23.328x + -10924.741</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>403.8846045701454</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3428.99574492553</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.308474421580248e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7741987323164977</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-278.53</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.03863e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.599</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4532238388966155</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.084860522011715</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.231416291084194</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.537165432351892</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.66574973887193</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.63493727598764</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 24.212x + -11256.994</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>395.6985124484585</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3402.37693829069</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.028570739946239e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7921343136142551</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-275.198</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.03384e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.661</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4203710966716218</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.206035999465931</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.148835629407271</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.836405888051458</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32.25084933593374</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.68112606702171</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 24.695x + -11388.271</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>392.3154123634241</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3372.865831297919</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.186959869851276e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7851787481194796</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-269.0719999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.03217e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.739</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4613066447193263</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.117795046439185</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.94841769176275</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.512937988671994</v>
+      </c>
+      <c r="J12" t="n">
+        <v>32.41564744738827</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.73860685571304</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 25.323x + -11587.931</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>389.145647422873</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3348.019978078831</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8.896212750669811e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8744375434577657</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-272.334</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.02792e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.82599999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8613062043191407</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.391797827834696</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32.21113388199785</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.43887800715753</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 22.356x + -9948.767</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>387.430774162167</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3322.767583093016</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.689040659125571e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.761613722176729</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-270.4300000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.02749e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.83199999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4207312073421638</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.487442345568135</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.820962908315295</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32.28785022531749</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.61504044963438</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 24.010x + -10693.157</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>385.2630321057063</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3298.72348165928</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.092965923134083e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.7939652896558055</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-263.349</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.02581e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.881</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4370695070022121</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.176831735344071</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.268598840545317</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.948083568485353</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.73472926800861</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.80000684725178</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 26.031x + -11615.392</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>387.811655867922</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6597.83021612438</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.87374654933605e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9999185116922792</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-257.817</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.02478e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.952</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.19007462518868</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9870451921734733</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.904164269555052</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.418234383125347</v>
+      </c>
+      <c r="J16" t="n">
+        <v>33.93760634056244</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.81973538823236</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 26.267x + -11609.430</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>396.1033591762223</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>216015388.1743194</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.724884697611362e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9541916668591555</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-255.014</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.02314e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.014</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.06152741611271256</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8557027305477052</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.818856024088006</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.089084734269747</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.3550431275999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.80958887751102</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 26.145x + -11429.527</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>393.1878154747255</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>214757656.8707898</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.70843335055864e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9549917941196892</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-262.587</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.02081e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.032</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.08160848432130344</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.253254636452201</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.792407922780852</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33.8918018433255</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.62649270100589</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 24.126x + -10346.713</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>390.1497452323471</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>212996290.450841</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.699984214560284e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9553067099821752</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-249.416</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.02006e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.095</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6711085370714951</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.273100752825741</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.206985496078668</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.696443390072759</v>
+      </c>
+      <c r="J19" t="n">
+        <v>35.26272114298408</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.94026050456966</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 27.805x + -12029.670</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>387.1222911284498</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>211564676.3490336</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.685623821567904e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9560561345612519</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-259.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.01904e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.101</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1869623488434732</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.287170588975514</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.692045825842893</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33.98001770452366</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.69417283319656</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 24.835x + -10489.715</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>384.0414995523008</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>836933480.7986488</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.681501399578432e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.956230592041715</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-248.335</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.01896e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.18600000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1276305058101053</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8825506483908083</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.667847470498626</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.275334793257701</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.57127648434289</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.86886394465913</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 26.873x + -11335.917</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>381.0114202350169</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>158367121.1464663</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.664095332736867e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9572016161535086</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-249.9010000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.01866e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.22799999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1825123084849544</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.099233275955284</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.592188967708458</v>
+      </c>
+      <c r="J22" t="n">
+        <v>35.04735653502429</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.75691782074087</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 25.530x + -10590.833</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>377.9163953705417</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>824009950.5852665</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.654781821075532e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9577150497867044</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-748.462</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.22512e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-78.753</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.184426970816433</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6323302754709929</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.294531888600593</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.400600637356927</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.863173848471527</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.53400045001383</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.823x + -5603.650</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>510.3035093823291</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>560170766.6245534</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.747546682862158e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8562031265119606</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-557.048</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.22012e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2984099085137235</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8791336755986013</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.594035941763847</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.873597310332431</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.47236306307091</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.2135347838045</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.943x + -6714.692</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>481.2660958168094</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>49650136.99958347</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.350575643664988e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.897507102159935</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-462.0590000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.17361e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.124</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1742624290108125</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7372918313219549</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.521771812932162</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.811644344688933</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.83663410297559</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.0328088599905</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.419x + -7842.537</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>472.8891771331856</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>28408239.65208392</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.804381518473373e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9144283937340101</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-401.734</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.13532e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.81100000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03792359626600208</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7331182729724244</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.472825614000463</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.748206522146763</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.88483657007108</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.55257332379307</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.600x + -8893.673</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>467.7896614165775</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>127512352.6531525</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.504288151220924e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9241056821068518</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-359.6890000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.10868e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.258</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6389322190557999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.29395187117923</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.238708351055914</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.858394566081011</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.25996704074455</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.9861017701369</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.993x + -10116.136</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>463.0239290112445</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>381339097.4644856</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.319013594846779e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9303974673699865</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-334.443</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.09044e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.58499999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2174102017086053</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.088029671062537</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.038927741645087</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.68303614252538</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25.55913431298514</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.15739869539549</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 20.140x + -10551.996</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>458.0798676900543</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>188651834.3147243</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.191725725384624e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9349918180524557</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-322.317</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.07551e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.771</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2789375891047515</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.199250926770966</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.248095214433262</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.70736160640064</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.76594286231919</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.27536092498359</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 21.013x + -10865.610</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>453.0595149208056</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>422324301.2284553</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.11056400521917e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9378244514291909</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-295.515</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.06564e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.06100000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2726719933297478</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.055623614632268</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.101175354086276</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.463055107101084</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.5499022628461</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.46431559652837</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 22.581x + -11525.196</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>448.2523363095118</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>491171586.2060832</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.01938652258721e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9415819661731251</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-292.604</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.05665e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.15900000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.222616817627816</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.106832256456649</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.911767326299603</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.229979974930675</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29.56351252774681</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.50165181635789</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 22.919x + -11537.728</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>443.4853755438477</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>485784741.1051268</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.974394904184702e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9432194539486946</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-283.772</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.05115e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.285</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2659321263301174</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.152235822457563</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.942005816562692</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.184999579354628</v>
+      </c>
+      <c r="J11" t="n">
+        <v>30.66232521441981</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.57951358152002</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 23.657x + -11766.050</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>438.8706743763116</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>360109425.4336346</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.931007929726052e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9450493901569904</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-512.5859999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.22285e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.63200000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2727336068863681</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8698393476826706</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.608084537460634</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.589735431929222</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.69059711550178</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.55460818823437</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.863x + -6830.029</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>457.4997079118085</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>312612632.3179682</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.043693871259796e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9087480537130986</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-392.625</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.1491e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.053</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3958112980760272</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8765642391622859</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.800995321214326</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.074226612318605</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.44456479499822</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.62761733792514</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.970x + -8632.904</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>403.3609078212102</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>9279.368412308988</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.675247436031156e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9988156554213184</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-342.393</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.10827e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.63800000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4784614325994419</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.300495520323005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.009112106615301</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.477540110191591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24.38716907986659</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.08333961834244</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 19.627x + -9838.499</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>441.7997160107934</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>362464404.8865823</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.181633620200979e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9368092617042773</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-318.89</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.08546e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.941</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5085153186148947</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.017928047727818</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.666709834826022</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.005408346354286</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.26801112372376</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.26957672282155</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 20.968x + -10368.112</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>437.6099678784668</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>239907240.0106749</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.061414370027394e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9409937211675136</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-302.451</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.07034e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.149</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4106064055111844</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.076895569296044</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.133439375887749</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.436671396366434</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.37176007734292</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.43468155584721</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 22.320x + -10926.868</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>413.9216791495396</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7181.639270335022</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.801008221149333e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9984205476257983</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-290.348</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.06051e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.318</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2247783854365876</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9420812597613175</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.796989685216409</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.226006776159974</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.78371348462237</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.49497990291154</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 22.858x + -11031.725</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>405.7518897540633</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3530.122982021144</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.746351472270337e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8405277647447856</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-283.67</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.05404e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.416</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4858896500989283</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.246049735318378</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.949304017107382</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.409348568570824</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.53295388773145</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.59416461102664</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 23.801x + -11395.359</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>407.5285837146329</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3497.19075329124</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.435726347952618e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7784829378881105</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-277.1820000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.04961e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.52200000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.09847322629938747</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9243186369749968</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.828073945252128</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.112744126261214</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.2803411373005</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.60864652955547</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 23.946x + -11315.451</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>412.6356352748284</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3466.283946499125</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.559443951561254e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9792420809295083</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-275.333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.0466e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.578</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2538001115545359</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9842765939257518</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.976379855157723</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.059520054268474</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.29164892220447</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.6386457399631</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 24.250x + -11341.202</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>398.0667829807337</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3436.279317545162</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.445688758224025e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7797991419828746</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-270.114</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.04342e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.661</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2129077917083431</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.070612087741861</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.98681041543249</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.62128448619094</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32.78802215592863</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.67719434439918</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 24.653x + -11416.140</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>397.396766860261</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3404.429639909844</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.910935847238245e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7744668085293805</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-260.621</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.03987e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.752</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.613263766501153</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.261639875322701</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.305253206345751</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.806485475902905</v>
+      </c>
+      <c r="J12" t="n">
+        <v>33.76448618335485</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.81009305977385</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 26.151x + -12062.416</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>393.4547150869861</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3376.897137777153</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.316767111265437e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.7529243354056714</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-258.417</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.04002e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.804</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3722886007709775</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.395146977259223</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.359847920868554</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.318396579603955</v>
+      </c>
+      <c r="J13" t="n">
+        <v>33.69892292556712</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.8205424696433</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 26.276x + -11996.189</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>391.0891370872379</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3350.051935983317</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.047276587104414e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.7955704223007315</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-258.862</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.03873e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.83799999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.354044236440671</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.228885902515347</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.162738266499807</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.585393898011672</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33.99439767109963</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.81078071201776</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 26.159x + -11820.668</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>393.6635995248881</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6693.224436311711</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.734491907564514e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9998477806299197</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-253.519</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.03755e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.923</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1138258593208402</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9904127030817002</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.795755995533814</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.114755631809096</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.34160662694209</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.80126866914307</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 26.046x + -11618.539</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>401.7714964571455</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>110136818.9024218</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.738074642512763e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9544302529760966</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-251.8559999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.03504e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.964</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1654709225932478</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.243660192253664</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.961076126071156</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.95384570279446</v>
+      </c>
+      <c r="J16" t="n">
+        <v>35.4428691564582</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.85506756801165</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 26.700x + -11837.104</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>398.604764654611</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>217461088.2834669</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.724765264228142e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9549944994411119</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-252.708</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.03351e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.98</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4689263664283869</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.09383119965625</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.171182420792224</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.477711087984271</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.64000641714301</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.87431166686969</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 26.942x + -11856.623</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>395.4786579321065</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>218565100.2905012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.717446277148552e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9553056574385524</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-250.297</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.03396e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.03400000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2590507331233595</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.097233807556352</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.840785113532157</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.537842367716643</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.19008420517838</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.87075907823763</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 26.897x + -11709.909</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>392.3821265747468</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>320922055.6702399</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.706710776409562e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9559371910029408</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-250.292</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.03227e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.072</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.179263955957194</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8502379229694961</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.882994969455472</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.262700247347318</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.92074830151425</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.87213590775382</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 26.914x + -11602.875</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>389.2297349092733</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>424392238.0302437</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.695351437307313e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9564556629632146</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-238.028</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.03251e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.179</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3704925876254813</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.336372605556543</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.151956238112274</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.37506092115072</v>
+      </c>
+      <c r="J20" t="n">
+        <v>36.88059889262986</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.98453019173634</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 28.416x + -12183.948</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>386.1861154748777</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>423121026.1880721</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.674479118209682e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9576380706450214</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-242.771</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.03131e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.175</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3994804786415376</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.146492231588173</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.290161651375075</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.658428291943398</v>
+      </c>
+      <c r="J21" t="n">
+        <v>36.39426736182816</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.94558538440631</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 27.877x + -11829.639</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>383.0878902717469</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1043691509.916825</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.6718394981589e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9577174277947021</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-239.959</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.03144e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.227</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2128092192072268</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8987857300538579</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.96662963401963</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.459431524946105</v>
+      </c>
+      <c r="J22" t="n">
+        <v>36.52333326679923</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.95924052707389</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 28.064x + -11793.208</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>379.979431224596</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>104725804.1511465</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.660548930483863e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9583700677178829</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-672.124</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.17122e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.84</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.22368219778042</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5176941506163643</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.232181209490716</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.665603301512612</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.57533922269205</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.30135020506781</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.021x + -6202.506</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>496.4300008690061</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>270503285.953953</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.971412741518568e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8741619200281474</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-462.144</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.13894e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.291</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5775538096748181</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.107257940958444</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.946663922396656</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.548398968201671</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.38649034700869</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.16611206061488</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.922x + -8055.543</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>462.2924872699581</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>386408749.5787792</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.696957143001951e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9163403427526926</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-373.249</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.0923e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.303</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3451219304581013</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9832540586188205</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.948404961926173</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.032810017928474</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.07642996612148</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.89790606768399</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 18.452x + -9600.725</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>452.7040384209214</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>372439264.3355919</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.284121272966834e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9308259589892216</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-331.0459999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.06293e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.782</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5014116526935954</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.083349003992867</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.953325131456958</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.344098879667673</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.69663370893696</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.25868349814803</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 20.885x + -10692.072</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>446.8893871986931</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>443629263.2080497</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.097473312523191e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9375291038585979</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-300.462</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.04438e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.137</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3186688345224311</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.197259631775435</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.988602461542484</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.281872821617615</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.10508064868849</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.46486275737671</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 22.586x + -11363.750</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>441.2957596951944</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>120762018.9660457</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.973416487429197e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9423403938295931</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-285.783</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.03261e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.327</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6217782950061154</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.378947597215335</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.293908828987977</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.489335476302424</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.78389211918288</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.62832172715183</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 24.145x + -11997.677</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>399.5036448819612</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5394.212979040413</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9.208391941885388e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.867647384897354</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-278.0069999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.026e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.488</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07148547961386087</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9090159341521014</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.875570720310376</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.406821273157866</v>
+      </c>
+      <c r="J8" t="n">
+        <v>32.33331500372852</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.5960437431378</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 23.820x + -11557.959</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>429.3846945898102</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>469373915.0184879</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.853134075543249e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9472507494403682</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-268.289</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.02286e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.614</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2961373587062034</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7134114230285462</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.839951526979798</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.360662519324279</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33.27114953299792</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.70247041294871</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 24.925x + -11937.196</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>401.5191020089013</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3481.605398927772</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.721666061233418e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.995610285704855</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-263.598</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.01866e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.71299999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2868318821391643</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.028715070618016</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.737793072629829</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.454932504043695</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.05470114037922</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.75258186234397</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 25.481x + -12032.781</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>400.259534994683</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3438.919964037749</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.928901445658376e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7696462191807913</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-257.052</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.01751e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.803</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1908237995194199</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.080481267471709</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.037667587069403</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.606016578900993</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35.15007195889579</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.81604736855897</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 26.222x + -12231.938</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>393.1229108155648</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3401.468041000346</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.658440801982039e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7879378883207873</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-436.0269999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.95684e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.229</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3208127548787971</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.073190683722449</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.877088444242726</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.234522444400748</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.31029355783512</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.59898046193919</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 16.827x + -8917.561</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8917.560906360937</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>392.3852699213554</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>436.0269999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.438600227885863e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9994679136179709</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-397.9630000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.93942e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.654</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1231714171600944</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7130234854191176</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.702595518853785</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.885321865869633</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22.50477610680859</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.84187794720729</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 18.124x + -9369.249</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9369.249437810791</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>396.0456486697562</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>397.9630000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.78915101036418e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9999204281533011</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-366.481</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.93022e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.976</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1753272424821282</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8738414020778685</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.865122512914454</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.18940407417868</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24.74606660616811</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.07381138958991</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 19.563x + -9930.846</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9930.846499784375</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>400.0436482782952</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>366.481</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.802709651195645e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9998357885914216</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-353.082</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.92323e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.145</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3648508373970669</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.039597550228843</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.885255374837915</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.21940974697796</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.78714942178529</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.22672167315558</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 20.644x + -10328.323</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10328.32300117538</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>438.2503615064896</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>353.082</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.818973701837098e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9411084336405583</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-344.706</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.91832e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.27500000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4321565143512269</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.023357505890349</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.955316327773355</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.182214669039217</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.37599565327824</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.29904299341725</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 21.197x + -10436.236</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10436.23635366751</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>396.8350111428777</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>344.706</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.615074796157945e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.99486852195708</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-323.819</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.91547e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.476</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3172675111350877</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.157184541831332</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.217424748782278</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.717595493427388</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.8774494467614</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.43089619523025</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 22.287x + -10820.748</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10820.7482676827</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>428.0516198845814</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>323.819</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.722918176483303e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9457552793606907</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-326.3699999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.91229e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.533</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.771941403216189</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.822827469753552</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.256847868231681</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.61904033384828</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.36127043195773</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 21.698x + -10337.404</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10337.40422219515</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>404.595726137393</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>326.3699999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.757651812312542e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9997968082972996</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-309.6209999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.91113e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2723414596402358</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.171441207398501</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.994259193936862</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.67011912879991</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.16440290734911</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.54139385253745</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 23.290x + -11034.898</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11034.89805168537</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>396.344364468504</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>309.6209999999999</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.674240548518478e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.796426022002927</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-301.8200000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.90915e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.752</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6357019505659253</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.547274509438579</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.058392608206847</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.571404123191046</v>
+      </c>
+      <c r="J10" t="n">
+        <v>30.65718330154114</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.62724237395334</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 24.134x + -11342.238</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11342.23762260074</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>416.6103328079388</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>301.8200000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.34341227999384e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9473352648101334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-302.818</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.90844e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.788</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3736837694569778</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.072550711670762</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.991903264101188</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.516652578434989</v>
+      </c>
+      <c r="J11" t="n">
+        <v>30.71783060294778</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.60634959575397</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 23.923x + -11101.298</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11101.29796171167</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>398.2819710877487</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>302.818</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.02322983282711e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8546244248852769</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>87.32876199545412</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 21.434x + -11454.311</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-11454.311163739</v>
       </c>
       <c r="Y2" t="n">
         <v>396.7494757253389</v>
       </c>
       <c r="Z2" t="n">
-        <v>9476.531367599982</v>
+        <v>301.671</v>
       </c>
       <c r="AA2" t="n">
         <v>2.882106739746401e-07</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>87.58173862750681</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 23.679x + -11972.298</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-11972.29840595214</v>
       </c>
       <c r="Y3" t="n">
         <v>444.3248684806564</v>
       </c>
       <c r="Z3" t="n">
-        <v>124542088.0869367</v>
+        <v>274.621</v>
       </c>
       <c r="AA3" t="n">
         <v>2.872969470109779e-07</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>87.68526055021523</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 24.739x + -12293.225</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-12293.22524157472</v>
       </c>
       <c r="Y4" t="n">
         <v>438.6912072937703</v>
       </c>
       <c r="Z4" t="n">
-        <v>180002047.1834024</v>
+        <v>269.188</v>
       </c>
       <c r="AA4" t="n">
         <v>2.833385558037288e-07</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>87.70455818397799</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 24.947x + -12220.466</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-12220.46556277548</v>
       </c>
       <c r="Y5" t="n">
         <v>417.8418410683744</v>
       </c>
       <c r="Z5" t="n">
-        <v>5838.71159234117</v>
+        <v>265.18</v>
       </c>
       <c r="AA5" t="n">
         <v>4.397371370064106e-07</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>87.85913255689807</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 26.750x + -13032.513</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13032.51340970559</v>
       </c>
       <c r="Y6" t="n">
         <v>407.3648962783021</v>
       </c>
       <c r="Z6" t="n">
-        <v>3541.201247124014</v>
+        <v>253.147</v>
       </c>
       <c r="AA6" t="n">
         <v>1.883231697752806e-06</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>87.83021175901268</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 26.394x + -12696.378</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-12696.37825638546</v>
       </c>
       <c r="Y7" t="n">
         <v>409.4310658951832</v>
       </c>
       <c r="Z7" t="n">
-        <v>3513.279001399675</v>
+        <v>256.03</v>
       </c>
       <c r="AA7" t="n">
         <v>2.832195786694801e-06</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>87.87954763265597</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 27.008x + -12867.182</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12867.18162016381</v>
       </c>
       <c r="Y8" t="n">
         <v>410.3922897139009</v>
       </c>
       <c r="Z8" t="n">
-        <v>3480.175744170541</v>
+        <v>249.344</v>
       </c>
       <c r="AA8" t="n">
         <v>2.436075765014825e-06</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>87.89616406398055</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 27.222x + -12859.536</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12859.53640128036</v>
       </c>
       <c r="Y9" t="n">
         <v>401.8272138803461</v>
       </c>
       <c r="Z9" t="n">
-        <v>3451.573212426066</v>
+        <v>253.11</v>
       </c>
       <c r="AA9" t="n">
         <v>2.042168233436052e-06</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>87.85680783890082</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 26.721x + -12442.841</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-12442.84112008396</v>
       </c>
       <c r="Y10" t="n">
         <v>398.0725959979554</v>
       </c>
       <c r="Z10" t="n">
-        <v>3420.699389341019</v>
+        <v>251.138</v>
       </c>
       <c r="AA10" t="n">
         <v>2.163559562718493e-06</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>87.92552157173371</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 27.607x + -12767.128</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-12767.12813026552</v>
       </c>
       <c r="Y11" t="n">
         <v>394.9177349925651</v>
       </c>
       <c r="Z11" t="n">
-        <v>3391.415712651376</v>
+        <v>246.883</v>
       </c>
       <c r="AA11" t="n">
         <v>2.207869693961968e-06</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>87.97173264315612</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 28.237x + -12949.649</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-12949.64916619227</v>
       </c>
       <c r="Y12" t="n">
         <v>392.6016724387123</v>
       </c>
       <c r="Z12" t="n">
-        <v>3360.517903602971</v>
+        <v>243.092</v>
       </c>
       <c r="AA12" t="n">
         <v>2.052067875112602e-06</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>87.96799672088163</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 28.185x + -12800.423</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-12800.42298278033</v>
       </c>
       <c r="Y13" t="n">
         <v>396.7291897181614</v>
       </c>
       <c r="Z13" t="n">
-        <v>5447.895109564663</v>
+        <v>244.6220000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>1.086245210894876e-06</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>87.94510256937021</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 27.871x + -12513.055</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-12513.05546288944</v>
       </c>
       <c r="Y14" t="n">
         <v>392.4449466826355</v>
       </c>
       <c r="Z14" t="n">
-        <v>6664.223827601112</v>
+        <v>245.7910000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>3.80176729512535e-07</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>87.98725928861322</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 28.455x + -12665.157</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-12665.15693548672</v>
       </c>
       <c r="Y15" t="n">
         <v>399.7722451537153</v>
       </c>
       <c r="Z15" t="n">
-        <v>109184778.3241984</v>
+        <v>239.637</v>
       </c>
       <c r="AA15" t="n">
         <v>2.641568219533586e-07</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>88.03368550909551</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 29.127x + -12882.958</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-12882.958399677</v>
       </c>
       <c r="Y16" t="n">
         <v>396.4967727724966</v>
       </c>
       <c r="Z16" t="n">
-        <v>433539134.4037449</v>
+        <v>239.664</v>
       </c>
       <c r="AA16" t="n">
         <v>2.636242338467464e-07</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>87.95778491032624</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 28.044x + -12228.123</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-12228.12304005591</v>
       </c>
       <c r="Y17" t="n">
         <v>393.2524944883046</v>
       </c>
       <c r="Z17" t="n">
-        <v>214709801.261642</v>
+        <v>243.848</v>
       </c>
       <c r="AA17" t="n">
         <v>2.629495894298315e-07</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>88.01332091202561</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 28.828x + -12471.714</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-12471.71380696104</v>
       </c>
       <c r="Y18" t="n">
         <v>389.9716284979895</v>
       </c>
       <c r="Z18" t="n">
-        <v>213081000.0809783</v>
+        <v>237.5960000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>2.615101207613322e-07</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>88.08313119401684</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 29.879x + -12841.971</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-12841.97133392083</v>
       </c>
       <c r="Y19" t="n">
         <v>386.7074171342449</v>
       </c>
       <c r="Z19" t="n">
-        <v>421719329.5008657</v>
+        <v>231.955</v>
       </c>
       <c r="AA19" t="n">
         <v>2.602481999857752e-07</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>88.08689395371252</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 29.938x + -12743.901</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-12743.90095813156</v>
       </c>
       <c r="Y20" t="n">
         <v>383.4161594966821</v>
       </c>
       <c r="Z20" t="n">
-        <v>156971907.8893668</v>
+        <v>231.742</v>
       </c>
       <c r="AA20" t="n">
         <v>2.596409672831079e-07</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>88.02856032291847</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 29.051x + -12207.673</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-12207.67305997291</v>
       </c>
       <c r="Y21" t="n">
         <v>380.0833278472551</v>
       </c>
       <c r="Z21" t="n">
-        <v>417669598.8100793</v>
+        <v>237.4179999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>2.59198318755664e-07</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>88.07628340723382</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 29.773x + -12408.931</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-12408.9306361771</v>
       </c>
       <c r="Y22" t="n">
         <v>376.7321260772224</v>
       </c>
       <c r="Z22" t="n">
-        <v>821698538.8496218</v>
+        <v>233.336</v>
       </c>
       <c r="AA22" t="n">
         <v>2.583546293951973e-07</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-450.226</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.00357e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.938</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4200011734694252</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9940472693558702</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.746159550582137</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.223935769902778</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.43501072245498</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.38020420064518</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 15.807x + -8443.835</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8443.835225751443</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>389.2641854037344</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>450.226</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.691687203878487e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9999915846588626</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-367.91</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.97585e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.81999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2610396645436801</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9536879091524775</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.79275854437065</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.387927028194629</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24.36001526537238</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.01377844719572</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 19.169x + -9732.232</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9732.232477525022</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>444.3892088893612</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.978991088999044e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9368204391709387</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-336.725</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.95816e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.15900000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1470599752502239</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8098500558071156</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.77566232502651</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.967191458864904</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.60964515202612</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.23446466668166</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 20.702x + -10335.718</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10335.71761182124</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>440.0568515880346</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>336.725</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.860956787255022e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9415976713744054</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-316.309</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.94808e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.361</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4618229172716094</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.028033940687215</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.024578423614556</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.552723677713138</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29.18547583600702</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.41994073913304</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 22.192x + -10994.988</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10994.98780652848</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>398.2001340594994</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>316.309</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.860492604380701e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9977171249270285</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-306.176</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.93611e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4406566577300882</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.224184212609088</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.980234040924987</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.362890998537315</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.93763837413455</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.53032833875157</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 23.185x + -11392.269</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-11392.26888037231</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>432.9405962807775</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>306.176</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.740835969958982e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9464005142652194</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-307.239</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.92993e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.57899999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4409145931804097</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.483459448980113</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.918185676655043</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.74914148719506</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.41936889334809</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 22.187x + -10691.157</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10691.1573461141</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>429.2720127468851</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>307.239</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.711191797803587e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9475764609978318</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-293.404</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.92702e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.688</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3555821745237654</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.01892165317923</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.098937101313518</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.63449850937999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.85563833481953</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.61896829912003</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 24.050x + -11568.185</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11568.18492996886</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>400.6062179018882</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>293.404</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.372327666852999e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8122906554785371</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-287.354</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.92354e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.779</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2538486486890528</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.078896447741263</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.912195124435945</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.545770803606079</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32.81621361214628</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.63267641090459</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 24.189x + -11495.585</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11495.58480201084</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>398.3053204553214</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>287.354</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.887831323794435e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8276861352393354</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-287.978</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.91975e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.809</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2284271559336333</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.066283491837474</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.754211385509747</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.162314727567449</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.89781039037618</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.65642212767953</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 24.434x + -11513.671</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11513.67109539355</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>396.1497307437309</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>287.978</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.431068250308762e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8343893934695371</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-273.841</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.91844e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.93600000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4938271616686675</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.111066459321754</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.189362207831645</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.679355763108733</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.48164743078598</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.76719803237502</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 25.648x + -12010.666</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-12010.66582961547</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>401.7231552261159</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>273.841</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.456768027234675e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.885752725635782</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-279.389</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.91816e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.922</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4947257992760141</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.099528210342078</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.245421529545161</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.947758798134435</v>
+      </c>
+      <c r="J12" t="n">
+        <v>33.61806720268441</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.75235859302603</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 25.478x + -11829.414</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-11829.41361215599</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>399.3818093506226</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>279.389</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.383942218219332e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.7488318759247224</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-274.962</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.91696e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.986</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4390437822853679</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.190577909762701</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.1365858216495</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.631496692370797</v>
+      </c>
+      <c r="J13" t="n">
+        <v>33.99677059479588</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.78795154004231</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 25.889x + -11915.852</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11915.85226544596</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>389.5323363948127</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>274.962</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>9.195862087507691e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9070175407960126</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-272.161</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.91522e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-85.05200000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.07428125808921056</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7621182230113378</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.661652042756442</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.102370154811961</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33.9949937823656</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.75696375283815</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 25.531x + -11602.944</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-11602.94415101687</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>387.823236919842</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>272.161</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.338465187457495e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.865753442133903</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-274.611</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.91392e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-85.06</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1561381419973648</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8682838816269173</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.027847680292711</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.434234717493796</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.03108187241908</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.77691167013957</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 25.760x + -11623.649</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11623.64944297491</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>385.9210006002306</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>274.611</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.278261324028647e-06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.77288927840608</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-274.359</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.91196e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-85.111</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5406235753610936</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.604850120855607</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.045549583949026</v>
+      </c>
+      <c r="J16" t="n">
+        <v>33.96892950447808</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.71409752347942</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 25.052x + -11144.202</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11144.20187366029</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>382.8073391755756</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>274.359</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.036033224453668e-06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.7812191704554601</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-265.248</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.91286e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.16800000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.650749816330784</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.166208192314804</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.179828495566464</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.54213652614677</v>
+      </c>
+      <c r="J17" t="n">
+        <v>35.15004559538603</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.87357340832048</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 26.932x + -11978.889</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-11978.88868680382</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>380.5451129956429</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>265.248</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.320747769681876e-06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.751164802217363</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-263.126</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.91463e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.21599999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.05420246270827726</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9927384045948704</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.061011591951937</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.190229444078986</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.14029471201894</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.8496137014821</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 26.632x + -11703.522</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-11703.52185731023</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>378.2082836349923</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>263.126</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.495366725827964e-06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.737177830170329</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-262.763</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.91275e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.255</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.02074758537599437</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8791161195569749</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.003659716593457</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.566232325911919</v>
+      </c>
+      <c r="J19" t="n">
+        <v>35.80680584834101</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.85397681378903</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 26.686x + -11613.070</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-11613.07042188007</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>381.0013491713657</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>262.763</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.300741278904517e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9817457185723493</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-264.878</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.91232e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.26600000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.02091128691412585</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.854479775133777</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.746977837737144</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.312514852597034</v>
+      </c>
+      <c r="J20" t="n">
+        <v>35.2493281205692</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.84760266490638</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 26.607x + -11474.180</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-11474.17973212605</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>387.8804115815154</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>264.878</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.525816888742271e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.95700397432562</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-261.5310000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.91346e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.298</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5495179612628041</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.224370708847964</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.227174929898299</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.14077312965572</v>
+      </c>
+      <c r="J21" t="n">
+        <v>36.03113036579494</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.92485720785696</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 27.598x + -11847.352</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-11847.35195363607</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>384.7771348296757</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>261.5310000000001</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.52074311950449e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9573990661956717</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-257.716</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.91362e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.358</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2979968033085993</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.028356861479891</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.029766236861083</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.551030700104907</v>
+      </c>
+      <c r="J22" t="n">
+        <v>36.1762515043449</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.93518090933146</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 27.737x + -11786.014</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-11786.01441180474</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>381.7412887030474</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>257.716</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.508632464002284e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9581466573941858</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>83.18999817840536</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.374x + -5401.071</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5401.071129848235</v>
       </c>
       <c r="Y2" t="n">
         <v>514.5894486391926</v>
       </c>
       <c r="Z2" t="n">
-        <v>285869104.6976956</v>
+        <v>810.442</v>
       </c>
       <c r="AA2" t="n">
         <v>5.772404767762741e-07</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>84.75512454019101</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 10.894x + -6178.568</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6178.567879544428</v>
       </c>
       <c r="Y3" t="n">
         <v>483.0142044814073</v>
       </c>
       <c r="Z3" t="n">
-        <v>268188951.6084123</v>
+        <v>619.3349999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>4.537211082018327e-07</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>85.55562048662085</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.866x + -7064.024</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7064.023934502686</v>
       </c>
       <c r="Y4" t="n">
         <v>473.6879955288285</v>
       </c>
       <c r="Z4" t="n">
-        <v>390715133.1608049</v>
+        <v>529.5049999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>4.025617682073349e-07</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>86.07531142267271</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.576x + -7877.713</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7877.713155714914</v>
       </c>
       <c r="Y5" t="n">
         <v>468.1671033032571</v>
       </c>
       <c r="Z5" t="n">
-        <v>193121447.887839</v>
+        <v>472.145</v>
       </c>
       <c r="AA5" t="n">
         <v>3.716303751517951e-07</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>86.44645856337118</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.103x + -8563.418</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8563.418396649791</v>
       </c>
       <c r="Y6" t="n">
         <v>463.1888459470676</v>
       </c>
       <c r="Z6" t="n">
-        <v>412945724.0501981</v>
+        <v>424.6659999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>3.493779008537029e-07</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>86.65975374096946</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.134x + -8990.945</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8990.945290288122</v>
       </c>
       <c r="Y7" t="n">
         <v>458.0781117823967</v>
       </c>
       <c r="Z7" t="n">
-        <v>251336372.6764174</v>
+        <v>402.571</v>
       </c>
       <c r="AA7" t="n">
         <v>3.355757330395731e-07</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>86.89567991017859</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.439x + -9548.569</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9548.56906772902</v>
       </c>
       <c r="Y8" t="n">
         <v>453.1056739293182</v>
       </c>
       <c r="Z8" t="n">
-        <v>248391625.5926813</v>
+        <v>372.673</v>
       </c>
       <c r="AA8" t="n">
         <v>3.227873529410139e-07</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>86.9898135424009</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.016x + -9704.214</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9704.214409331875</v>
       </c>
       <c r="Y9" t="n">
         <v>448.1286515640717</v>
       </c>
       <c r="Z9" t="n">
-        <v>321752148.2150379</v>
+        <v>362.136</v>
       </c>
       <c r="AA9" t="n">
         <v>3.147105274599211e-07</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>87.10116706600029</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.748x + -9930.241</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9930.241038703818</v>
       </c>
       <c r="Y10" t="n">
         <v>443.3643763277236</v>
       </c>
       <c r="Z10" t="n">
-        <v>364039937.4832708</v>
+        <v>345.299</v>
       </c>
       <c r="AA10" t="n">
         <v>3.068180290307751e-07</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>87.27482393024709</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 21.009x + -10483.117</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10483.1173978412</v>
       </c>
       <c r="Y11" t="n">
         <v>438.8792344827597</v>
       </c>
       <c r="Z11" t="n">
-        <v>241205774.9745677</v>
+        <v>330.157</v>
       </c>
       <c r="AA11" t="n">
         <v>3.006781957533359e-07</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.57652688229666</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.927x + -6760.276</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6760.275873835084</v>
       </c>
       <c r="Y2" t="n">
         <v>450.8678769253131</v>
       </c>
       <c r="Z2" t="n">
-        <v>123242275.114243</v>
+        <v>517.6370000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>3.884791817255893e-07</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>86.57243820920476</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.696x + -8375.073</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8375.07279202027</v>
       </c>
       <c r="Y3" t="n">
         <v>439.6563681340648</v>
       </c>
       <c r="Z3" t="n">
-        <v>180977512.9080008</v>
+        <v>410.001</v>
       </c>
       <c r="AA3" t="n">
         <v>3.366011558935878e-07</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>86.99561876236625</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 19.053x + -9418.214</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9418.213977467049</v>
       </c>
       <c r="Y4" t="n">
         <v>395.293628619102</v>
       </c>
       <c r="Z4" t="n">
-        <v>5395.605148669591</v>
+        <v>360.9400000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>8.798345134825952e-07</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>87.26124801782844</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 20.904x + -10235.100</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10235.1003737776</v>
       </c>
       <c r="Y5" t="n">
         <v>431.024296780722</v>
       </c>
       <c r="Z5" t="n">
-        <v>241022262.4156938</v>
+        <v>331.812</v>
       </c>
       <c r="AA5" t="n">
         <v>3.036202999131847e-07</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>87.37059469986423</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 21.775x + -10519.781</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10519.78062742743</v>
       </c>
       <c r="Y6" t="n">
         <v>402.2937102302833</v>
       </c>
       <c r="Z6" t="n">
-        <v>3512.599583949087</v>
+        <v>315.943</v>
       </c>
       <c r="AA6" t="n">
         <v>1.287681571068858e-06</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>87.4355951855562</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 22.328x + -10653.125</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10653.12477143453</v>
       </c>
       <c r="Y7" t="n">
         <v>405.4904995387254</v>
       </c>
       <c r="Z7" t="n">
-        <v>3480.233216384322</v>
+        <v>306.8489999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>2.353391950136328e-06</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>87.46913154353524</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 22.624x + -10653.923</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10653.92286913183</v>
       </c>
       <c r="Y8" t="n">
         <v>402.3831554181585</v>
       </c>
       <c r="Z8" t="n">
-        <v>3451.586194284745</v>
+        <v>296.956</v>
       </c>
       <c r="AA8" t="n">
         <v>2.05675726637929e-06</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>87.55871172853033</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 23.455x + -11004.725</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11004.72459310727</v>
       </c>
       <c r="Y9" t="n">
         <v>403.8965751825108</v>
       </c>
       <c r="Z9" t="n">
-        <v>3427.772219435024</v>
+        <v>295.492</v>
       </c>
       <c r="AA9" t="n">
         <v>1.826980749065107e-06</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>87.62033215672666</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 24.063x + -11176.696</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11176.69561498338</v>
       </c>
       <c r="Y10" t="n">
         <v>394.3707398400769</v>
       </c>
       <c r="Z10" t="n">
-        <v>3400.063772847948</v>
+        <v>284.792</v>
       </c>
       <c r="AA10" t="n">
         <v>2.130406602422708e-06</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>87.62493867185771</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 24.110x + -11078.258</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11078.25843263301</v>
       </c>
       <c r="Y11" t="n">
         <v>392.2629985923898</v>
       </c>
       <c r="Z11" t="n">
-        <v>3373.167806019072</v>
+        <v>282.722</v>
       </c>
       <c r="AA11" t="n">
         <v>2.190957564552214e-06</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>87.7093320023989</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 24.999x + -11416.585</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-11416.58527712284</v>
       </c>
       <c r="Y12" t="n">
         <v>389.4832884581104</v>
       </c>
       <c r="Z12" t="n">
-        <v>3345.463254356214</v>
+        <v>277.197</v>
       </c>
       <c r="AA12" t="n">
         <v>9.44109590473631e-07</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>87.73285262931817</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 25.259x + -11422.213</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11422.21325459859</v>
       </c>
       <c r="Y13" t="n">
         <v>387.1864115939476</v>
       </c>
       <c r="Z13" t="n">
-        <v>3315.766509785056</v>
+        <v>271.838</v>
       </c>
       <c r="AA13" t="n">
         <v>2.085072054046103e-06</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>87.81481647224859</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 26.207x + -11779.848</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-11779.8479738181</v>
       </c>
       <c r="Y14" t="n">
         <v>391.6978607263177</v>
       </c>
       <c r="Z14" t="n">
-        <v>5379.752486957718</v>
+        <v>265.651</v>
       </c>
       <c r="AA14" t="n">
         <v>1.064923145243585e-06</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>87.82043187161247</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 26.275x + -11687.953</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11687.95348266325</v>
       </c>
       <c r="Y15" t="n">
         <v>387.3264559726508</v>
       </c>
       <c r="Z15" t="n">
-        <v>6582.322267194906</v>
+        <v>263.128</v>
       </c>
       <c r="AA15" t="n">
         <v>3.872510354953958e-07</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>87.69925981326088</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 24.890x + -10906.624</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10906.62431198059</v>
       </c>
       <c r="Y16" t="n">
         <v>395.0548991229824</v>
       </c>
       <c r="Z16" t="n">
-        <v>215610645.3962327</v>
+        <v>273.386</v>
       </c>
       <c r="AA16" t="n">
         <v>2.698851289753131e-07</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>87.72580019033398</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 25.181x + -10929.057</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10929.05680077098</v>
       </c>
       <c r="Y17" t="n">
         <v>391.9623220307058</v>
       </c>
       <c r="Z17" t="n">
-        <v>110429064.5540533</v>
+        <v>267.936</v>
       </c>
       <c r="AA17" t="n">
         <v>2.681525107923475e-07</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>87.81287807470544</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 26.184x + -11299.127</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-11299.12688764321</v>
       </c>
       <c r="Y18" t="n">
         <v>388.9329620833877</v>
       </c>
       <c r="Z18" t="n">
-        <v>424417102.6382215</v>
+        <v>259.605</v>
       </c>
       <c r="AA18" t="n">
         <v>2.664634351187337e-07</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>87.8797697509733</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 27.011x + -11597.276</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-11597.27597952438</v>
       </c>
       <c r="Y19" t="n">
         <v>385.8920534170926</v>
       </c>
       <c r="Z19" t="n">
-        <v>421248590.2657109</v>
+        <v>257.252</v>
       </c>
       <c r="AA19" t="n">
         <v>2.654126478313937e-07</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>87.88074814245793</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 27.024x + -11485.191</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-11485.19132452939</v>
       </c>
       <c r="Y20" t="n">
         <v>382.817670241769</v>
       </c>
       <c r="Z20" t="n">
-        <v>208983998.0971246</v>
+        <v>256.595</v>
       </c>
       <c r="AA20" t="n">
         <v>2.644063102284988e-07</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>87.82758369754721</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 26.362x + -11047.969</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-11047.96890203932</v>
       </c>
       <c r="Y21" t="n">
         <v>379.7669731489552</v>
       </c>
       <c r="Z21" t="n">
-        <v>414165340.4579787</v>
+        <v>256.1849999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>2.632497046580194e-07</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>87.9701621601189</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 28.215x + -11809.651</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-11809.65080898267</v>
       </c>
       <c r="Y22" t="n">
         <v>376.7423984880032</v>
       </c>
       <c r="Z22" t="n">
-        <v>308630477.7942852</v>
+        <v>247.955</v>
       </c>
       <c r="AA22" t="n">
         <v>2.615821687966625e-07</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>83.45949046664951</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.722x + -5528.900</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5528.900488859498</v>
       </c>
       <c r="Y2" t="n">
         <v>510.0230643160938</v>
       </c>
       <c r="Z2" t="n">
-        <v>280240702.0054348</v>
+        <v>762.902</v>
       </c>
       <c r="AA2" t="n">
         <v>5.747730760022037e-07</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>85.03443553300878</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.510x + -6517.298</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6517.297981851735</v>
       </c>
       <c r="Y3" t="n">
         <v>482.4254909750563</v>
       </c>
       <c r="Z3" t="n">
-        <v>805207626.7345194</v>
+        <v>578.886</v>
       </c>
       <c r="AA3" t="n">
         <v>4.462534064680492e-07</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.86524912306481</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.833x + -7611.660</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7611.660186011932</v>
       </c>
       <c r="Y4" t="n">
         <v>473.7800385816096</v>
       </c>
       <c r="Z4" t="n">
-        <v>260510951.643348</v>
+        <v>488.2439999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>3.942887961099986e-07</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>86.3631281959031</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.733x + -8509.877</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8509.876928372587</v>
       </c>
       <c r="Y5" t="n">
         <v>468.275077592011</v>
       </c>
       <c r="Z5" t="n">
-        <v>128529960.5918365</v>
+        <v>430.6420000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>3.631311019853731e-07</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>86.68943968421829</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.288x + -9225.698</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9225.697987366791</v>
       </c>
       <c r="Y6" t="n">
         <v>463.1657707101388</v>
       </c>
       <c r="Z6" t="n">
-        <v>190577286.1824888</v>
+        <v>393.077</v>
       </c>
       <c r="AA6" t="n">
         <v>3.433202917606022e-07</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>86.87646964071794</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.325x + -9608.469</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9608.468929090981</v>
       </c>
       <c r="Y7" t="n">
         <v>458.1120111061471</v>
       </c>
       <c r="Z7" t="n">
-        <v>754170482.2608846</v>
+        <v>365.943</v>
       </c>
       <c r="AA7" t="n">
         <v>3.28840568000323e-07</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>87.10560889338865</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 19.779x + -10257.965</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10257.96468520767</v>
       </c>
       <c r="Y8" t="n">
         <v>453.0741271720851</v>
       </c>
       <c r="Z8" t="n">
-        <v>496407696.4325032</v>
+        <v>341.428</v>
       </c>
       <c r="AA8" t="n">
         <v>3.179195488138277e-07</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>87.20011358068641</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 20.447x + -10444.717</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10444.71707993587</v>
       </c>
       <c r="Y9" t="n">
         <v>403.7724355794147</v>
       </c>
       <c r="Z9" t="n">
-        <v>9304.183362649805</v>
+        <v>328.872</v>
       </c>
       <c r="AA9" t="n">
         <v>2.894594238925443e-07</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>87.30416266343487</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 21.238x + -10705.669</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10705.66882549406</v>
       </c>
       <c r="Y10" t="n">
         <v>443.4328412523989</v>
       </c>
       <c r="Z10" t="n">
-        <v>485106620.7304722</v>
+        <v>315.638</v>
       </c>
       <c r="AA10" t="n">
         <v>3.037941546175563e-07</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>87.40591634175149</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 22.072x + -11014.710</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11014.7101948853</v>
       </c>
       <c r="Y11" t="n">
         <v>438.9773628255097</v>
       </c>
       <c r="Z11" t="n">
-        <v>720381305.7444178</v>
+        <v>305.871</v>
       </c>
       <c r="AA11" t="n">
         <v>2.994258849657866e-07</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>85.40007102497242</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.429x + -6545.016</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6545.016377602506</v>
       </c>
       <c r="Y2" t="n">
         <v>452.3508453541294</v>
       </c>
       <c r="Z2" t="n">
-        <v>248183263.2253623</v>
+        <v>528.6270000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>4.112824161963975e-07</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>86.51054109016846</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.399x + -8261.792</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8261.791834220494</v>
       </c>
       <c r="Y3" t="n">
         <v>441.1915900308161</v>
       </c>
       <c r="Z3" t="n">
-        <v>241859846.0119839</v>
+        <v>409.328</v>
       </c>
       <c r="AA3" t="n">
         <v>3.463548461689567e-07</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>87.00645554276082</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 19.122x + -9490.960</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9490.960038724663</v>
       </c>
       <c r="Y4" t="n">
         <v>436.3548310285325</v>
       </c>
       <c r="Z4" t="n">
-        <v>119278596.0502252</v>
+        <v>352.181</v>
       </c>
       <c r="AA4" t="n">
         <v>3.208848820771064e-07</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>87.22812280110165</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 20.654x + -10121.659</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10121.65857072952</v>
       </c>
       <c r="Y5" t="n">
         <v>432.4205249758801</v>
       </c>
       <c r="Z5" t="n">
-        <v>118581029.3885973</v>
+        <v>325.645</v>
       </c>
       <c r="AA5" t="n">
         <v>3.079512572913859e-07</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>87.2890872318856</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 21.119x + -10176.591</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10176.59073855654</v>
       </c>
       <c r="Y6" t="n">
         <v>408.3964641392536</v>
       </c>
       <c r="Z6" t="n">
-        <v>7101.422942289118</v>
+        <v>309.522</v>
       </c>
       <c r="AA6" t="n">
         <v>3.6379726903005e-07</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>87.50462129892919</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 22.946x + -11045.048</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11045.04798626547</v>
       </c>
       <c r="Y7" t="n">
         <v>401.966931862572</v>
       </c>
       <c r="Z7" t="n">
-        <v>3492.649307771641</v>
+        <v>299.2690000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>6.058865907241843e-07</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>87.52145584907113</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 23.102x + -10977.462</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10977.46229465216</v>
       </c>
       <c r="Y8" t="n">
         <v>398.597674306599</v>
       </c>
       <c r="Z8" t="n">
-        <v>3459.703656614961</v>
+        <v>295.419</v>
       </c>
       <c r="AA8" t="n">
         <v>1.541397465901892e-06</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>87.54544948096554</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 23.328x + -10924.741</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10924.74103120476</v>
       </c>
       <c r="Y9" t="n">
         <v>403.8846045701454</v>
       </c>
       <c r="Z9" t="n">
-        <v>3428.99574492553</v>
+        <v>285.576</v>
       </c>
       <c r="AA9" t="n">
         <v>2.308474421580248e-06</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>87.63493727598764</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 24.212x + -11256.994</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11256.99445885403</v>
       </c>
       <c r="Y10" t="n">
         <v>395.6985124484585</v>
       </c>
       <c r="Z10" t="n">
-        <v>3402.37693829069</v>
+        <v>278.53</v>
       </c>
       <c r="AA10" t="n">
         <v>2.028570739946239e-06</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>87.68112606702171</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 24.695x + -11388.271</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11388.270789623</v>
       </c>
       <c r="Y11" t="n">
         <v>392.3154123634241</v>
       </c>
       <c r="Z11" t="n">
-        <v>3372.865831297919</v>
+        <v>275.198</v>
       </c>
       <c r="AA11" t="n">
         <v>2.186959869851276e-06</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>87.73860685571304</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 25.323x + -11587.931</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-11587.93137669101</v>
       </c>
       <c r="Y12" t="n">
         <v>389.145647422873</v>
       </c>
       <c r="Z12" t="n">
-        <v>3348.019978078831</v>
+        <v>269.0719999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>8.896212750669811e-07</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>87.43887800715753</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 22.356x + -9948.767</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-9948.766866542572</v>
       </c>
       <c r="Y13" t="n">
         <v>387.430774162167</v>
       </c>
       <c r="Z13" t="n">
-        <v>3322.767583093016</v>
+        <v>272.334</v>
       </c>
       <c r="AA13" t="n">
         <v>2.689040659125571e-06</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>87.61504044963438</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 24.010x + -10693.157</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10693.15704751849</v>
       </c>
       <c r="Y14" t="n">
         <v>385.2630321057063</v>
       </c>
       <c r="Z14" t="n">
-        <v>3298.72348165928</v>
+        <v>270.4300000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>2.092965923134083e-06</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>87.80000684725178</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 26.031x + -11615.392</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11615.39179086089</v>
       </c>
       <c r="Y15" t="n">
         <v>387.811655867922</v>
       </c>
       <c r="Z15" t="n">
-        <v>6597.83021612438</v>
+        <v>263.349</v>
       </c>
       <c r="AA15" t="n">
         <v>3.87374654933605e-07</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>87.81973538823236</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 26.267x + -11609.430</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11609.43019424543</v>
       </c>
       <c r="Y16" t="n">
         <v>396.1033591762223</v>
       </c>
       <c r="Z16" t="n">
-        <v>216015388.1743194</v>
+        <v>257.817</v>
       </c>
       <c r="AA16" t="n">
         <v>2.724884697611362e-07</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>87.80958887751102</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 26.145x + -11429.527</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-11429.52742617746</v>
       </c>
       <c r="Y17" t="n">
         <v>393.1878154747255</v>
       </c>
       <c r="Z17" t="n">
-        <v>214757656.8707898</v>
+        <v>255.014</v>
       </c>
       <c r="AA17" t="n">
         <v>2.70843335055864e-07</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>87.62649270100589</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 24.126x + -10346.713</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10346.71251131366</v>
       </c>
       <c r="Y18" t="n">
         <v>390.1497452323471</v>
       </c>
       <c r="Z18" t="n">
-        <v>212996290.450841</v>
+        <v>262.587</v>
       </c>
       <c r="AA18" t="n">
         <v>2.699984214560284e-07</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>87.94026050456966</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 27.805x + -12029.670</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-12029.67002916425</v>
       </c>
       <c r="Y19" t="n">
         <v>387.1222911284498</v>
       </c>
       <c r="Z19" t="n">
-        <v>211564676.3490336</v>
+        <v>249.416</v>
       </c>
       <c r="AA19" t="n">
         <v>2.685623821567904e-07</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>87.69417283319656</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 24.835x + -10489.715</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-10489.71513985551</v>
       </c>
       <c r="Y20" t="n">
         <v>384.0414995523008</v>
       </c>
       <c r="Z20" t="n">
-        <v>836933480.7986488</v>
+        <v>259.9</v>
       </c>
       <c r="AA20" t="n">
         <v>2.681501399578432e-07</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>87.86886394465913</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 26.873x + -11335.917</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-11335.91746104349</v>
       </c>
       <c r="Y21" t="n">
         <v>381.0114202350169</v>
       </c>
       <c r="Z21" t="n">
-        <v>158367121.1464663</v>
+        <v>248.335</v>
       </c>
       <c r="AA21" t="n">
         <v>2.664095332736867e-07</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>87.75691782074087</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 25.530x + -10590.833</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-10590.83304695597</v>
       </c>
       <c r="Y22" t="n">
         <v>377.9163953705417</v>
       </c>
       <c r="Z22" t="n">
-        <v>824009950.5852665</v>
+        <v>249.9010000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>2.654781821075532e-07</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>83.53400045001383</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.823x + -5603.650</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5603.649728868509</v>
       </c>
       <c r="Y2" t="n">
         <v>510.3035093823291</v>
       </c>
       <c r="Z2" t="n">
-        <v>560170766.6245534</v>
+        <v>748.462</v>
       </c>
       <c r="AA2" t="n">
         <v>5.747546682862158e-07</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.2135347838045</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.943x + -6714.692</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6714.69197562406</v>
       </c>
       <c r="Y3" t="n">
         <v>481.2660958168094</v>
       </c>
       <c r="Z3" t="n">
-        <v>49650136.99958347</v>
+        <v>557.048</v>
       </c>
       <c r="AA3" t="n">
         <v>4.350575643664988e-07</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>86.0328088599905</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.419x + -7842.537</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7842.536772160747</v>
       </c>
       <c r="Y4" t="n">
         <v>472.8891771331856</v>
       </c>
       <c r="Z4" t="n">
-        <v>28408239.65208392</v>
+        <v>462.0590000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>3.804381518473373e-07</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>86.55257332379307</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.600x + -8893.673</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8893.673459773989</v>
       </c>
       <c r="Y5" t="n">
         <v>467.7896614165775</v>
       </c>
       <c r="Z5" t="n">
-        <v>127512352.6531525</v>
+        <v>401.734</v>
       </c>
       <c r="AA5" t="n">
         <v>3.504288151220924e-07</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>86.9861017701369</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.993x + -10116.136</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10116.13588290864</v>
       </c>
       <c r="Y6" t="n">
         <v>463.0239290112445</v>
       </c>
       <c r="Z6" t="n">
-        <v>381339097.4644856</v>
+        <v>359.6890000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>3.319013594846779e-07</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>87.15739869539549</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 20.140x + -10551.996</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10551.99627331281</v>
       </c>
       <c r="Y7" t="n">
         <v>458.0798676900543</v>
       </c>
       <c r="Z7" t="n">
-        <v>188651834.3147243</v>
+        <v>334.443</v>
       </c>
       <c r="AA7" t="n">
         <v>3.191725725384624e-07</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>87.27536092498359</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 21.013x + -10865.610</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10865.60988569405</v>
       </c>
       <c r="Y8" t="n">
         <v>453.0595149208056</v>
       </c>
       <c r="Z8" t="n">
-        <v>422324301.2284553</v>
+        <v>322.317</v>
       </c>
       <c r="AA8" t="n">
         <v>3.11056400521917e-07</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>87.46431559652837</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 22.581x + -11525.196</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11525.19590796948</v>
       </c>
       <c r="Y9" t="n">
         <v>448.2523363095118</v>
       </c>
       <c r="Z9" t="n">
-        <v>491171586.2060832</v>
+        <v>295.515</v>
       </c>
       <c r="AA9" t="n">
         <v>3.01938652258721e-07</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>87.50165181635789</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 22.919x + -11537.728</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11537.7280858147</v>
       </c>
       <c r="Y10" t="n">
         <v>443.4853755438477</v>
       </c>
       <c r="Z10" t="n">
-        <v>485784741.1051268</v>
+        <v>292.604</v>
       </c>
       <c r="AA10" t="n">
         <v>2.974394904184702e-07</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>87.57951358152002</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 23.657x + -11766.050</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11766.05015049437</v>
       </c>
       <c r="Y11" t="n">
         <v>438.8706743763116</v>
       </c>
       <c r="Z11" t="n">
-        <v>360109425.4336346</v>
+        <v>283.772</v>
       </c>
       <c r="AA11" t="n">
         <v>2.931007929726052e-07</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>85.55460818823437</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.863x + -6830.029</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6830.028950954207</v>
       </c>
       <c r="Y2" t="n">
         <v>457.4997079118085</v>
       </c>
       <c r="Z2" t="n">
-        <v>312612632.3179682</v>
+        <v>512.5859999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>4.043693871259796e-07</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>86.62761733792514</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.970x + -8632.904</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8632.903832591566</v>
       </c>
       <c r="Y3" t="n">
         <v>403.3609078212102</v>
       </c>
       <c r="Z3" t="n">
-        <v>9279.368412308988</v>
+        <v>392.625</v>
       </c>
       <c r="AA3" t="n">
         <v>2.675247436031156e-07</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>87.08333961834244</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 19.627x + -9838.499</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9838.498825688595</v>
       </c>
       <c r="Y4" t="n">
         <v>441.7997160107934</v>
       </c>
       <c r="Z4" t="n">
-        <v>362464404.8865823</v>
+        <v>342.393</v>
       </c>
       <c r="AA4" t="n">
         <v>3.181633620200979e-07</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>87.26957672282155</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 20.968x + -10368.112</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10368.1116933688</v>
       </c>
       <c r="Y5" t="n">
         <v>437.6099678784668</v>
       </c>
       <c r="Z5" t="n">
-        <v>239907240.0106749</v>
+        <v>318.89</v>
       </c>
       <c r="AA5" t="n">
         <v>3.061414370027394e-07</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>87.43468155584721</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 22.320x + -10926.868</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10926.86794640467</v>
       </c>
       <c r="Y6" t="n">
         <v>413.9216791495396</v>
       </c>
       <c r="Z6" t="n">
-        <v>7181.639270335022</v>
+        <v>302.451</v>
       </c>
       <c r="AA6" t="n">
         <v>3.801008221149333e-07</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>87.49497990291154</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 22.858x + -11031.725</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11031.72547674831</v>
       </c>
       <c r="Y7" t="n">
         <v>405.7518897540633</v>
       </c>
       <c r="Z7" t="n">
-        <v>3530.122982021144</v>
+        <v>290.348</v>
       </c>
       <c r="AA7" t="n">
         <v>1.746351472270337e-06</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>87.59416461102664</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 23.801x + -11395.359</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11395.35855692168</v>
       </c>
       <c r="Y8" t="n">
         <v>407.5285837146329</v>
       </c>
       <c r="Z8" t="n">
-        <v>3497.19075329124</v>
+        <v>283.67</v>
       </c>
       <c r="AA8" t="n">
         <v>2.435726347952618e-06</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>87.60864652955547</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 23.946x + -11315.451</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11315.45057022371</v>
       </c>
       <c r="Y9" t="n">
         <v>412.6356352748284</v>
       </c>
       <c r="Z9" t="n">
-        <v>3466.283946499125</v>
+        <v>277.1820000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>5.559443951561254e-07</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>87.6386457399631</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 24.250x + -11341.202</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11341.20189378039</v>
       </c>
       <c r="Y10" t="n">
         <v>398.0667829807337</v>
       </c>
       <c r="Z10" t="n">
-        <v>3436.279317545162</v>
+        <v>275.333</v>
       </c>
       <c r="AA10" t="n">
         <v>2.445688758224025e-06</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>87.67719434439918</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 24.653x + -11416.140</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11416.13996383517</v>
       </c>
       <c r="Y11" t="n">
         <v>397.396766860261</v>
       </c>
       <c r="Z11" t="n">
-        <v>3404.429639909844</v>
+        <v>270.114</v>
       </c>
       <c r="AA11" t="n">
         <v>1.910935847238245e-06</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>87.81009305977385</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 26.151x + -12062.416</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-12062.4157865</v>
       </c>
       <c r="Y12" t="n">
         <v>393.4547150869861</v>
       </c>
       <c r="Z12" t="n">
-        <v>3376.897137777153</v>
+        <v>260.621</v>
       </c>
       <c r="AA12" t="n">
         <v>2.316767111265437e-06</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>87.8205424696433</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 26.276x + -11996.189</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11996.18885363217</v>
       </c>
       <c r="Y13" t="n">
         <v>391.0891370872379</v>
       </c>
       <c r="Z13" t="n">
-        <v>3350.051935983317</v>
+        <v>258.417</v>
       </c>
       <c r="AA13" t="n">
         <v>2.047276587104414e-06</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>87.81078071201776</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 26.159x + -11820.668</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-11820.66809178136</v>
       </c>
       <c r="Y14" t="n">
         <v>393.6635995248881</v>
       </c>
       <c r="Z14" t="n">
-        <v>6693.224436311711</v>
+        <v>258.862</v>
       </c>
       <c r="AA14" t="n">
         <v>3.734491907564514e-07</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>87.80126866914307</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 26.046x + -11618.539</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11618.53853203202</v>
       </c>
       <c r="Y15" t="n">
         <v>401.7714964571455</v>
       </c>
       <c r="Z15" t="n">
-        <v>110136818.9024218</v>
+        <v>253.519</v>
       </c>
       <c r="AA15" t="n">
         <v>2.738074642512763e-07</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>87.85506756801165</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 26.700x + -11837.104</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11837.10365352957</v>
       </c>
       <c r="Y16" t="n">
         <v>398.604764654611</v>
       </c>
       <c r="Z16" t="n">
-        <v>217461088.2834669</v>
+        <v>251.8559999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>2.724765264228142e-07</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>87.87431166686969</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 26.942x + -11856.623</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-11856.62252356277</v>
       </c>
       <c r="Y17" t="n">
         <v>395.4786579321065</v>
       </c>
       <c r="Z17" t="n">
-        <v>218565100.2905012</v>
+        <v>252.708</v>
       </c>
       <c r="AA17" t="n">
         <v>2.717446277148552e-07</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>87.87075907823763</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 26.897x + -11709.909</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-11709.90918424021</v>
       </c>
       <c r="Y18" t="n">
         <v>392.3821265747468</v>
       </c>
       <c r="Z18" t="n">
-        <v>320922055.6702399</v>
+        <v>250.297</v>
       </c>
       <c r="AA18" t="n">
         <v>2.706710776409562e-07</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>87.87213590775382</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 26.914x + -11602.875</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-11602.87499830767</v>
       </c>
       <c r="Y19" t="n">
         <v>389.2297349092733</v>
       </c>
       <c r="Z19" t="n">
-        <v>424392238.0302437</v>
+        <v>250.292</v>
       </c>
       <c r="AA19" t="n">
         <v>2.695351437307313e-07</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>87.98453019173634</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 28.416x + -12183.948</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-12183.94804322583</v>
       </c>
       <c r="Y20" t="n">
         <v>386.1861154748777</v>
       </c>
       <c r="Z20" t="n">
-        <v>423121026.1880721</v>
+        <v>238.028</v>
       </c>
       <c r="AA20" t="n">
         <v>2.674479118209682e-07</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>87.94558538440631</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 27.877x + -11829.639</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-11829.63864477345</v>
       </c>
       <c r="Y21" t="n">
         <v>383.0878902717469</v>
       </c>
       <c r="Z21" t="n">
-        <v>1043691509.916825</v>
+        <v>242.771</v>
       </c>
       <c r="AA21" t="n">
         <v>2.6718394981589e-07</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>87.95924052707389</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 28.064x + -11793.208</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-11793.20759591702</v>
       </c>
       <c r="Y22" t="n">
         <v>379.979431224596</v>
       </c>
       <c r="Z22" t="n">
-        <v>104725804.1511465</v>
+        <v>239.959</v>
       </c>
       <c r="AA22" t="n">
         <v>2.660548930483863e-07</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>84.30135020506781</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.021x + -6202.506</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6202.506470869546</v>
       </c>
       <c r="Y2" t="n">
         <v>496.4300008690061</v>
       </c>
       <c r="Z2" t="n">
-        <v>270503285.953953</v>
+        <v>672.124</v>
       </c>
       <c r="AA2" t="n">
         <v>4.971412741518568e-07</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>86.16611206061488</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.922x + -8055.543</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8055.542724286479</v>
       </c>
       <c r="Y3" t="n">
         <v>462.2924872699581</v>
       </c>
       <c r="Z3" t="n">
-        <v>386408749.5787792</v>
+        <v>462.144</v>
       </c>
       <c r="AA3" t="n">
         <v>3.696957143001951e-07</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>86.89790606768399</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 18.452x + -9600.725</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9600.724840700765</v>
       </c>
       <c r="Y4" t="n">
         <v>452.7040384209214</v>
       </c>
       <c r="Z4" t="n">
-        <v>372439264.3355919</v>
+        <v>373.249</v>
       </c>
       <c r="AA4" t="n">
         <v>3.284121272966834e-07</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>87.25868349814803</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 20.885x + -10692.072</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10692.07200967175</v>
       </c>
       <c r="Y5" t="n">
         <v>446.8893871986931</v>
       </c>
       <c r="Z5" t="n">
-        <v>443629263.2080497</v>
+        <v>331.0459999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>3.097473312523191e-07</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>87.46486275737671</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 22.586x + -11363.750</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-11363.75009103374</v>
       </c>
       <c r="Y6" t="n">
         <v>441.2957596951944</v>
       </c>
       <c r="Z6" t="n">
-        <v>120762018.9660457</v>
+        <v>300.462</v>
       </c>
       <c r="AA6" t="n">
         <v>2.973416487429197e-07</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>87.62832172715183</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 24.145x + -11997.677</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11997.67667630151</v>
       </c>
       <c r="Y7" t="n">
         <v>399.5036448819612</v>
       </c>
       <c r="Z7" t="n">
-        <v>5394.212979040413</v>
+        <v>285.783</v>
       </c>
       <c r="AA7" t="n">
         <v>9.208391941885388e-07</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>87.5960437431378</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 23.820x + -11557.959</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11557.95890420135</v>
       </c>
       <c r="Y8" t="n">
         <v>429.3846945898102</v>
       </c>
       <c r="Z8" t="n">
-        <v>469373915.0184879</v>
+        <v>278.0069999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>2.853134075543249e-07</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>87.70247041294871</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 24.925x + -11937.196</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11937.19550199226</v>
       </c>
       <c r="Y9" t="n">
         <v>401.5191020089013</v>
       </c>
       <c r="Z9" t="n">
-        <v>3481.605398927772</v>
+        <v>268.289</v>
       </c>
       <c r="AA9" t="n">
         <v>4.721666061233418e-07</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>87.75258186234397</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 25.481x + -12032.781</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-12032.78076299674</v>
       </c>
       <c r="Y10" t="n">
         <v>400.259534994683</v>
       </c>
       <c r="Z10" t="n">
-        <v>3438.919964037749</v>
+        <v>263.598</v>
       </c>
       <c r="AA10" t="n">
         <v>1.928901445658376e-06</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>87.81604736855897</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 26.222x + -12231.938</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-12231.93795227585</v>
       </c>
       <c r="Y11" t="n">
         <v>393.1229108155648</v>
       </c>
       <c r="Z11" t="n">
-        <v>3401.468041000346</v>
+        <v>257.052</v>
       </c>
       <c r="AA11" t="n">
         <v>1.658440801982039e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>86.59898046193919</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 16.827x + -8917.561</t>
-        </is>
+      <c r="W2" t="n">
+        <v>16.82685717222788</v>
       </c>
       <c r="X2" t="n">
         <v>-8917.560906360937</v>
@@ -600,7 +598,7 @@
         <v>392.3852699213554</v>
       </c>
       <c r="Z2" t="n">
-        <v>436.0269999999999</v>
+        <v>9533.264975735194</v>
       </c>
       <c r="AA2" t="n">
         <v>2.438600227885863e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>86.84187794720729</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 18.124x + -9369.249</t>
-        </is>
+      <c r="W3" t="n">
+        <v>18.12398063236787</v>
       </c>
       <c r="X3" t="n">
         <v>-9369.249437810791</v>
@@ -652,7 +648,7 @@
         <v>396.0456486697562</v>
       </c>
       <c r="Z3" t="n">
-        <v>397.9630000000001</v>
+        <v>9362.811443314769</v>
       </c>
       <c r="AA3" t="n">
         <v>2.78915101036418e-07</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>87.07381138958991</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 19.563x + -9930.846</t>
-        </is>
+      <c r="W4" t="n">
+        <v>19.56331713381845</v>
       </c>
       <c r="X4" t="n">
         <v>-9930.846499784375</v>
@@ -704,7 +698,7 @@
         <v>400.0436482782952</v>
       </c>
       <c r="Z4" t="n">
-        <v>366.481</v>
+        <v>9220.651362595481</v>
       </c>
       <c r="AA4" t="n">
         <v>2.802709651195645e-07</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>87.22672167315558</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 20.644x + -10328.323</t>
-        </is>
+      <c r="W5" t="n">
+        <v>20.64380885308847</v>
       </c>
       <c r="X5" t="n">
         <v>-10328.32300117538</v>
@@ -756,7 +748,7 @@
         <v>438.2503615064896</v>
       </c>
       <c r="Z5" t="n">
-        <v>353.082</v>
+        <v>119712396.0346604</v>
       </c>
       <c r="AA5" t="n">
         <v>2.818973701837098e-07</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>87.29904299341725</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.197x + -10436.236</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.19742428818224</v>
       </c>
       <c r="X6" t="n">
         <v>-10436.23635366751</v>
@@ -808,7 +798,7 @@
         <v>396.8350111428777</v>
       </c>
       <c r="Z6" t="n">
-        <v>344.706</v>
+        <v>5361.791099819091</v>
       </c>
       <c r="AA6" t="n">
         <v>4.615074796157945e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>87.43089619523025</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.287x + -10820.748</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.28690615880484</v>
       </c>
       <c r="X7" t="n">
         <v>-10820.7482676827</v>
@@ -860,7 +848,7 @@
         <v>428.0516198845814</v>
       </c>
       <c r="Z7" t="n">
-        <v>323.819</v>
+        <v>584645167.8581148</v>
       </c>
       <c r="AA7" t="n">
         <v>2.722918176483303e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>87.36127043195773</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 21.698x + -10337.404</t>
-        </is>
+      <c r="W8" t="n">
+        <v>21.69804211984916</v>
       </c>
       <c r="X8" t="n">
         <v>-10337.40422219515</v>
@@ -912,7 +898,7 @@
         <v>404.595726137393</v>
       </c>
       <c r="Z8" t="n">
-        <v>326.3699999999999</v>
+        <v>7008.41535739208</v>
       </c>
       <c r="AA8" t="n">
         <v>3.757651812312542e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>87.54139385253745</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 23.290x + -11034.898</t>
-        </is>
+      <c r="W9" t="n">
+        <v>23.28986623510717</v>
       </c>
       <c r="X9" t="n">
         <v>-11034.89805168537</v>
@@ -964,7 +948,7 @@
         <v>396.344364468504</v>
       </c>
       <c r="Z9" t="n">
-        <v>309.6209999999999</v>
+        <v>3445.918760952376</v>
       </c>
       <c r="AA9" t="n">
         <v>1.674240548518478e-06</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>87.62724237395334</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 24.134x + -11342.238</t>
-        </is>
+      <c r="W10" t="n">
+        <v>24.13353190833924</v>
       </c>
       <c r="X10" t="n">
         <v>-11342.23762260074</v>
@@ -1016,7 +998,7 @@
         <v>416.6103328079388</v>
       </c>
       <c r="Z10" t="n">
-        <v>301.8200000000001</v>
+        <v>3414.342682673649</v>
       </c>
       <c r="AA10" t="n">
         <v>5.34341227999384e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>87.60634959575397</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 23.923x + -11101.298</t>
-        </is>
+      <c r="W11" t="n">
+        <v>23.92264229159832</v>
       </c>
       <c r="X11" t="n">
         <v>-11101.29796171167</v>
@@ -1068,7 +1048,7 @@
         <v>398.2819710877487</v>
       </c>
       <c r="Z11" t="n">
-        <v>302.818</v>
+        <v>3384.168171902844</v>
       </c>
       <c r="AA11" t="n">
         <v>1.02322983282711e-06</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>87.32876199545412</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 21.434x + -11454.311</t>
-        </is>
+      <c r="W2" t="n">
+        <v>21.43360519357709</v>
       </c>
       <c r="X2" t="n">
         <v>-11454.311163739</v>
@@ -1266,7 +1244,7 @@
         <v>396.7494757253389</v>
       </c>
       <c r="Z2" t="n">
-        <v>301.671</v>
+        <v>9476.531367599982</v>
       </c>
       <c r="AA2" t="n">
         <v>2.882106739746401e-07</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>87.58173862750681</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 23.679x + -11972.298</t>
-        </is>
+      <c r="W3" t="n">
+        <v>23.67889340159697</v>
       </c>
       <c r="X3" t="n">
         <v>-11972.29840595214</v>
@@ -1318,7 +1294,7 @@
         <v>444.3248684806564</v>
       </c>
       <c r="Z3" t="n">
-        <v>274.621</v>
+        <v>124542088.0869367</v>
       </c>
       <c r="AA3" t="n">
         <v>2.872969470109779e-07</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>87.68526055021523</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 24.739x + -12293.225</t>
-        </is>
+      <c r="W4" t="n">
+        <v>24.73911456287036</v>
       </c>
       <c r="X4" t="n">
         <v>-12293.22524157472</v>
@@ -1370,7 +1344,7 @@
         <v>438.6912072937703</v>
       </c>
       <c r="Z4" t="n">
-        <v>269.188</v>
+        <v>180002047.1834024</v>
       </c>
       <c r="AA4" t="n">
         <v>2.833385558037288e-07</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>87.70455818397799</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 24.947x + -12220.466</t>
-        </is>
+      <c r="W5" t="n">
+        <v>24.94732026064058</v>
       </c>
       <c r="X5" t="n">
         <v>-12220.46556277548</v>
@@ -1422,7 +1394,7 @@
         <v>417.8418410683744</v>
       </c>
       <c r="Z5" t="n">
-        <v>265.18</v>
+        <v>5838.71159234117</v>
       </c>
       <c r="AA5" t="n">
         <v>4.397371370064106e-07</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>87.85913255689807</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 26.750x + -13032.513</t>
-        </is>
+      <c r="W6" t="n">
+        <v>26.75042426324197</v>
       </c>
       <c r="X6" t="n">
         <v>-13032.51340970559</v>
@@ -1474,7 +1444,7 @@
         <v>407.3648962783021</v>
       </c>
       <c r="Z6" t="n">
-        <v>253.147</v>
+        <v>3541.201247124014</v>
       </c>
       <c r="AA6" t="n">
         <v>1.883231697752806e-06</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>87.83021175901268</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 26.394x + -12696.378</t>
-        </is>
+      <c r="W7" t="n">
+        <v>26.39353734569671</v>
       </c>
       <c r="X7" t="n">
         <v>-12696.37825638546</v>
@@ -1526,7 +1494,7 @@
         <v>409.4310658951832</v>
       </c>
       <c r="Z7" t="n">
-        <v>256.03</v>
+        <v>3513.279001399675</v>
       </c>
       <c r="AA7" t="n">
         <v>2.832195786694801e-06</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>87.87954763265597</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 27.008x + -12867.182</t>
-        </is>
+      <c r="W8" t="n">
+        <v>27.00820800647183</v>
       </c>
       <c r="X8" t="n">
         <v>-12867.18162016381</v>
@@ -1578,7 +1544,7 @@
         <v>410.3922897139009</v>
       </c>
       <c r="Z8" t="n">
-        <v>249.344</v>
+        <v>3480.175744170541</v>
       </c>
       <c r="AA8" t="n">
         <v>2.436075765014825e-06</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>87.89616406398055</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 27.222x + -12859.536</t>
-        </is>
+      <c r="W9" t="n">
+        <v>27.22171727486583</v>
       </c>
       <c r="X9" t="n">
         <v>-12859.53640128036</v>
@@ -1630,7 +1594,7 @@
         <v>401.8272138803461</v>
       </c>
       <c r="Z9" t="n">
-        <v>253.11</v>
+        <v>3451.573212426066</v>
       </c>
       <c r="AA9" t="n">
         <v>2.042168233436052e-06</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>87.85680783890082</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 26.721x + -12442.841</t>
-        </is>
+      <c r="W10" t="n">
+        <v>26.72138107005438</v>
       </c>
       <c r="X10" t="n">
         <v>-12442.84112008396</v>
@@ -1682,7 +1644,7 @@
         <v>398.0725959979554</v>
       </c>
       <c r="Z10" t="n">
-        <v>251.138</v>
+        <v>3420.699389341019</v>
       </c>
       <c r="AA10" t="n">
         <v>2.163559562718493e-06</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>87.92552157173371</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 27.607x + -12767.128</t>
-        </is>
+      <c r="W11" t="n">
+        <v>27.60729638093326</v>
       </c>
       <c r="X11" t="n">
         <v>-12767.12813026552</v>
@@ -1734,7 +1694,7 @@
         <v>394.9177349925651</v>
       </c>
       <c r="Z11" t="n">
-        <v>246.883</v>
+        <v>3391.415712651376</v>
       </c>
       <c r="AA11" t="n">
         <v>2.207869693961968e-06</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>87.97173264315612</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 28.237x + -12949.649</t>
-        </is>
+      <c r="W12" t="n">
+        <v>28.23683169947766</v>
       </c>
       <c r="X12" t="n">
         <v>-12949.64916619227</v>
@@ -1786,7 +1744,7 @@
         <v>392.6016724387123</v>
       </c>
       <c r="Z12" t="n">
-        <v>243.092</v>
+        <v>3360.517903602971</v>
       </c>
       <c r="AA12" t="n">
         <v>2.052067875112602e-06</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>87.96799672088163</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 28.185x + -12800.423</t>
-        </is>
+      <c r="W13" t="n">
+        <v>28.18487367697258</v>
       </c>
       <c r="X13" t="n">
         <v>-12800.42298278033</v>
@@ -1838,7 +1794,7 @@
         <v>396.7291897181614</v>
       </c>
       <c r="Z13" t="n">
-        <v>244.6220000000001</v>
+        <v>5447.895109564663</v>
       </c>
       <c r="AA13" t="n">
         <v>1.086245210894876e-06</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>87.94510256937021</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 27.871x + -12513.055</t>
-        </is>
+      <c r="W14" t="n">
+        <v>27.87059365664241</v>
       </c>
       <c r="X14" t="n">
         <v>-12513.05546288944</v>
@@ -1890,7 +1844,7 @@
         <v>392.4449466826355</v>
       </c>
       <c r="Z14" t="n">
-        <v>245.7910000000001</v>
+        <v>6664.223827601112</v>
       </c>
       <c r="AA14" t="n">
         <v>3.80176729512535e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>87.98725928861322</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 28.455x + -12665.157</t>
-        </is>
+      <c r="W15" t="n">
+        <v>28.454837107926</v>
       </c>
       <c r="X15" t="n">
         <v>-12665.15693548672</v>
@@ -1942,7 +1894,7 @@
         <v>399.7722451537153</v>
       </c>
       <c r="Z15" t="n">
-        <v>239.637</v>
+        <v>109184778.3241984</v>
       </c>
       <c r="AA15" t="n">
         <v>2.641568219533586e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>88.03368550909551</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 29.127x + -12882.958</t>
-        </is>
+      <c r="W16" t="n">
+        <v>29.12722468905563</v>
       </c>
       <c r="X16" t="n">
         <v>-12882.958399677</v>
@@ -1994,7 +1944,7 @@
         <v>396.4967727724966</v>
       </c>
       <c r="Z16" t="n">
-        <v>239.664</v>
+        <v>433539134.4037449</v>
       </c>
       <c r="AA16" t="n">
         <v>2.636242338467464e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>87.95778491032624</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 28.044x + -12228.123</t>
-        </is>
+      <c r="W17" t="n">
+        <v>28.04382062056042</v>
       </c>
       <c r="X17" t="n">
         <v>-12228.12304005591</v>
@@ -2046,7 +1994,7 @@
         <v>393.2524944883046</v>
       </c>
       <c r="Z17" t="n">
-        <v>243.848</v>
+        <v>214709801.261642</v>
       </c>
       <c r="AA17" t="n">
         <v>2.629495894298315e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>88.01332091202561</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 28.828x + -12471.714</t>
-        </is>
+      <c r="W18" t="n">
+        <v>28.82841819886061</v>
       </c>
       <c r="X18" t="n">
         <v>-12471.71380696104</v>
@@ -2098,7 +2044,7 @@
         <v>389.9716284979895</v>
       </c>
       <c r="Z18" t="n">
-        <v>237.5960000000001</v>
+        <v>213081000.0809783</v>
       </c>
       <c r="AA18" t="n">
         <v>2.615101207613322e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>88.08313119401684</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 29.879x + -12841.971</t>
-        </is>
+      <c r="W19" t="n">
+        <v>29.87914510773695</v>
       </c>
       <c r="X19" t="n">
         <v>-12841.97133392083</v>
@@ -2150,7 +2094,7 @@
         <v>386.7074171342449</v>
       </c>
       <c r="Z19" t="n">
-        <v>231.955</v>
+        <v>421719329.5008657</v>
       </c>
       <c r="AA19" t="n">
         <v>2.602481999857752e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>88.08689395371252</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 29.938x + -12743.901</t>
-        </is>
+      <c r="W20" t="n">
+        <v>29.93795622124546</v>
       </c>
       <c r="X20" t="n">
         <v>-12743.90095813156</v>
@@ -2202,7 +2144,7 @@
         <v>383.4161594966821</v>
       </c>
       <c r="Z20" t="n">
-        <v>231.742</v>
+        <v>156971907.8893668</v>
       </c>
       <c r="AA20" t="n">
         <v>2.596409672831079e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>88.02856032291847</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 29.051x + -12207.673</t>
-        </is>
+      <c r="W21" t="n">
+        <v>29.05144256795678</v>
       </c>
       <c r="X21" t="n">
         <v>-12207.67305997291</v>
@@ -2254,7 +2194,7 @@
         <v>380.0833278472551</v>
       </c>
       <c r="Z21" t="n">
-        <v>237.4179999999999</v>
+        <v>417669598.8100793</v>
       </c>
       <c r="AA21" t="n">
         <v>2.59198318755664e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>88.07628340723382</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 29.773x + -12408.931</t>
-        </is>
+      <c r="W22" t="n">
+        <v>29.77270581049706</v>
       </c>
       <c r="X22" t="n">
         <v>-12408.9306361771</v>
@@ -2306,7 +2244,7 @@
         <v>376.7321260772224</v>
       </c>
       <c r="Z22" t="n">
-        <v>233.336</v>
+        <v>821698538.8496218</v>
       </c>
       <c r="AA22" t="n">
         <v>2.583546293951973e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>86.38020420064518</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 15.807x + -8443.835</t>
-        </is>
+      <c r="W2" t="n">
+        <v>15.80739154497107</v>
       </c>
       <c r="X2" t="n">
         <v>-8443.835225751443</v>
@@ -2504,7 +2440,7 @@
         <v>389.2641854037344</v>
       </c>
       <c r="Z2" t="n">
-        <v>450.226</v>
+        <v>9438.734488921295</v>
       </c>
       <c r="AA2" t="n">
         <v>2.691687203878487e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>87.01377844719572</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 19.169x + -9732.232</t>
-        </is>
+      <c r="W3" t="n">
+        <v>19.16933793413983</v>
       </c>
       <c r="X3" t="n">
         <v>-9732.232477525022</v>
@@ -2556,7 +2490,7 @@
         <v>444.3892088893612</v>
       </c>
       <c r="Z3" t="n">
-        <v>367.91</v>
+        <v>275034535.7965506</v>
       </c>
       <c r="AA3" t="n">
         <v>2.978991088999044e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>87.23446466668166</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 20.702x + -10335.718</t>
-        </is>
+      <c r="W4" t="n">
+        <v>20.70169799323632</v>
       </c>
       <c r="X4" t="n">
         <v>-10335.71761182124</v>
@@ -2608,7 +2540,7 @@
         <v>440.0568515880346</v>
       </c>
       <c r="Z4" t="n">
-        <v>336.725</v>
+        <v>240621612.1324463</v>
       </c>
       <c r="AA4" t="n">
         <v>2.860956787255022e-07</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>87.41994073913304</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 22.192x + -10994.988</t>
-        </is>
+      <c r="W5" t="n">
+        <v>22.19214418862437</v>
       </c>
       <c r="X5" t="n">
         <v>-10994.98780652848</v>
@@ -2660,7 +2590,7 @@
         <v>398.2001340594994</v>
       </c>
       <c r="Z5" t="n">
-        <v>316.309</v>
+        <v>5406.38089737983</v>
       </c>
       <c r="AA5" t="n">
         <v>4.860492604380701e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>87.53032833875157</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 23.185x + -11392.269</t>
-        </is>
+      <c r="W6" t="n">
+        <v>23.18538607941273</v>
       </c>
       <c r="X6" t="n">
         <v>-11392.26888037231</v>
@@ -2712,7 +2640,7 @@
         <v>432.9405962807775</v>
       </c>
       <c r="Z6" t="n">
-        <v>306.176</v>
+        <v>177597871.0050992</v>
       </c>
       <c r="AA6" t="n">
         <v>2.740835969958982e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>87.41936889334809</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.187x + -10691.157</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.18721994445826</v>
       </c>
       <c r="X7" t="n">
         <v>-10691.1573461141</v>
@@ -2764,7 +2690,7 @@
         <v>429.2720127468851</v>
       </c>
       <c r="Z7" t="n">
-        <v>307.239</v>
+        <v>131379918.8100471</v>
       </c>
       <c r="AA7" t="n">
         <v>2.711191797803587e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>87.61896829912003</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 24.050x + -11568.185</t>
-        </is>
+      <c r="W8" t="n">
+        <v>24.04957186161613</v>
       </c>
       <c r="X8" t="n">
         <v>-11568.18492996886</v>
@@ -2816,7 +2740,7 @@
         <v>400.6062179018882</v>
       </c>
       <c r="Z8" t="n">
-        <v>293.404</v>
+        <v>3497.323809068671</v>
       </c>
       <c r="AA8" t="n">
         <v>1.372327666852999e-06</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>87.63267641090459</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 24.189x + -11495.585</t>
-        </is>
+      <c r="W9" t="n">
+        <v>24.18899217225247</v>
       </c>
       <c r="X9" t="n">
         <v>-11495.58480201084</v>
@@ -2868,7 +2790,7 @@
         <v>398.3053204553214</v>
       </c>
       <c r="Z9" t="n">
-        <v>287.354</v>
+        <v>3467.883491214865</v>
       </c>
       <c r="AA9" t="n">
         <v>1.887831323794435e-06</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>87.65642212767953</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 24.434x + -11513.671</t>
-        </is>
+      <c r="W10" t="n">
+        <v>24.43435884322485</v>
       </c>
       <c r="X10" t="n">
         <v>-11513.67109539355</v>
@@ -2920,7 +2840,7 @@
         <v>396.1497307437309</v>
       </c>
       <c r="Z10" t="n">
-        <v>287.978</v>
+        <v>3438.441035097835</v>
       </c>
       <c r="AA10" t="n">
         <v>1.431068250308762e-06</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>87.76719803237502</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 25.648x + -12010.666</t>
-        </is>
+      <c r="W11" t="n">
+        <v>25.64794079284616</v>
       </c>
       <c r="X11" t="n">
         <v>-12010.66582961547</v>
@@ -2972,7 +2890,7 @@
         <v>401.7231552261159</v>
       </c>
       <c r="Z11" t="n">
-        <v>273.841</v>
+        <v>3412.832673651475</v>
       </c>
       <c r="AA11" t="n">
         <v>1.456768027234675e-06</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>87.75235859302603</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 25.478x + -11829.414</t>
-        </is>
+      <c r="W12" t="n">
+        <v>25.47843512937785</v>
       </c>
       <c r="X12" t="n">
         <v>-11829.41361215599</v>
@@ -3024,7 +2940,7 @@
         <v>399.3818093506226</v>
       </c>
       <c r="Z12" t="n">
-        <v>279.389</v>
+        <v>3387.691293796541</v>
       </c>
       <c r="AA12" t="n">
         <v>2.383942218219332e-06</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>87.78795154004231</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 25.889x + -11915.852</t>
-        </is>
+      <c r="W13" t="n">
+        <v>25.88881323306629</v>
       </c>
       <c r="X13" t="n">
         <v>-11915.85226544596</v>
@@ -3076,7 +2990,7 @@
         <v>389.5323363948127</v>
       </c>
       <c r="Z13" t="n">
-        <v>274.962</v>
+        <v>3360.216150151757</v>
       </c>
       <c r="AA13" t="n">
         <v>9.195862087507691e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>87.75696375283815</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 25.531x + -11602.944</t>
-        </is>
+      <c r="W14" t="n">
+        <v>25.53079835059791</v>
       </c>
       <c r="X14" t="n">
         <v>-11602.94415101687</v>
@@ -3128,7 +3040,7 @@
         <v>387.823236919842</v>
       </c>
       <c r="Z14" t="n">
-        <v>272.161</v>
+        <v>3336.477931899493</v>
       </c>
       <c r="AA14" t="n">
         <v>1.338465187457495e-06</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>87.77691167013957</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 25.760x + -11623.649</t>
-        </is>
+      <c r="W15" t="n">
+        <v>25.76012107080732</v>
       </c>
       <c r="X15" t="n">
         <v>-11623.64944297491</v>
@@ -3180,7 +3090,7 @@
         <v>385.9210006002306</v>
       </c>
       <c r="Z15" t="n">
-        <v>274.611</v>
+        <v>3310.725987911137</v>
       </c>
       <c r="AA15" t="n">
         <v>2.278261324028647e-06</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>87.71409752347942</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 25.052x + -11144.202</t>
-        </is>
+      <c r="W16" t="n">
+        <v>25.05153960857943</v>
       </c>
       <c r="X16" t="n">
         <v>-11144.20187366029</v>
@@ -3232,7 +3140,7 @@
         <v>382.8073391755756</v>
       </c>
       <c r="Z16" t="n">
-        <v>274.359</v>
+        <v>3284.53309290317</v>
       </c>
       <c r="AA16" t="n">
         <v>2.036033224453668e-06</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>87.87357340832048</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 26.932x + -11978.889</t>
-        </is>
+      <c r="W17" t="n">
+        <v>26.93225865162789</v>
       </c>
       <c r="X17" t="n">
         <v>-11978.88868680382</v>
@@ -3284,7 +3190,7 @@
         <v>380.5451129956429</v>
       </c>
       <c r="Z17" t="n">
-        <v>265.248</v>
+        <v>3256.532925106155</v>
       </c>
       <c r="AA17" t="n">
         <v>2.320747769681876e-06</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>87.8496137014821</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 26.632x + -11703.522</t>
-        </is>
+      <c r="W18" t="n">
+        <v>26.63190085723615</v>
       </c>
       <c r="X18" t="n">
         <v>-11703.52185731023</v>
@@ -3336,7 +3240,7 @@
         <v>378.2082836349923</v>
       </c>
       <c r="Z18" t="n">
-        <v>263.126</v>
+        <v>3233.147256429379</v>
       </c>
       <c r="AA18" t="n">
         <v>2.495366725827964e-06</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>87.85397681378903</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 26.686x + -11613.070</t>
-        </is>
+      <c r="W19" t="n">
+        <v>26.68609740727373</v>
       </c>
       <c r="X19" t="n">
         <v>-11613.07042188007</v>
@@ -3388,7 +3290,7 @@
         <v>381.0013491713657</v>
       </c>
       <c r="Z19" t="n">
-        <v>262.763</v>
+        <v>6456.10592856806</v>
       </c>
       <c r="AA19" t="n">
         <v>3.300741278904517e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>87.84760266490638</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 26.607x + -11474.180</t>
-        </is>
+      <c r="W20" t="n">
+        <v>26.60699463907108</v>
       </c>
       <c r="X20" t="n">
         <v>-11474.17973212605</v>
@@ -3440,7 +3340,7 @@
         <v>387.8804115815154</v>
       </c>
       <c r="Z20" t="n">
-        <v>264.878</v>
+        <v>211750724.108005</v>
       </c>
       <c r="AA20" t="n">
         <v>2.525816888742271e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>87.92485720785696</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 27.598x + -11847.352</t>
-        </is>
+      <c r="W21" t="n">
+        <v>27.598450082704</v>
       </c>
       <c r="X21" t="n">
         <v>-11847.35195363607</v>
@@ -3492,7 +3390,7 @@
         <v>384.7771348296757</v>
       </c>
       <c r="Z21" t="n">
-        <v>261.5310000000001</v>
+        <v>839146429.5784309</v>
       </c>
       <c r="AA21" t="n">
         <v>2.52074311950449e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>87.93518090933146</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 27.737x + -11786.014</t>
-        </is>
+      <c r="W22" t="n">
+        <v>27.73655751015672</v>
       </c>
       <c r="X22" t="n">
         <v>-11786.01441180474</v>
@@ -3544,7 +3440,7 @@
         <v>381.7412887030474</v>
       </c>
       <c r="Z22" t="n">
-        <v>257.716</v>
+        <v>420170915.8172156</v>
       </c>
       <c r="AA22" t="n">
         <v>2.508632464002284e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>83.18999817840536</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.374x + -5401.071</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.373818569362371</v>
       </c>
       <c r="X2" t="n">
         <v>-5401.071129848235</v>
@@ -3742,7 +3636,7 @@
         <v>514.5894486391926</v>
       </c>
       <c r="Z2" t="n">
-        <v>810.442</v>
+        <v>285869104.6976956</v>
       </c>
       <c r="AA2" t="n">
         <v>5.772404767762741e-07</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>84.75512454019101</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.894x + -6178.568</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.89361439320064</v>
       </c>
       <c r="X3" t="n">
         <v>-6178.567879544428</v>
@@ -3794,7 +3686,7 @@
         <v>483.0142044814073</v>
       </c>
       <c r="Z3" t="n">
-        <v>619.3349999999999</v>
+        <v>268188951.6084123</v>
       </c>
       <c r="AA3" t="n">
         <v>4.537211082018327e-07</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>85.55562048662085</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.866x + -7064.024</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.86587200254209</v>
       </c>
       <c r="X4" t="n">
         <v>-7064.023934502686</v>
@@ -3846,7 +3736,7 @@
         <v>473.6879955288285</v>
       </c>
       <c r="Z4" t="n">
-        <v>529.5049999999999</v>
+        <v>390715133.1608049</v>
       </c>
       <c r="AA4" t="n">
         <v>4.025617682073349e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>86.07531142267271</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.576x + -7877.713</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.57596909182956</v>
       </c>
       <c r="X5" t="n">
         <v>-7877.713155714914</v>
@@ -3898,7 +3786,7 @@
         <v>468.1671033032571</v>
       </c>
       <c r="Z5" t="n">
-        <v>472.145</v>
+        <v>193121447.887839</v>
       </c>
       <c r="AA5" t="n">
         <v>3.716303751517951e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.44645856337118</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.103x + -8563.418</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.10289255334038</v>
       </c>
       <c r="X6" t="n">
         <v>-8563.418396649791</v>
@@ -3950,7 +3836,7 @@
         <v>463.1888459470676</v>
       </c>
       <c r="Z6" t="n">
-        <v>424.6659999999999</v>
+        <v>412945724.0501981</v>
       </c>
       <c r="AA6" t="n">
         <v>3.493779008537029e-07</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.65975374096946</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.134x + -8990.945</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.13372312763676</v>
       </c>
       <c r="X7" t="n">
         <v>-8990.945290288122</v>
@@ -4002,7 +3886,7 @@
         <v>458.0781117823967</v>
       </c>
       <c r="Z7" t="n">
-        <v>402.571</v>
+        <v>251336372.6764174</v>
       </c>
       <c r="AA7" t="n">
         <v>3.355757330395731e-07</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.89567991017859</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.439x + -9548.569</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.43872482002768</v>
       </c>
       <c r="X8" t="n">
         <v>-9548.56906772902</v>
@@ -4054,7 +3936,7 @@
         <v>453.1056739293182</v>
       </c>
       <c r="Z8" t="n">
-        <v>372.673</v>
+        <v>248391625.5926813</v>
       </c>
       <c r="AA8" t="n">
         <v>3.227873529410139e-07</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.9898135424009</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.016x + -9704.214</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.01644783826014</v>
       </c>
       <c r="X9" t="n">
         <v>-9704.214409331875</v>
@@ -4106,7 +3986,7 @@
         <v>448.1286515640717</v>
       </c>
       <c r="Z9" t="n">
-        <v>362.136</v>
+        <v>321752148.2150379</v>
       </c>
       <c r="AA9" t="n">
         <v>3.147105274599211e-07</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>87.10116706600029</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.748x + -9930.241</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.74825195082037</v>
       </c>
       <c r="X10" t="n">
         <v>-9930.241038703818</v>
@@ -4158,7 +4036,7 @@
         <v>443.3643763277236</v>
       </c>
       <c r="Z10" t="n">
-        <v>345.299</v>
+        <v>364039937.4832708</v>
       </c>
       <c r="AA10" t="n">
         <v>3.068180290307751e-07</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>87.27482393024709</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 21.009x + -10483.117</t>
-        </is>
+      <c r="W11" t="n">
+        <v>21.00875885158368</v>
       </c>
       <c r="X11" t="n">
         <v>-10483.1173978412</v>
@@ -4210,7 +4086,7 @@
         <v>438.8792344827597</v>
       </c>
       <c r="Z11" t="n">
-        <v>330.157</v>
+        <v>241205774.9745677</v>
       </c>
       <c r="AA11" t="n">
         <v>3.006781957533359e-07</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.57652688229666</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.927x + -6760.276</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.92692322836171</v>
       </c>
       <c r="X2" t="n">
         <v>-6760.275873835084</v>
@@ -4408,7 +4282,7 @@
         <v>450.8678769253131</v>
       </c>
       <c r="Z2" t="n">
-        <v>517.6370000000002</v>
+        <v>123242275.114243</v>
       </c>
       <c r="AA2" t="n">
         <v>3.884791817255893e-07</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>86.57243820920476</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.696x + -8375.073</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.69624606476608</v>
       </c>
       <c r="X3" t="n">
         <v>-8375.07279202027</v>
@@ -4460,7 +4332,7 @@
         <v>439.6563681340648</v>
       </c>
       <c r="Z3" t="n">
-        <v>410.001</v>
+        <v>180977512.9080008</v>
       </c>
       <c r="AA3" t="n">
         <v>3.366011558935878e-07</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>86.99561876236625</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 19.053x + -9418.214</t>
-        </is>
+      <c r="W4" t="n">
+        <v>19.05326003383767</v>
       </c>
       <c r="X4" t="n">
         <v>-9418.213977467049</v>
@@ -4512,7 +4382,7 @@
         <v>395.293628619102</v>
       </c>
       <c r="Z4" t="n">
-        <v>360.9400000000001</v>
+        <v>5395.605148669591</v>
       </c>
       <c r="AA4" t="n">
         <v>8.798345134825952e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>87.26124801782844</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 20.904x + -10235.100</t>
-        </is>
+      <c r="W5" t="n">
+        <v>20.90446143731829</v>
       </c>
       <c r="X5" t="n">
         <v>-10235.1003737776</v>
@@ -4564,7 +4432,7 @@
         <v>431.024296780722</v>
       </c>
       <c r="Z5" t="n">
-        <v>331.812</v>
+        <v>241022262.4156938</v>
       </c>
       <c r="AA5" t="n">
         <v>3.036202999131847e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>87.37059469986423</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.775x + -10519.781</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.77509536669055</v>
       </c>
       <c r="X6" t="n">
         <v>-10519.78062742743</v>
@@ -4616,7 +4482,7 @@
         <v>402.2937102302833</v>
       </c>
       <c r="Z6" t="n">
-        <v>315.943</v>
+        <v>3512.599583949087</v>
       </c>
       <c r="AA6" t="n">
         <v>1.287681571068858e-06</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>87.4355951855562</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.328x + -10653.125</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.32779920786768</v>
       </c>
       <c r="X7" t="n">
         <v>-10653.12477143453</v>
@@ -4668,7 +4532,7 @@
         <v>405.4904995387254</v>
       </c>
       <c r="Z7" t="n">
-        <v>306.8489999999999</v>
+        <v>3480.233216384322</v>
       </c>
       <c r="AA7" t="n">
         <v>2.353391950136328e-06</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>87.46913154353524</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 22.624x + -10653.923</t>
-        </is>
+      <c r="W8" t="n">
+        <v>22.62405618989666</v>
       </c>
       <c r="X8" t="n">
         <v>-10653.92286913183</v>
@@ -4720,7 +4582,7 @@
         <v>402.3831554181585</v>
       </c>
       <c r="Z8" t="n">
-        <v>296.956</v>
+        <v>3451.586194284745</v>
       </c>
       <c r="AA8" t="n">
         <v>2.05675726637929e-06</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>87.55871172853033</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 23.455x + -11004.725</t>
-        </is>
+      <c r="W9" t="n">
+        <v>23.45528086937025</v>
       </c>
       <c r="X9" t="n">
         <v>-11004.72459310727</v>
@@ -4772,7 +4632,7 @@
         <v>403.8965751825108</v>
       </c>
       <c r="Z9" t="n">
-        <v>295.492</v>
+        <v>3427.772219435024</v>
       </c>
       <c r="AA9" t="n">
         <v>1.826980749065107e-06</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>87.62033215672666</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 24.063x + -11176.696</t>
-        </is>
+      <c r="W10" t="n">
+        <v>24.06337125574727</v>
       </c>
       <c r="X10" t="n">
         <v>-11176.69561498338</v>
@@ -4824,7 +4682,7 @@
         <v>394.3707398400769</v>
       </c>
       <c r="Z10" t="n">
-        <v>284.792</v>
+        <v>3400.063772847948</v>
       </c>
       <c r="AA10" t="n">
         <v>2.130406602422708e-06</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>87.62493867185771</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 24.110x + -11078.258</t>
-        </is>
+      <c r="W11" t="n">
+        <v>24.11009667570395</v>
       </c>
       <c r="X11" t="n">
         <v>-11078.25843263301</v>
@@ -4876,7 +4732,7 @@
         <v>392.2629985923898</v>
       </c>
       <c r="Z11" t="n">
-        <v>282.722</v>
+        <v>3373.167806019072</v>
       </c>
       <c r="AA11" t="n">
         <v>2.190957564552214e-06</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>87.7093320023989</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 24.999x + -11416.585</t>
-        </is>
+      <c r="W12" t="n">
+        <v>24.99936681393503</v>
       </c>
       <c r="X12" t="n">
         <v>-11416.58527712284</v>
@@ -4928,7 +4782,7 @@
         <v>389.4832884581104</v>
       </c>
       <c r="Z12" t="n">
-        <v>277.197</v>
+        <v>3345.463254356214</v>
       </c>
       <c r="AA12" t="n">
         <v>9.44109590473631e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>87.73285262931817</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 25.259x + -11422.213</t>
-        </is>
+      <c r="W13" t="n">
+        <v>25.25899907213341</v>
       </c>
       <c r="X13" t="n">
         <v>-11422.21325459859</v>
@@ -4980,7 +4832,7 @@
         <v>387.1864115939476</v>
       </c>
       <c r="Z13" t="n">
-        <v>271.838</v>
+        <v>3315.766509785056</v>
       </c>
       <c r="AA13" t="n">
         <v>2.085072054046103e-06</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>87.81481647224859</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 26.207x + -11779.848</t>
-        </is>
+      <c r="W14" t="n">
+        <v>26.20740826126609</v>
       </c>
       <c r="X14" t="n">
         <v>-11779.8479738181</v>
@@ -5032,7 +4882,7 @@
         <v>391.6978607263177</v>
       </c>
       <c r="Z14" t="n">
-        <v>265.651</v>
+        <v>5379.752486957718</v>
       </c>
       <c r="AA14" t="n">
         <v>1.064923145243585e-06</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>87.82043187161247</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 26.275x + -11687.953</t>
-        </is>
+      <c r="W15" t="n">
+        <v>26.27499398236535</v>
       </c>
       <c r="X15" t="n">
         <v>-11687.95348266325</v>
@@ -5084,7 +4932,7 @@
         <v>387.3264559726508</v>
       </c>
       <c r="Z15" t="n">
-        <v>263.128</v>
+        <v>6582.322267194906</v>
       </c>
       <c r="AA15" t="n">
         <v>3.872510354953958e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>87.69925981326088</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 24.890x + -10906.624</t>
-        </is>
+      <c r="W16" t="n">
+        <v>24.88980752708708</v>
       </c>
       <c r="X16" t="n">
         <v>-10906.62431198059</v>
@@ -5136,7 +4982,7 @@
         <v>395.0548991229824</v>
       </c>
       <c r="Z16" t="n">
-        <v>273.386</v>
+        <v>215610645.3962327</v>
       </c>
       <c r="AA16" t="n">
         <v>2.698851289753131e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>87.72580019033398</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 25.181x + -10929.057</t>
-        </is>
+      <c r="W17" t="n">
+        <v>25.18058735259119</v>
       </c>
       <c r="X17" t="n">
         <v>-10929.05680077098</v>
@@ -5188,7 +5032,7 @@
         <v>391.9623220307058</v>
       </c>
       <c r="Z17" t="n">
-        <v>267.936</v>
+        <v>110429064.5540533</v>
       </c>
       <c r="AA17" t="n">
         <v>2.681525107923475e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>87.81287807470544</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 26.184x + -11299.127</t>
-        </is>
+      <c r="W18" t="n">
+        <v>26.18415866924689</v>
       </c>
       <c r="X18" t="n">
         <v>-11299.12688764321</v>
@@ -5240,7 +5082,7 @@
         <v>388.9329620833877</v>
       </c>
       <c r="Z18" t="n">
-        <v>259.605</v>
+        <v>424417102.6382215</v>
       </c>
       <c r="AA18" t="n">
         <v>2.664634351187337e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>87.8797697509733</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 27.011x + -11597.276</t>
-        </is>
+      <c r="W19" t="n">
+        <v>27.01104000958359</v>
       </c>
       <c r="X19" t="n">
         <v>-11597.27597952438</v>
@@ -5292,7 +5132,7 @@
         <v>385.8920534170926</v>
       </c>
       <c r="Z19" t="n">
-        <v>257.252</v>
+        <v>421248590.2657109</v>
       </c>
       <c r="AA19" t="n">
         <v>2.654126478313937e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>87.88074814245793</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 27.024x + -11485.191</t>
-        </is>
+      <c r="W20" t="n">
+        <v>27.02352154036311</v>
       </c>
       <c r="X20" t="n">
         <v>-11485.19132452939</v>
@@ -5344,7 +5182,7 @@
         <v>382.817670241769</v>
       </c>
       <c r="Z20" t="n">
-        <v>256.595</v>
+        <v>208983998.0971246</v>
       </c>
       <c r="AA20" t="n">
         <v>2.644063102284988e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>87.82758369754721</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 26.362x + -11047.969</t>
-        </is>
+      <c r="W21" t="n">
+        <v>26.36157743039207</v>
       </c>
       <c r="X21" t="n">
         <v>-11047.96890203932</v>
@@ -5396,7 +5232,7 @@
         <v>379.7669731489552</v>
       </c>
       <c r="Z21" t="n">
-        <v>256.1849999999999</v>
+        <v>414165340.4579787</v>
       </c>
       <c r="AA21" t="n">
         <v>2.632497046580194e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>87.9701621601189</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 28.215x + -11809.651</t>
-        </is>
+      <c r="W22" t="n">
+        <v>28.21496662817601</v>
       </c>
       <c r="X22" t="n">
         <v>-11809.65080898267</v>
@@ -5448,7 +5282,7 @@
         <v>376.7423984880032</v>
       </c>
       <c r="Z22" t="n">
-        <v>247.955</v>
+        <v>308630477.7942852</v>
       </c>
       <c r="AA22" t="n">
         <v>2.615821687966625e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>83.45949046664951</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.722x + -5528.900</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.722055810969508</v>
       </c>
       <c r="X2" t="n">
         <v>-5528.900488859498</v>
@@ -5646,7 +5478,7 @@
         <v>510.0230643160938</v>
       </c>
       <c r="Z2" t="n">
-        <v>762.902</v>
+        <v>280240702.0054348</v>
       </c>
       <c r="AA2" t="n">
         <v>5.747730760022037e-07</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.03443553300878</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.510x + -6517.298</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.5097206749733</v>
       </c>
       <c r="X3" t="n">
         <v>-6517.297981851735</v>
@@ -5698,7 +5528,7 @@
         <v>482.4254909750563</v>
       </c>
       <c r="Z3" t="n">
-        <v>578.886</v>
+        <v>805207626.7345194</v>
       </c>
       <c r="AA3" t="n">
         <v>4.462534064680492e-07</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.86524912306481</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.833x + -7611.660</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.83306641960545</v>
       </c>
       <c r="X4" t="n">
         <v>-7611.660186011932</v>
@@ -5750,7 +5578,7 @@
         <v>473.7800385816096</v>
       </c>
       <c r="Z4" t="n">
-        <v>488.2439999999999</v>
+        <v>260510951.643348</v>
       </c>
       <c r="AA4" t="n">
         <v>3.942887961099986e-07</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>86.3631281959031</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.733x + -8509.877</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.7329736383577</v>
       </c>
       <c r="X5" t="n">
         <v>-8509.876928372587</v>
@@ -5802,7 +5628,7 @@
         <v>468.275077592011</v>
       </c>
       <c r="Z5" t="n">
-        <v>430.6420000000001</v>
+        <v>128529960.5918365</v>
       </c>
       <c r="AA5" t="n">
         <v>3.631311019853731e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>86.68943968421829</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.288x + -9225.698</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.28770910974309</v>
       </c>
       <c r="X6" t="n">
         <v>-9225.697987366791</v>
@@ -5854,7 +5678,7 @@
         <v>463.1657707101388</v>
       </c>
       <c r="Z6" t="n">
-        <v>393.077</v>
+        <v>190577286.1824888</v>
       </c>
       <c r="AA6" t="n">
         <v>3.433202917606022e-07</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>86.87646964071794</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.325x + -9608.469</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.32510044780342</v>
       </c>
       <c r="X7" t="n">
         <v>-9608.468929090981</v>
@@ -5906,7 +5728,7 @@
         <v>458.1120111061471</v>
       </c>
       <c r="Z7" t="n">
-        <v>365.943</v>
+        <v>754170482.2608846</v>
       </c>
       <c r="AA7" t="n">
         <v>3.28840568000323e-07</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>87.10560889338865</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 19.779x + -10257.965</t>
-        </is>
+      <c r="W8" t="n">
+        <v>19.77861000535064</v>
       </c>
       <c r="X8" t="n">
         <v>-10257.96468520767</v>
@@ -5958,7 +5778,7 @@
         <v>453.0741271720851</v>
       </c>
       <c r="Z8" t="n">
-        <v>341.428</v>
+        <v>496407696.4325032</v>
       </c>
       <c r="AA8" t="n">
         <v>3.179195488138277e-07</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>87.20011358068641</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 20.447x + -10444.717</t>
-        </is>
+      <c r="W9" t="n">
+        <v>20.44731682148933</v>
       </c>
       <c r="X9" t="n">
         <v>-10444.71707993587</v>
@@ -6010,7 +5828,7 @@
         <v>403.7724355794147</v>
       </c>
       <c r="Z9" t="n">
-        <v>328.872</v>
+        <v>9304.183362649805</v>
       </c>
       <c r="AA9" t="n">
         <v>2.894594238925443e-07</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>87.30416266343487</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 21.238x + -10705.669</t>
-        </is>
+      <c r="W10" t="n">
+        <v>21.23774000284141</v>
       </c>
       <c r="X10" t="n">
         <v>-10705.66882549406</v>
@@ -6062,7 +5878,7 @@
         <v>443.4328412523989</v>
       </c>
       <c r="Z10" t="n">
-        <v>315.638</v>
+        <v>485106620.7304722</v>
       </c>
       <c r="AA10" t="n">
         <v>3.037941546175563e-07</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>87.40591634175149</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 22.072x + -11014.710</t>
-        </is>
+      <c r="W11" t="n">
+        <v>22.07200399026673</v>
       </c>
       <c r="X11" t="n">
         <v>-11014.7101948853</v>
@@ -6114,7 +5928,7 @@
         <v>438.9773628255097</v>
       </c>
       <c r="Z11" t="n">
-        <v>305.871</v>
+        <v>720381305.7444178</v>
       </c>
       <c r="AA11" t="n">
         <v>2.994258849657866e-07</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>85.40007102497242</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.429x + -6545.016</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.42902375371085</v>
       </c>
       <c r="X2" t="n">
         <v>-6545.016377602506</v>
@@ -6312,7 +6124,7 @@
         <v>452.3508453541294</v>
       </c>
       <c r="Z2" t="n">
-        <v>528.6270000000001</v>
+        <v>248183263.2253623</v>
       </c>
       <c r="AA2" t="n">
         <v>4.112824161963975e-07</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>86.51054109016846</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.399x + -8261.792</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.39936863863073</v>
       </c>
       <c r="X3" t="n">
         <v>-8261.791834220494</v>
@@ -6364,7 +6174,7 @@
         <v>441.1915900308161</v>
       </c>
       <c r="Z3" t="n">
-        <v>409.328</v>
+        <v>241859846.0119839</v>
       </c>
       <c r="AA3" t="n">
         <v>3.463548461689567e-07</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>87.00645554276082</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 19.122x + -9490.960</t>
-        </is>
+      <c r="W4" t="n">
+        <v>19.12236015249242</v>
       </c>
       <c r="X4" t="n">
         <v>-9490.960038724663</v>
@@ -6416,7 +6224,7 @@
         <v>436.3548310285325</v>
       </c>
       <c r="Z4" t="n">
-        <v>352.181</v>
+        <v>119278596.0502252</v>
       </c>
       <c r="AA4" t="n">
         <v>3.208848820771064e-07</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>87.22812280110165</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 20.654x + -10121.659</t>
-        </is>
+      <c r="W5" t="n">
+        <v>20.65426019363998</v>
       </c>
       <c r="X5" t="n">
         <v>-10121.65857072952</v>
@@ -6468,7 +6274,7 @@
         <v>432.4205249758801</v>
       </c>
       <c r="Z5" t="n">
-        <v>325.645</v>
+        <v>118581029.3885973</v>
       </c>
       <c r="AA5" t="n">
         <v>3.079512572913859e-07</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>87.2890872318856</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.119x + -10176.591</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.11946159826942</v>
       </c>
       <c r="X6" t="n">
         <v>-10176.59073855654</v>
@@ -6520,7 +6324,7 @@
         <v>408.3964641392536</v>
       </c>
       <c r="Z6" t="n">
-        <v>309.522</v>
+        <v>7101.422942289118</v>
       </c>
       <c r="AA6" t="n">
         <v>3.6379726903005e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>87.50462129892919</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.946x + -11045.048</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.94623584966731</v>
       </c>
       <c r="X7" t="n">
         <v>-11045.04798626547</v>
@@ -6572,7 +6374,7 @@
         <v>401.966931862572</v>
       </c>
       <c r="Z7" t="n">
-        <v>299.2690000000001</v>
+        <v>3492.649307771641</v>
       </c>
       <c r="AA7" t="n">
         <v>6.058865907241843e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>87.52145584907113</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 23.102x + -10977.462</t>
-        </is>
+      <c r="W8" t="n">
+        <v>23.10228585324511</v>
       </c>
       <c r="X8" t="n">
         <v>-10977.46229465216</v>
@@ -6624,7 +6424,7 @@
         <v>398.597674306599</v>
       </c>
       <c r="Z8" t="n">
-        <v>295.419</v>
+        <v>3459.703656614961</v>
       </c>
       <c r="AA8" t="n">
         <v>1.541397465901892e-06</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>87.54544948096554</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 23.328x + -10924.741</t>
-        </is>
+      <c r="W9" t="n">
+        <v>23.32839508007688</v>
       </c>
       <c r="X9" t="n">
         <v>-10924.74103120476</v>
@@ -6676,7 +6474,7 @@
         <v>403.8846045701454</v>
       </c>
       <c r="Z9" t="n">
-        <v>285.576</v>
+        <v>3428.99574492553</v>
       </c>
       <c r="AA9" t="n">
         <v>2.308474421580248e-06</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>87.63493727598764</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 24.212x + -11256.994</t>
-        </is>
+      <c r="W10" t="n">
+        <v>24.21214179417457</v>
       </c>
       <c r="X10" t="n">
         <v>-11256.99445885403</v>
@@ -6728,7 +6524,7 @@
         <v>395.6985124484585</v>
       </c>
       <c r="Z10" t="n">
-        <v>278.53</v>
+        <v>3402.37693829069</v>
       </c>
       <c r="AA10" t="n">
         <v>2.028570739946239e-06</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>87.68112606702171</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 24.695x + -11388.271</t>
-        </is>
+      <c r="W11" t="n">
+        <v>24.69495738355592</v>
       </c>
       <c r="X11" t="n">
         <v>-11388.270789623</v>
@@ -6780,7 +6574,7 @@
         <v>392.3154123634241</v>
       </c>
       <c r="Z11" t="n">
-        <v>275.198</v>
+        <v>3372.865831297919</v>
       </c>
       <c r="AA11" t="n">
         <v>2.186959869851276e-06</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>87.73860685571304</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 25.323x + -11587.931</t>
-        </is>
+      <c r="W12" t="n">
+        <v>25.32333889373832</v>
       </c>
       <c r="X12" t="n">
         <v>-11587.93137669101</v>
@@ -6832,7 +6624,7 @@
         <v>389.145647422873</v>
       </c>
       <c r="Z12" t="n">
-        <v>269.0719999999999</v>
+        <v>3348.019978078831</v>
       </c>
       <c r="AA12" t="n">
         <v>8.896212750669811e-07</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>87.43887800715753</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 22.356x + -9948.767</t>
-        </is>
+      <c r="W13" t="n">
+        <v>22.35645699874262</v>
       </c>
       <c r="X13" t="n">
         <v>-9948.766866542572</v>
@@ -6884,7 +6674,7 @@
         <v>387.430774162167</v>
       </c>
       <c r="Z13" t="n">
-        <v>272.334</v>
+        <v>3322.767583093016</v>
       </c>
       <c r="AA13" t="n">
         <v>2.689040659125571e-06</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>87.61504044963438</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 24.010x + -10693.157</t>
-        </is>
+      <c r="W14" t="n">
+        <v>24.00991834519344</v>
       </c>
       <c r="X14" t="n">
         <v>-10693.15704751849</v>
@@ -6936,7 +6724,7 @@
         <v>385.2630321057063</v>
       </c>
       <c r="Z14" t="n">
-        <v>270.4300000000001</v>
+        <v>3298.72348165928</v>
       </c>
       <c r="AA14" t="n">
         <v>2.092965923134083e-06</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>87.80000684725178</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 26.031x + -11615.392</t>
-        </is>
+      <c r="W15" t="n">
+        <v>26.0308169005995</v>
       </c>
       <c r="X15" t="n">
         <v>-11615.39179086089</v>
@@ -6988,7 +6774,7 @@
         <v>387.811655867922</v>
       </c>
       <c r="Z15" t="n">
-        <v>263.349</v>
+        <v>6597.83021612438</v>
       </c>
       <c r="AA15" t="n">
         <v>3.87374654933605e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>87.81973538823236</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 26.267x + -11609.430</t>
-        </is>
+      <c r="W16" t="n">
+        <v>26.26659235722757</v>
       </c>
       <c r="X16" t="n">
         <v>-11609.43019424543</v>
@@ -7040,7 +6824,7 @@
         <v>396.1033591762223</v>
       </c>
       <c r="Z16" t="n">
-        <v>257.817</v>
+        <v>216015388.1743194</v>
       </c>
       <c r="AA16" t="n">
         <v>2.724884697611362e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>87.80958887751102</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 26.145x + -11429.527</t>
-        </is>
+      <c r="W17" t="n">
+        <v>26.14480137958938</v>
       </c>
       <c r="X17" t="n">
         <v>-11429.52742617746</v>
@@ -7092,7 +6874,7 @@
         <v>393.1878154747255</v>
       </c>
       <c r="Z17" t="n">
-        <v>255.014</v>
+        <v>214757656.8707898</v>
       </c>
       <c r="AA17" t="n">
         <v>2.70843335055864e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>87.62649270100589</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 24.126x + -10346.713</t>
-        </is>
+      <c r="W18" t="n">
+        <v>24.12590060204456</v>
       </c>
       <c r="X18" t="n">
         <v>-10346.71251131366</v>
@@ -7144,7 +6924,7 @@
         <v>390.1497452323471</v>
       </c>
       <c r="Z18" t="n">
-        <v>262.587</v>
+        <v>212996290.450841</v>
       </c>
       <c r="AA18" t="n">
         <v>2.699984214560284e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>87.94026050456966</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 27.805x + -12029.670</t>
-        </is>
+      <c r="W19" t="n">
+        <v>27.80501878660194</v>
       </c>
       <c r="X19" t="n">
         <v>-12029.67002916425</v>
@@ -7196,7 +6974,7 @@
         <v>387.1222911284498</v>
       </c>
       <c r="Z19" t="n">
-        <v>249.416</v>
+        <v>211564676.3490336</v>
       </c>
       <c r="AA19" t="n">
         <v>2.685623821567904e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>87.69417283319656</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 24.835x + -10489.715</t>
-        </is>
+      <c r="W20" t="n">
+        <v>24.83483796277044</v>
       </c>
       <c r="X20" t="n">
         <v>-10489.71513985551</v>
@@ -7248,7 +7024,7 @@
         <v>384.0414995523008</v>
       </c>
       <c r="Z20" t="n">
-        <v>259.9</v>
+        <v>836933480.7986488</v>
       </c>
       <c r="AA20" t="n">
         <v>2.681501399578432e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>87.86886394465913</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 26.873x + -11335.917</t>
-        </is>
+      <c r="W21" t="n">
+        <v>26.87268799886095</v>
       </c>
       <c r="X21" t="n">
         <v>-11335.91746104349</v>
@@ -7300,7 +7074,7 @@
         <v>381.0114202350169</v>
       </c>
       <c r="Z21" t="n">
-        <v>248.335</v>
+        <v>158367121.1464663</v>
       </c>
       <c r="AA21" t="n">
         <v>2.664095332736867e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>87.75691782074087</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 25.530x + -10590.833</t>
-        </is>
+      <c r="W22" t="n">
+        <v>25.53027501616126</v>
       </c>
       <c r="X22" t="n">
         <v>-10590.83304695597</v>
@@ -7352,7 +7124,7 @@
         <v>377.9163953705417</v>
       </c>
       <c r="Z22" t="n">
-        <v>249.9010000000001</v>
+        <v>824009950.5852665</v>
       </c>
       <c r="AA22" t="n">
         <v>2.654781821075532e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>83.53400045001383</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.823x + -5603.650</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.823436581631196</v>
       </c>
       <c r="X2" t="n">
         <v>-5603.649728868509</v>
@@ -7550,7 +7320,7 @@
         <v>510.3035093823291</v>
       </c>
       <c r="Z2" t="n">
-        <v>748.462</v>
+        <v>560170766.6245534</v>
       </c>
       <c r="AA2" t="n">
         <v>5.747546682862158e-07</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.2135347838045</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.943x + -6714.692</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.94251466375319</v>
       </c>
       <c r="X3" t="n">
         <v>-6714.69197562406</v>
@@ -7602,7 +7370,7 @@
         <v>481.2660958168094</v>
       </c>
       <c r="Z3" t="n">
-        <v>557.048</v>
+        <v>49650136.99958347</v>
       </c>
       <c r="AA3" t="n">
         <v>4.350575643664988e-07</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>86.0328088599905</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.419x + -7842.537</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.41931702309659</v>
       </c>
       <c r="X4" t="n">
         <v>-7842.536772160747</v>
@@ -7654,7 +7420,7 @@
         <v>472.8891771331856</v>
       </c>
       <c r="Z4" t="n">
-        <v>462.0590000000001</v>
+        <v>28408239.65208392</v>
       </c>
       <c r="AA4" t="n">
         <v>3.804381518473373e-07</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>86.55257332379307</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.600x + -8893.673</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.59980777479657</v>
       </c>
       <c r="X5" t="n">
         <v>-8893.673459773989</v>
@@ -7706,7 +7470,7 @@
         <v>467.7896614165775</v>
       </c>
       <c r="Z5" t="n">
-        <v>401.734</v>
+        <v>127512352.6531525</v>
       </c>
       <c r="AA5" t="n">
         <v>3.504288151220924e-07</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>86.9861017701369</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.993x + -10116.136</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.99298491695694</v>
       </c>
       <c r="X6" t="n">
         <v>-10116.13588290864</v>
@@ -7758,7 +7520,7 @@
         <v>463.0239290112445</v>
       </c>
       <c r="Z6" t="n">
-        <v>359.6890000000001</v>
+        <v>381339097.4644856</v>
       </c>
       <c r="AA6" t="n">
         <v>3.319013594846779e-07</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>87.15739869539549</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 20.140x + -10551.996</t>
-        </is>
+      <c r="W7" t="n">
+        <v>20.13956791849008</v>
       </c>
       <c r="X7" t="n">
         <v>-10551.99627331281</v>
@@ -7810,7 +7570,7 @@
         <v>458.0798676900543</v>
       </c>
       <c r="Z7" t="n">
-        <v>334.443</v>
+        <v>188651834.3147243</v>
       </c>
       <c r="AA7" t="n">
         <v>3.191725725384624e-07</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>87.27536092498359</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 21.013x + -10865.610</t>
-        </is>
+      <c r="W8" t="n">
+        <v>21.01290568482053</v>
       </c>
       <c r="X8" t="n">
         <v>-10865.60988569405</v>
@@ -7862,7 +7620,7 @@
         <v>453.0595149208056</v>
       </c>
       <c r="Z8" t="n">
-        <v>322.317</v>
+        <v>422324301.2284553</v>
       </c>
       <c r="AA8" t="n">
         <v>3.11056400521917e-07</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>87.46431559652837</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 22.581x + -11525.196</t>
-        </is>
+      <c r="W9" t="n">
+        <v>22.58103102183825</v>
       </c>
       <c r="X9" t="n">
         <v>-11525.19590796948</v>
@@ -7914,7 +7670,7 @@
         <v>448.2523363095118</v>
       </c>
       <c r="Z9" t="n">
-        <v>295.515</v>
+        <v>491171586.2060832</v>
       </c>
       <c r="AA9" t="n">
         <v>3.01938652258721e-07</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>87.50165181635789</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 22.919x + -11537.728</t>
-        </is>
+      <c r="W10" t="n">
+        <v>22.91892791072446</v>
       </c>
       <c r="X10" t="n">
         <v>-11537.7280858147</v>
@@ -7966,7 +7720,7 @@
         <v>443.4853755438477</v>
       </c>
       <c r="Z10" t="n">
-        <v>292.604</v>
+        <v>485784741.1051268</v>
       </c>
       <c r="AA10" t="n">
         <v>2.974394904184702e-07</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>87.57951358152002</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 23.657x + -11766.050</t>
-        </is>
+      <c r="W11" t="n">
+        <v>23.6571005595406</v>
       </c>
       <c r="X11" t="n">
         <v>-11766.05015049437</v>
@@ -8018,7 +7770,7 @@
         <v>438.8706743763116</v>
       </c>
       <c r="Z11" t="n">
-        <v>283.772</v>
+        <v>360109425.4336346</v>
       </c>
       <c r="AA11" t="n">
         <v>2.931007929726052e-07</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.55460818823437</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.863x + -6830.029</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.86293041747631</v>
       </c>
       <c r="X2" t="n">
         <v>-6830.028950954207</v>
@@ -8216,7 +7966,7 @@
         <v>457.4997079118085</v>
       </c>
       <c r="Z2" t="n">
-        <v>512.5859999999999</v>
+        <v>312612632.3179682</v>
       </c>
       <c r="AA2" t="n">
         <v>4.043693871259796e-07</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>86.62761733792514</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.970x + -8632.904</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.97007864582658</v>
       </c>
       <c r="X3" t="n">
         <v>-8632.903832591566</v>
@@ -8268,7 +8016,7 @@
         <v>403.3609078212102</v>
       </c>
       <c r="Z3" t="n">
-        <v>392.625</v>
+        <v>9279.368412308988</v>
       </c>
       <c r="AA3" t="n">
         <v>2.675247436031156e-07</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>87.08333961834244</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 19.627x + -9838.499</t>
-        </is>
+      <c r="W4" t="n">
+        <v>19.62733821795843</v>
       </c>
       <c r="X4" t="n">
         <v>-9838.498825688595</v>
@@ -8320,7 +8066,7 @@
         <v>441.7997160107934</v>
       </c>
       <c r="Z4" t="n">
-        <v>342.393</v>
+        <v>362464404.8865823</v>
       </c>
       <c r="AA4" t="n">
         <v>3.181633620200979e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>87.26957672282155</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 20.968x + -10368.112</t>
-        </is>
+      <c r="W5" t="n">
+        <v>20.96832412855604</v>
       </c>
       <c r="X5" t="n">
         <v>-10368.1116933688</v>
@@ -8372,7 +8116,7 @@
         <v>437.6099678784668</v>
       </c>
       <c r="Z5" t="n">
-        <v>318.89</v>
+        <v>239907240.0106749</v>
       </c>
       <c r="AA5" t="n">
         <v>3.061414370027394e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>87.43468155584721</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 22.320x + -10926.868</t>
-        </is>
+      <c r="W6" t="n">
+        <v>22.31983660425665</v>
       </c>
       <c r="X6" t="n">
         <v>-10926.86794640467</v>
@@ -8424,7 +8166,7 @@
         <v>413.9216791495396</v>
       </c>
       <c r="Z6" t="n">
-        <v>302.451</v>
+        <v>7181.639270335022</v>
       </c>
       <c r="AA6" t="n">
         <v>3.801008221149333e-07</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>87.49497990291154</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.858x + -11031.725</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.85780769787742</v>
       </c>
       <c r="X7" t="n">
         <v>-11031.72547674831</v>
@@ -8476,7 +8216,7 @@
         <v>405.7518897540633</v>
       </c>
       <c r="Z7" t="n">
-        <v>290.348</v>
+        <v>3530.122982021144</v>
       </c>
       <c r="AA7" t="n">
         <v>1.746351472270337e-06</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>87.59416461102664</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 23.801x + -11395.359</t>
-        </is>
+      <c r="W8" t="n">
+        <v>23.80133833854714</v>
       </c>
       <c r="X8" t="n">
         <v>-11395.35855692168</v>
@@ -8528,7 +8266,7 @@
         <v>407.5285837146329</v>
       </c>
       <c r="Z8" t="n">
-        <v>283.67</v>
+        <v>3497.19075329124</v>
       </c>
       <c r="AA8" t="n">
         <v>2.435726347952618e-06</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>87.60864652955547</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 23.946x + -11315.451</t>
-        </is>
+      <c r="W9" t="n">
+        <v>23.94564712269023</v>
       </c>
       <c r="X9" t="n">
         <v>-11315.45057022371</v>
@@ -8580,7 +8316,7 @@
         <v>412.6356352748284</v>
       </c>
       <c r="Z9" t="n">
-        <v>277.1820000000001</v>
+        <v>3466.283946499125</v>
       </c>
       <c r="AA9" t="n">
         <v>5.559443951561254e-07</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>87.6386457399631</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 24.250x + -11341.202</t>
-        </is>
+      <c r="W10" t="n">
+        <v>24.25020971670905</v>
       </c>
       <c r="X10" t="n">
         <v>-11341.20189378039</v>
@@ -8632,7 +8366,7 @@
         <v>398.0667829807337</v>
       </c>
       <c r="Z10" t="n">
-        <v>275.333</v>
+        <v>3436.279317545162</v>
       </c>
       <c r="AA10" t="n">
         <v>2.445688758224025e-06</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>87.67719434439918</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 24.653x + -11416.140</t>
-        </is>
+      <c r="W11" t="n">
+        <v>24.65311147250479</v>
       </c>
       <c r="X11" t="n">
         <v>-11416.13996383517</v>
@@ -8684,7 +8416,7 @@
         <v>397.396766860261</v>
       </c>
       <c r="Z11" t="n">
-        <v>270.114</v>
+        <v>3404.429639909844</v>
       </c>
       <c r="AA11" t="n">
         <v>1.910935847238245e-06</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>87.81009305977385</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 26.151x + -12062.416</t>
-        </is>
+      <c r="W12" t="n">
+        <v>26.15082656531312</v>
       </c>
       <c r="X12" t="n">
         <v>-12062.4157865</v>
@@ -8736,7 +8466,7 @@
         <v>393.4547150869861</v>
       </c>
       <c r="Z12" t="n">
-        <v>260.621</v>
+        <v>3376.897137777153</v>
       </c>
       <c r="AA12" t="n">
         <v>2.316767111265437e-06</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>87.8205424696433</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 26.276x + -11996.189</t>
-        </is>
+      <c r="W13" t="n">
+        <v>26.27632861166523</v>
       </c>
       <c r="X13" t="n">
         <v>-11996.18885363217</v>
@@ -8788,7 +8516,7 @@
         <v>391.0891370872379</v>
       </c>
       <c r="Z13" t="n">
-        <v>258.417</v>
+        <v>3350.051935983317</v>
       </c>
       <c r="AA13" t="n">
         <v>2.047276587104414e-06</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>87.81078071201776</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 26.159x + -11820.668</t>
-        </is>
+      <c r="W14" t="n">
+        <v>26.15904876452573</v>
       </c>
       <c r="X14" t="n">
         <v>-11820.66809178136</v>
@@ -8840,7 +8566,7 @@
         <v>393.6635995248881</v>
       </c>
       <c r="Z14" t="n">
-        <v>258.862</v>
+        <v>6693.224436311711</v>
       </c>
       <c r="AA14" t="n">
         <v>3.734491907564514e-07</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>87.80126866914307</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 26.046x + -11618.539</t>
-        </is>
+      <c r="W15" t="n">
+        <v>26.04577032008059</v>
       </c>
       <c r="X15" t="n">
         <v>-11618.53853203202</v>
@@ -8892,7 +8616,7 @@
         <v>401.7714964571455</v>
       </c>
       <c r="Z15" t="n">
-        <v>253.519</v>
+        <v>110136818.9024218</v>
       </c>
       <c r="AA15" t="n">
         <v>2.738074642512763e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>87.85506756801165</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 26.700x + -11837.104</t>
-        </is>
+      <c r="W16" t="n">
+        <v>26.69968068263704</v>
       </c>
       <c r="X16" t="n">
         <v>-11837.10365352957</v>
@@ -8944,7 +8666,7 @@
         <v>398.604764654611</v>
       </c>
       <c r="Z16" t="n">
-        <v>251.8559999999999</v>
+        <v>217461088.2834669</v>
       </c>
       <c r="AA16" t="n">
         <v>2.724765264228142e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>87.87431166686969</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 26.942x + -11856.623</t>
-        </is>
+      <c r="W17" t="n">
+        <v>26.94162090673175</v>
       </c>
       <c r="X17" t="n">
         <v>-11856.62252356277</v>
@@ -8996,7 +8716,7 @@
         <v>395.4786579321065</v>
       </c>
       <c r="Z17" t="n">
-        <v>252.708</v>
+        <v>218565100.2905012</v>
       </c>
       <c r="AA17" t="n">
         <v>2.717446277148552e-07</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>87.87075907823763</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 26.897x + -11709.909</t>
-        </is>
+      <c r="W18" t="n">
+        <v>26.89662813360137</v>
       </c>
       <c r="X18" t="n">
         <v>-11709.90918424021</v>
@@ -9048,7 +8766,7 @@
         <v>392.3821265747468</v>
       </c>
       <c r="Z18" t="n">
-        <v>250.297</v>
+        <v>320922055.6702399</v>
       </c>
       <c r="AA18" t="n">
         <v>2.706710776409562e-07</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>87.87213590775382</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 26.914x + -11602.875</t>
-        </is>
+      <c r="W19" t="n">
+        <v>26.91404756260455</v>
       </c>
       <c r="X19" t="n">
         <v>-11602.87499830767</v>
@@ -9100,7 +8816,7 @@
         <v>389.2297349092733</v>
       </c>
       <c r="Z19" t="n">
-        <v>250.292</v>
+        <v>424392238.0302437</v>
       </c>
       <c r="AA19" t="n">
         <v>2.695351437307313e-07</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>87.98453019173634</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 28.416x + -12183.948</t>
-        </is>
+      <c r="W20" t="n">
+        <v>28.41627539185486</v>
       </c>
       <c r="X20" t="n">
         <v>-12183.94804322583</v>
@@ -9152,7 +8866,7 @@
         <v>386.1861154748777</v>
       </c>
       <c r="Z20" t="n">
-        <v>238.028</v>
+        <v>423121026.1880721</v>
       </c>
       <c r="AA20" t="n">
         <v>2.674479118209682e-07</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>87.94558538440631</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 27.877x + -11829.639</t>
-        </is>
+      <c r="W21" t="n">
+        <v>27.87714924002999</v>
       </c>
       <c r="X21" t="n">
         <v>-11829.63864477345</v>
@@ -9204,7 +8916,7 @@
         <v>383.0878902717469</v>
       </c>
       <c r="Z21" t="n">
-        <v>242.771</v>
+        <v>1043691509.916825</v>
       </c>
       <c r="AA21" t="n">
         <v>2.6718394981589e-07</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>87.95924052707389</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 28.064x + -11793.208</t>
-        </is>
+      <c r="W22" t="n">
+        <v>28.06384044051653</v>
       </c>
       <c r="X22" t="n">
         <v>-11793.20759591702</v>
@@ -9256,7 +8966,7 @@
         <v>379.979431224596</v>
       </c>
       <c r="Z22" t="n">
-        <v>239.959</v>
+        <v>104725804.1511465</v>
       </c>
       <c r="AA22" t="n">
         <v>2.660548930483863e-07</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>84.30135020506781</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.021x + -6202.506</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.02109749397026</v>
       </c>
       <c r="X2" t="n">
         <v>-6202.506470869546</v>
@@ -9454,7 +9162,7 @@
         <v>496.4300008690061</v>
       </c>
       <c r="Z2" t="n">
-        <v>672.124</v>
+        <v>270503285.953953</v>
       </c>
       <c r="AA2" t="n">
         <v>4.971412741518568e-07</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>86.16611206061488</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.922x + -8055.543</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.9222515967568</v>
       </c>
       <c r="X3" t="n">
         <v>-8055.542724286479</v>
@@ -9506,7 +9212,7 @@
         <v>462.2924872699581</v>
       </c>
       <c r="Z3" t="n">
-        <v>462.144</v>
+        <v>386408749.5787792</v>
       </c>
       <c r="AA3" t="n">
         <v>3.696957143001951e-07</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>86.89790606768399</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 18.452x + -9600.725</t>
-        </is>
+      <c r="W4" t="n">
+        <v>18.45198293498987</v>
       </c>
       <c r="X4" t="n">
         <v>-9600.724840700765</v>
@@ -9558,7 +9262,7 @@
         <v>452.7040384209214</v>
       </c>
       <c r="Z4" t="n">
-        <v>373.249</v>
+        <v>372439264.3355919</v>
       </c>
       <c r="AA4" t="n">
         <v>3.284121272966834e-07</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>87.25868349814803</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 20.885x + -10692.072</t>
-        </is>
+      <c r="W5" t="n">
+        <v>20.88487534099069</v>
       </c>
       <c r="X5" t="n">
         <v>-10692.07200967175</v>
@@ -9610,7 +9312,7 @@
         <v>446.8893871986931</v>
       </c>
       <c r="Z5" t="n">
-        <v>331.0459999999999</v>
+        <v>443629263.2080497</v>
       </c>
       <c r="AA5" t="n">
         <v>3.097473312523191e-07</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>87.46486275737671</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 22.586x + -11363.750</t>
-        </is>
+      <c r="W6" t="n">
+        <v>22.58591107401257</v>
       </c>
       <c r="X6" t="n">
         <v>-11363.75009103374</v>
@@ -9662,7 +9362,7 @@
         <v>441.2957596951944</v>
       </c>
       <c r="Z6" t="n">
-        <v>300.462</v>
+        <v>120762018.9660457</v>
       </c>
       <c r="AA6" t="n">
         <v>2.973416487429197e-07</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>87.62832172715183</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 24.145x + -11997.677</t>
-        </is>
+      <c r="W7" t="n">
+        <v>24.14452766787483</v>
       </c>
       <c r="X7" t="n">
         <v>-11997.67667630151</v>
@@ -9714,7 +9412,7 @@
         <v>399.5036448819612</v>
       </c>
       <c r="Z7" t="n">
-        <v>285.783</v>
+        <v>5394.212979040413</v>
       </c>
       <c r="AA7" t="n">
         <v>9.208391941885388e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>87.5960437431378</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 23.820x + -11557.959</t>
-        </is>
+      <c r="W8" t="n">
+        <v>23.8199653221709</v>
       </c>
       <c r="X8" t="n">
         <v>-11557.95890420135</v>
@@ -9766,7 +9462,7 @@
         <v>429.3846945898102</v>
       </c>
       <c r="Z8" t="n">
-        <v>278.0069999999999</v>
+        <v>469373915.0184879</v>
       </c>
       <c r="AA8" t="n">
         <v>2.853134075543249e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>87.70247041294871</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 24.925x + -11937.196</t>
-        </is>
+      <c r="W9" t="n">
+        <v>24.92462628024174</v>
       </c>
       <c r="X9" t="n">
         <v>-11937.19550199226</v>
@@ -9818,7 +9512,7 @@
         <v>401.5191020089013</v>
       </c>
       <c r="Z9" t="n">
-        <v>268.289</v>
+        <v>3481.605398927772</v>
       </c>
       <c r="AA9" t="n">
         <v>4.721666061233418e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>87.75258186234397</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 25.481x + -12032.781</t>
-        </is>
+      <c r="W10" t="n">
+        <v>25.48096887808072</v>
       </c>
       <c r="X10" t="n">
         <v>-12032.78076299674</v>
@@ -9870,7 +9562,7 @@
         <v>400.259534994683</v>
       </c>
       <c r="Z10" t="n">
-        <v>263.598</v>
+        <v>3438.919964037749</v>
       </c>
       <c r="AA10" t="n">
         <v>1.928901445658376e-06</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>87.81604736855897</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 26.222x + -12231.938</t>
-        </is>
+      <c r="W11" t="n">
+        <v>26.2221933327917</v>
       </c>
       <c r="X11" t="n">
         <v>-12231.93795227585</v>
@@ -9922,7 +9612,7 @@
         <v>393.1229108155648</v>
       </c>
       <c r="Z11" t="n">
-        <v>257.052</v>
+        <v>3401.468041000346</v>
       </c>
       <c r="AA11" t="n">
         <v>1.658440801982039e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-436.0269999999999</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-397.9630000000001</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-366.481</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-353.082</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-344.706</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-323.819</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-326.3699999999999</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-309.6209999999999</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-301.8200000000001</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-302.818</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-810.442</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-619.3349999999999</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-529.5049999999999</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-472.145</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-424.6659999999999</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-402.571</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-372.673</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-362.136</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-345.299</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-330.157</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-762.902</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-578.886</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-488.2439999999999</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-430.6420000000001</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-393.077</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-365.943</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-341.428</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-328.872</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-315.638</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-305.871</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-748.462</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-557.048</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-462.0590000000001</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-401.734</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-359.6890000000001</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-334.443</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-322.317</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-295.515</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-292.604</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-283.772</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-672.124</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-462.144</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-373.249</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-331.0459999999999</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-300.462</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-285.783</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-278.0069999999999</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-268.289</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-263.598</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-257.052</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-436.0269999999999</v>
+        <v>138.501</v>
       </c>
       <c r="D2" t="n">
         <v>1.95684e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-397.9630000000001</v>
+        <v>129.59</v>
       </c>
       <c r="D3" t="n">
         <v>1.93942e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-366.481</v>
+        <v>123.381</v>
       </c>
       <c r="D4" t="n">
         <v>1.93022e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-353.082</v>
+        <v>118.954</v>
       </c>
       <c r="D5" t="n">
         <v>1.92323e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-344.706</v>
+        <v>114.227</v>
       </c>
       <c r="D6" t="n">
         <v>1.91832e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-323.819</v>
+        <v>110.023</v>
       </c>
       <c r="D7" t="n">
         <v>1.91547e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-326.3699999999999</v>
+        <v>103.65</v>
       </c>
       <c r="D8" t="n">
         <v>1.91229e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-309.6209999999999</v>
+        <v>104.213</v>
       </c>
       <c r="D9" t="n">
         <v>1.91113e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-301.8200000000001</v>
+        <v>103.201</v>
       </c>
       <c r="D10" t="n">
         <v>1.90915e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-302.818</v>
+        <v>99.61799999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.90844e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-301.671</v>
+        <v>141.597</v>
       </c>
       <c r="D2" t="n">
         <v>2.01573e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-274.621</v>
+        <v>119.287</v>
       </c>
       <c r="D3" t="n">
         <v>2.01753e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-269.188</v>
+        <v>112.807</v>
       </c>
       <c r="D4" t="n">
         <v>2.01569e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-265.18</v>
+        <v>108.606</v>
       </c>
       <c r="D5" t="n">
         <v>2.01135e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-253.147</v>
+        <v>107.688</v>
       </c>
       <c r="D6" t="n">
         <v>2.00886e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-256.03</v>
+        <v>104.328</v>
       </c>
       <c r="D7" t="n">
         <v>2.00712e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-249.344</v>
+        <v>101.577</v>
       </c>
       <c r="D8" t="n">
         <v>2.00704e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-253.11</v>
+        <v>100.219</v>
       </c>
       <c r="D9" t="n">
         <v>2.00308e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-251.138</v>
+        <v>95.584</v>
       </c>
       <c r="D10" t="n">
         <v>2.00132e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-246.883</v>
+        <v>95.19200000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.00153e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-243.092</v>
+        <v>93.88599999999997</v>
       </c>
       <c r="D12" t="n">
         <v>2.00104e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-244.6220000000001</v>
+        <v>92.255</v>
       </c>
       <c r="D13" t="n">
         <v>2.0007e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-245.7910000000001</v>
+        <v>89.22300000000001</v>
       </c>
       <c r="D14" t="n">
         <v>2.00008e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-239.637</v>
+        <v>87.88100000000003</v>
       </c>
       <c r="D15" t="n">
         <v>1.99847e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-239.664</v>
+        <v>87.47899999999998</v>
       </c>
       <c r="D16" t="n">
         <v>1.99828e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-243.848</v>
+        <v>83.63200000000001</v>
       </c>
       <c r="D17" t="n">
         <v>1.99709e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-237.5960000000001</v>
+        <v>82.82799999999997</v>
       </c>
       <c r="D18" t="n">
         <v>1.99687e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-231.955</v>
+        <v>82.50600000000003</v>
       </c>
       <c r="D19" t="n">
         <v>1.99669e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-231.742</v>
+        <v>81.18900000000002</v>
       </c>
       <c r="D20" t="n">
         <v>1.99708e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-237.4179999999999</v>
+        <v>78.11099999999999</v>
       </c>
       <c r="D21" t="n">
         <v>1.9952e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-233.336</v>
+        <v>77.51800000000003</v>
       </c>
       <c r="D22" t="n">
         <v>1.99644e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-450.226</v>
+        <v>144.443</v>
       </c>
       <c r="D2" t="n">
         <v>2.00357e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-367.91</v>
+        <v>122.482</v>
       </c>
       <c r="D3" t="n">
         <v>1.97585e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-336.725</v>
+        <v>116.396</v>
       </c>
       <c r="D4" t="n">
         <v>1.95816e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-316.309</v>
+        <v>114.402</v>
       </c>
       <c r="D5" t="n">
         <v>1.94808e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-306.176</v>
+        <v>112.248</v>
       </c>
       <c r="D6" t="n">
         <v>1.93611e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-307.239</v>
+        <v>104.444</v>
       </c>
       <c r="D7" t="n">
         <v>1.92993e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-293.404</v>
+        <v>106.312</v>
       </c>
       <c r="D8" t="n">
         <v>1.92702e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-287.354</v>
+        <v>103.194</v>
       </c>
       <c r="D9" t="n">
         <v>1.92354e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-287.978</v>
+        <v>101.917</v>
       </c>
       <c r="D10" t="n">
         <v>1.91975e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-273.841</v>
+        <v>100.543</v>
       </c>
       <c r="D11" t="n">
         <v>1.91844e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-279.389</v>
+        <v>99.43799999999999</v>
       </c>
       <c r="D12" t="n">
         <v>1.91816e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-274.962</v>
+        <v>97.267</v>
       </c>
       <c r="D13" t="n">
         <v>1.91696e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-272.161</v>
+        <v>93.57899999999995</v>
       </c>
       <c r="D14" t="n">
         <v>1.91522e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-274.611</v>
+        <v>92.46599999999995</v>
       </c>
       <c r="D15" t="n">
         <v>1.91392e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-274.359</v>
+        <v>88.57900000000001</v>
       </c>
       <c r="D16" t="n">
         <v>1.91196e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-265.248</v>
+        <v>91.46300000000002</v>
       </c>
       <c r="D17" t="n">
         <v>1.91286e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-263.126</v>
+        <v>88.37800000000004</v>
       </c>
       <c r="D18" t="n">
         <v>1.91463e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-262.763</v>
+        <v>85.84299999999996</v>
       </c>
       <c r="D19" t="n">
         <v>1.91275e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-264.878</v>
+        <v>84.73099999999999</v>
       </c>
       <c r="D20" t="n">
         <v>1.91232e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-261.5310000000001</v>
+        <v>85.08499999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.91346e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-257.716</v>
+        <v>82.61000000000001</v>
       </c>
       <c r="D22" t="n">
         <v>1.91362e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-810.442</v>
+        <v>230.682</v>
       </c>
       <c r="D2" t="n">
         <v>2.15998e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-619.3349999999999</v>
+        <v>164.109</v>
       </c>
       <c r="D3" t="n">
         <v>2.20096e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-529.5049999999999</v>
+        <v>149.1220000000001</v>
       </c>
       <c r="D4" t="n">
         <v>2.17127e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-472.145</v>
+        <v>142.2090000000001</v>
       </c>
       <c r="D5" t="n">
         <v>2.13877e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-424.6659999999999</v>
+        <v>136.679</v>
       </c>
       <c r="D6" t="n">
         <v>2.1135e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-402.571</v>
+        <v>131.244</v>
       </c>
       <c r="D7" t="n">
         <v>2.09211e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-372.673</v>
+        <v>127.628</v>
       </c>
       <c r="D8" t="n">
         <v>2.07505e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-362.136</v>
+        <v>123.512</v>
       </c>
       <c r="D9" t="n">
         <v>2.06022e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-345.299</v>
+        <v>117.948</v>
       </c>
       <c r="D10" t="n">
         <v>2.04932e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-330.157</v>
+        <v>117.15</v>
       </c>
       <c r="D11" t="n">
         <v>2.03996e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-517.6370000000002</v>
+        <v>136.706</v>
       </c>
       <c r="D2" t="n">
         <v>2.17316e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-410.001</v>
+        <v>119.534</v>
       </c>
       <c r="D3" t="n">
         <v>2.11682e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-360.9400000000001</v>
+        <v>114.835</v>
       </c>
       <c r="D4" t="n">
         <v>2.08477e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-331.812</v>
+        <v>111.529</v>
       </c>
       <c r="D5" t="n">
         <v>2.06316e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-315.943</v>
+        <v>107.625</v>
       </c>
       <c r="D6" t="n">
         <v>2.04785e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-306.8489999999999</v>
+        <v>103.759</v>
       </c>
       <c r="D7" t="n">
         <v>2.03659e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-296.956</v>
+        <v>99.08500000000004</v>
       </c>
       <c r="D8" t="n">
         <v>2.03039e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-295.492</v>
+        <v>100.075</v>
       </c>
       <c r="D9" t="n">
         <v>2.02408e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-284.792</v>
+        <v>97.40600000000001</v>
       </c>
       <c r="D10" t="n">
         <v>2.01857e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-282.722</v>
+        <v>94.82400000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.01567e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-277.197</v>
+        <v>94.07499999999999</v>
       </c>
       <c r="D12" t="n">
         <v>2.01191e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-271.838</v>
+        <v>92.39700000000005</v>
       </c>
       <c r="D13" t="n">
         <v>2.00889e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-265.651</v>
+        <v>91.89999999999998</v>
       </c>
       <c r="D14" t="n">
         <v>2.00738e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-263.128</v>
+        <v>89.77200000000005</v>
       </c>
       <c r="D15" t="n">
         <v>2.00478e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-273.386</v>
+        <v>85.26999999999998</v>
       </c>
       <c r="D16" t="n">
         <v>2.0028e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-267.936</v>
+        <v>83.24000000000001</v>
       </c>
       <c r="D17" t="n">
         <v>2.0016e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-259.605</v>
+        <v>83.59900000000005</v>
       </c>
       <c r="D18" t="n">
         <v>2.00064e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-257.252</v>
+        <v>83.59100000000001</v>
       </c>
       <c r="D19" t="n">
         <v>1.99927e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-256.595</v>
+        <v>81.74299999999999</v>
       </c>
       <c r="D20" t="n">
         <v>1.99843e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-256.1849999999999</v>
+        <v>78.03699999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.99763e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-247.955</v>
+        <v>80.00599999999997</v>
       </c>
       <c r="D22" t="n">
         <v>1.99554e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-762.902</v>
+        <v>220.98</v>
       </c>
       <c r="D2" t="n">
         <v>2.21037e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-578.886</v>
+        <v>163.473</v>
       </c>
       <c r="D3" t="n">
         <v>2.21752e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-488.2439999999999</v>
+        <v>149.741</v>
       </c>
       <c r="D4" t="n">
         <v>2.17976e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-430.6420000000001</v>
+        <v>142.8869999999999</v>
       </c>
       <c r="D5" t="n">
         <v>2.14361e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-393.077</v>
+        <v>138.543</v>
       </c>
       <c r="D6" t="n">
         <v>2.11582e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-365.943</v>
+        <v>131.31</v>
       </c>
       <c r="D7" t="n">
         <v>2.09581e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-341.428</v>
+        <v>129.036</v>
       </c>
       <c r="D8" t="n">
         <v>2.08005e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-328.872</v>
+        <v>123.597</v>
       </c>
       <c r="D9" t="n">
         <v>2.06787e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-315.638</v>
+        <v>119.544</v>
       </c>
       <c r="D10" t="n">
         <v>2.05925e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-305.871</v>
+        <v>117.968</v>
       </c>
       <c r="D11" t="n">
         <v>2.05354e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-528.6270000000001</v>
+        <v>140.104</v>
       </c>
       <c r="D2" t="n">
         <v>2.2279e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-409.328</v>
+        <v>120.864</v>
       </c>
       <c r="D3" t="n">
         <v>2.1518e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-352.181</v>
+        <v>116.357</v>
       </c>
       <c r="D4" t="n">
         <v>2.11094e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-325.645</v>
+        <v>111.87</v>
       </c>
       <c r="D5" t="n">
         <v>2.08667e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-309.522</v>
+        <v>105.504</v>
       </c>
       <c r="D6" t="n">
         <v>2.07064e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-299.2690000000001</v>
+        <v>107.727</v>
       </c>
       <c r="D7" t="n">
         <v>2.0586e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-295.419</v>
+        <v>103.9040000000001</v>
       </c>
       <c r="D8" t="n">
         <v>2.05e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-285.576</v>
+        <v>99.25</v>
       </c>
       <c r="D9" t="n">
         <v>2.04506e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-278.53</v>
+        <v>98.56200000000001</v>
       </c>
       <c r="D10" t="n">
         <v>2.03863e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-275.198</v>
+        <v>96.94099999999997</v>
       </c>
       <c r="D11" t="n">
         <v>2.03384e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-269.0719999999999</v>
+        <v>95.81400000000002</v>
       </c>
       <c r="D12" t="n">
         <v>2.03217e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-272.334</v>
+        <v>84.37900000000002</v>
       </c>
       <c r="D13" t="n">
         <v>2.02792e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-270.4300000000001</v>
+        <v>87.34799999999996</v>
       </c>
       <c r="D14" t="n">
         <v>2.02749e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-263.349</v>
+        <v>90.81100000000004</v>
       </c>
       <c r="D15" t="n">
         <v>2.02581e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-257.817</v>
+        <v>89.00400000000002</v>
       </c>
       <c r="D16" t="n">
         <v>2.02478e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-255.014</v>
+        <v>86.20400000000001</v>
       </c>
       <c r="D17" t="n">
         <v>2.02314e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-262.587</v>
+        <v>79.41500000000002</v>
       </c>
       <c r="D18" t="n">
         <v>2.02081e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-249.416</v>
+        <v>86.541</v>
       </c>
       <c r="D19" t="n">
         <v>2.02006e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-259.9</v>
+        <v>77.87</v>
       </c>
       <c r="D20" t="n">
         <v>2.01904e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-248.335</v>
+        <v>80.19100000000003</v>
       </c>
       <c r="D21" t="n">
         <v>2.01896e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-249.9010000000001</v>
+        <v>75.30499999999995</v>
       </c>
       <c r="D22" t="n">
         <v>2.01866e-07</v>
@@ -7115,7 +7115,7 @@
         <v>87.75691782074087</v>
       </c>
       <c r="W22" t="n">
-        <v>25.53027501616126</v>
+        <v>25.53027501616125</v>
       </c>
       <c r="X22" t="n">
         <v>-10590.83304695597</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-748.462</v>
+        <v>221.4800000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.22512e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-557.048</v>
+        <v>159.005</v>
       </c>
       <c r="D3" t="n">
         <v>2.22012e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-462.0590000000001</v>
+        <v>142.913</v>
       </c>
       <c r="D4" t="n">
         <v>2.17361e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-401.734</v>
+        <v>136.63</v>
       </c>
       <c r="D5" t="n">
         <v>2.13532e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-359.6890000000001</v>
+        <v>135.7259999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2.10868e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-334.443</v>
+        <v>129.151</v>
       </c>
       <c r="D7" t="n">
         <v>2.09044e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-322.317</v>
+        <v>126.192</v>
       </c>
       <c r="D8" t="n">
         <v>2.07551e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-295.515</v>
+        <v>121.662</v>
       </c>
       <c r="D9" t="n">
         <v>2.06564e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-292.604</v>
+        <v>117.721</v>
       </c>
       <c r="D10" t="n">
         <v>2.05665e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-283.772</v>
+        <v>114.834</v>
       </c>
       <c r="D11" t="n">
         <v>2.05115e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-512.5859999999999</v>
+        <v>139.05</v>
       </c>
       <c r="D2" t="n">
         <v>2.22285e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-392.625</v>
+        <v>120.947</v>
       </c>
       <c r="D3" t="n">
         <v>2.1491e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-342.393</v>
+        <v>115.583</v>
       </c>
       <c r="D4" t="n">
         <v>2.10827e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-318.89</v>
+        <v>111.215</v>
       </c>
       <c r="D5" t="n">
         <v>2.08546e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-302.451</v>
+        <v>108.997</v>
       </c>
       <c r="D6" t="n">
         <v>2.07034e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-290.348</v>
+        <v>104.198</v>
       </c>
       <c r="D7" t="n">
         <v>2.06051e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-283.67</v>
+        <v>102.777</v>
       </c>
       <c r="D8" t="n">
         <v>2.05404e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-277.1820000000001</v>
+        <v>99.59099999999995</v>
       </c>
       <c r="D9" t="n">
         <v>2.04961e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-275.333</v>
+        <v>97.113</v>
       </c>
       <c r="D10" t="n">
         <v>2.0466e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-270.114</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.04342e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-260.621</v>
+        <v>95.286</v>
       </c>
       <c r="D12" t="n">
         <v>2.03987e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-258.417</v>
+        <v>92.65300000000002</v>
       </c>
       <c r="D13" t="n">
         <v>2.04002e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-258.862</v>
+        <v>90.47900000000004</v>
       </c>
       <c r="D14" t="n">
         <v>2.03873e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-253.519</v>
+        <v>87.19799999999998</v>
       </c>
       <c r="D15" t="n">
         <v>2.03755e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-251.8559999999999</v>
+        <v>86.45800000000003</v>
       </c>
       <c r="D16" t="n">
         <v>2.03504e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-252.708</v>
+        <v>86.70999999999998</v>
       </c>
       <c r="D17" t="n">
         <v>2.03351e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-250.297</v>
+        <v>83.69299999999998</v>
       </c>
       <c r="D18" t="n">
         <v>2.03396e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-250.292</v>
+        <v>81.37099999999998</v>
       </c>
       <c r="D19" t="n">
         <v>2.03227e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-238.028</v>
+        <v>81.685</v>
       </c>
       <c r="D20" t="n">
         <v>2.03251e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-242.771</v>
+        <v>80.19</v>
       </c>
       <c r="D21" t="n">
         <v>2.03131e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-239.959</v>
+        <v>78.18800000000005</v>
       </c>
       <c r="D22" t="n">
         <v>2.03144e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-672.124</v>
+        <v>214.316</v>
       </c>
       <c r="D2" t="n">
         <v>2.17122e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-462.144</v>
+        <v>148.211</v>
       </c>
       <c r="D3" t="n">
         <v>2.13894e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-373.249</v>
+        <v>132.58</v>
       </c>
       <c r="D4" t="n">
         <v>2.0923e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-331.0459999999999</v>
+        <v>127.028</v>
       </c>
       <c r="D5" t="n">
         <v>2.06293e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-300.462</v>
+        <v>121.155</v>
       </c>
       <c r="D6" t="n">
         <v>2.04438e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-285.783</v>
+        <v>119.134</v>
       </c>
       <c r="D7" t="n">
         <v>2.03261e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-278.0069999999999</v>
+        <v>111.013</v>
       </c>
       <c r="D8" t="n">
         <v>2.026e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-268.289</v>
+        <v>108.872</v>
       </c>
       <c r="D9" t="n">
         <v>2.02286e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-263.598</v>
+        <v>104.855</v>
       </c>
       <c r="D10" t="n">
         <v>2.01866e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-257.052</v>
+        <v>102.53</v>
       </c>
       <c r="D11" t="n">
         <v>2.01751e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>138.501</v>
       </c>
+      <c r="C2" t="n">
+        <v>966.7349646646384</v>
+      </c>
       <c r="D2" t="n">
         <v>1.95684e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>129.59</v>
       </c>
+      <c r="C3" t="n">
+        <v>908.873917928286</v>
+      </c>
       <c r="D3" t="n">
         <v>1.93942e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>123.381</v>
       </c>
+      <c r="C4" t="n">
+        <v>923.6094680434049</v>
+      </c>
       <c r="D4" t="n">
         <v>1.93022e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>118.954</v>
       </c>
+      <c r="C5" t="n">
+        <v>985.1002062585757</v>
+      </c>
       <c r="D5" t="n">
         <v>1.92323e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>114.227</v>
       </c>
+      <c r="C6" t="n">
+        <v>1007.698689013435</v>
+      </c>
       <c r="D6" t="n">
         <v>1.91832e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>110.023</v>
       </c>
+      <c r="C7" t="n">
+        <v>990.6259045432533</v>
+      </c>
       <c r="D7" t="n">
         <v>1.91547e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>103.65</v>
       </c>
+      <c r="C8" t="n">
+        <v>852.5885015717703</v>
+      </c>
       <c r="D8" t="n">
         <v>1.91229e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>104.213</v>
       </c>
+      <c r="C9" t="n">
+        <v>987.9821862077644</v>
+      </c>
       <c r="D9" t="n">
         <v>1.91113e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>103.201</v>
       </c>
+      <c r="C10" t="n">
+        <v>1079.992084624996</v>
+      </c>
       <c r="D10" t="n">
         <v>1.90915e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>99.61799999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1016.052454862345</v>
       </c>
       <c r="D11" t="n">
         <v>1.90844e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>141.597</v>
       </c>
+      <c r="C2" t="n">
+        <v>1403.702084050206</v>
+      </c>
       <c r="D2" t="n">
         <v>2.01573e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>119.287</v>
       </c>
+      <c r="C3" t="n">
+        <v>906.9684210794503</v>
+      </c>
       <c r="D3" t="n">
         <v>2.01753e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>112.807</v>
       </c>
+      <c r="C4" t="n">
+        <v>918.0841593150506</v>
+      </c>
       <c r="D4" t="n">
         <v>2.01569e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>108.606</v>
       </c>
+      <c r="C5" t="n">
+        <v>871.306455621668</v>
+      </c>
       <c r="D5" t="n">
         <v>2.01135e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>107.688</v>
       </c>
+      <c r="C6" t="n">
+        <v>957.5271999468957</v>
+      </c>
       <c r="D6" t="n">
         <v>2.00886e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>104.328</v>
       </c>
+      <c r="C7" t="n">
+        <v>923.3383443510066</v>
+      </c>
       <c r="D7" t="n">
         <v>2.00712e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>101.577</v>
       </c>
+      <c r="C8" t="n">
+        <v>957.394322389359</v>
+      </c>
       <c r="D8" t="n">
         <v>2.00704e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>100.219</v>
       </c>
+      <c r="C9" t="n">
+        <v>994.39927794036</v>
+      </c>
       <c r="D9" t="n">
         <v>2.00308e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>95.584</v>
       </c>
+      <c r="C10" t="n">
+        <v>904.893478330109</v>
+      </c>
       <c r="D10" t="n">
         <v>2.00132e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>95.19200000000001</v>
       </c>
+      <c r="C11" t="n">
+        <v>965.0119477402844</v>
+      </c>
       <c r="D11" t="n">
         <v>2.00153e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>93.88599999999997</v>
       </c>
+      <c r="C12" t="n">
+        <v>1053.368548941682</v>
+      </c>
       <c r="D12" t="n">
         <v>2.00104e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>92.255</v>
       </c>
+      <c r="C13" t="n">
+        <v>987.0776317389048</v>
+      </c>
       <c r="D13" t="n">
         <v>2.0007e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>89.22300000000001</v>
       </c>
+      <c r="C14" t="n">
+        <v>943.9417919169543</v>
+      </c>
       <c r="D14" t="n">
         <v>2.00008e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>87.88100000000003</v>
       </c>
+      <c r="C15" t="n">
+        <v>977.8057462004066</v>
+      </c>
       <c r="D15" t="n">
         <v>1.99847e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>87.47899999999998</v>
       </c>
+      <c r="C16" t="n">
+        <v>1055.713465070319</v>
+      </c>
       <c r="D16" t="n">
         <v>1.99828e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>83.63200000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>925.4453826221197</v>
+      </c>
       <c r="D17" t="n">
         <v>1.99709e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>82.82799999999997</v>
       </c>
+      <c r="C18" t="n">
+        <v>973.3296052282029</v>
+      </c>
       <c r="D18" t="n">
         <v>1.99687e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>82.50600000000003</v>
       </c>
+      <c r="C19" t="n">
+        <v>1044.965415462835</v>
+      </c>
       <c r="D19" t="n">
         <v>1.99669e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>81.18900000000002</v>
       </c>
+      <c r="C20" t="n">
+        <v>1061.981477181439</v>
+      </c>
       <c r="D20" t="n">
         <v>1.99708e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>78.11099999999999</v>
       </c>
+      <c r="C21" t="n">
+        <v>934.8373786576835</v>
+      </c>
       <c r="D21" t="n">
         <v>1.9952e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>77.51800000000003</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1022.130042372366</v>
       </c>
       <c r="D22" t="n">
         <v>1.99644e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>144.443</v>
       </c>
+      <c r="C2" t="n">
+        <v>1523.140629019508</v>
+      </c>
       <c r="D2" t="n">
         <v>2.00357e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>122.482</v>
       </c>
+      <c r="C3" t="n">
+        <v>962.8337508199561</v>
+      </c>
       <c r="D3" t="n">
         <v>1.97585e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>116.396</v>
       </c>
+      <c r="C4" t="n">
+        <v>889.1978480225758</v>
+      </c>
       <c r="D4" t="n">
         <v>1.95816e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>114.402</v>
       </c>
+      <c r="C5" t="n">
+        <v>965.0040557511979</v>
+      </c>
       <c r="D5" t="n">
         <v>1.94808e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>112.248</v>
       </c>
+      <c r="C6" t="n">
+        <v>968.9116453602002</v>
+      </c>
       <c r="D6" t="n">
         <v>1.93611e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>104.444</v>
       </c>
+      <c r="C7" t="n">
+        <v>827.8846907544163</v>
+      </c>
       <c r="D7" t="n">
         <v>1.92993e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>106.312</v>
       </c>
+      <c r="C8" t="n">
+        <v>943.8484478722378</v>
+      </c>
       <c r="D8" t="n">
         <v>1.92702e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>103.194</v>
       </c>
+      <c r="C9" t="n">
+        <v>933.0623163200513</v>
+      </c>
       <c r="D9" t="n">
         <v>1.92354e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>101.917</v>
       </c>
+      <c r="C10" t="n">
+        <v>974.5262067881015</v>
+      </c>
       <c r="D10" t="n">
         <v>1.91975e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>100.543</v>
       </c>
+      <c r="C11" t="n">
+        <v>982.8799636306808</v>
+      </c>
       <c r="D11" t="n">
         <v>1.91844e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>99.43799999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>1008.073351985019</v>
+      </c>
       <c r="D12" t="n">
         <v>1.91816e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>97.267</v>
       </c>
+      <c r="C13" t="n">
+        <v>989.6636415229151</v>
+      </c>
       <c r="D13" t="n">
         <v>1.91696e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>93.57899999999995</v>
       </c>
+      <c r="C14" t="n">
+        <v>917.050035084088</v>
+      </c>
       <c r="D14" t="n">
         <v>1.91522e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>92.46599999999995</v>
       </c>
+      <c r="C15" t="n">
+        <v>915.1229033648135</v>
+      </c>
       <c r="D15" t="n">
         <v>1.91392e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>88.57900000000001</v>
       </c>
+      <c r="C16" t="n">
+        <v>857.667000833806</v>
+      </c>
       <c r="D16" t="n">
         <v>1.91196e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>91.46300000000002</v>
       </c>
+      <c r="C17" t="n">
+        <v>1002.993553995279</v>
+      </c>
       <c r="D17" t="n">
         <v>1.91286e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>88.37800000000004</v>
       </c>
+      <c r="C18" t="n">
+        <v>973.412526539846</v>
+      </c>
       <c r="D18" t="n">
         <v>1.91463e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>85.84299999999996</v>
       </c>
+      <c r="C19" t="n">
+        <v>898.7146910221624</v>
+      </c>
       <c r="D19" t="n">
         <v>1.91275e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>84.73099999999999</v>
       </c>
+      <c r="C20" t="n">
+        <v>902.171545790713</v>
+      </c>
       <c r="D20" t="n">
         <v>1.91232e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>85.08499999999998</v>
       </c>
+      <c r="C21" t="n">
+        <v>1036.441531195201</v>
+      </c>
       <c r="D21" t="n">
         <v>1.91346e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>82.61000000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>979.1045299897343</v>
       </c>
       <c r="D22" t="n">
         <v>1.91362e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>230.682</v>
       </c>
+      <c r="C2" t="n">
+        <v>2255.069829421123</v>
+      </c>
       <c r="D2" t="n">
         <v>2.15998e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>164.109</v>
       </c>
+      <c r="C3" t="n">
+        <v>1020.280386468572</v>
+      </c>
       <c r="D3" t="n">
         <v>2.20096e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>149.1220000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>912.2721961556513</v>
+      </c>
       <c r="D4" t="n">
         <v>2.17127e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>142.2090000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>904.5847994891204</v>
+      </c>
       <c r="D5" t="n">
         <v>2.13877e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>136.679</v>
       </c>
+      <c r="C6" t="n">
+        <v>874.1852419063313</v>
+      </c>
       <c r="D6" t="n">
         <v>2.1135e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>131.244</v>
       </c>
+      <c r="C7" t="n">
+        <v>878.295980157101</v>
+      </c>
       <c r="D7" t="n">
         <v>2.09211e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>127.628</v>
       </c>
+      <c r="C8" t="n">
+        <v>879.8765319173681</v>
+      </c>
       <c r="D8" t="n">
         <v>2.07505e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>123.512</v>
       </c>
+      <c r="C9" t="n">
+        <v>901.098218785148</v>
+      </c>
       <c r="D9" t="n">
         <v>2.06022e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>117.948</v>
       </c>
+      <c r="C10" t="n">
+        <v>847.0306868210185</v>
+      </c>
       <c r="D10" t="n">
         <v>2.04932e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>117.15</v>
+      </c>
+      <c r="C11" t="n">
+        <v>885.0039045711052</v>
       </c>
       <c r="D11" t="n">
         <v>2.03996e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>136.706</v>
       </c>
+      <c r="C2" t="n">
+        <v>1320.691826857443</v>
+      </c>
       <c r="D2" t="n">
         <v>2.17316e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>119.534</v>
       </c>
+      <c r="C3" t="n">
+        <v>1000.069379908184</v>
+      </c>
       <c r="D3" t="n">
         <v>2.11682e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>114.835</v>
       </c>
+      <c r="C4" t="n">
+        <v>975.8467179586069</v>
+      </c>
       <c r="D4" t="n">
         <v>2.08477e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>111.529</v>
       </c>
+      <c r="C5" t="n">
+        <v>1028.845286873228</v>
+      </c>
       <c r="D5" t="n">
         <v>2.06316e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>107.625</v>
       </c>
+      <c r="C6" t="n">
+        <v>979.8606459270776</v>
+      </c>
       <c r="D6" t="n">
         <v>2.04785e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>103.759</v>
       </c>
+      <c r="C7" t="n">
+        <v>927.1184177431016</v>
+      </c>
       <c r="D7" t="n">
         <v>2.03659e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>99.08500000000004</v>
       </c>
+      <c r="C8" t="n">
+        <v>873.5877452197328</v>
+      </c>
       <c r="D8" t="n">
         <v>2.03039e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>100.075</v>
       </c>
+      <c r="C9" t="n">
+        <v>984.3312479759579</v>
+      </c>
       <c r="D9" t="n">
         <v>2.02408e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>97.40600000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>988.1383306659585</v>
+      </c>
       <c r="D10" t="n">
         <v>2.01857e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>94.82400000000001</v>
       </c>
+      <c r="C11" t="n">
+        <v>934.6908420437614</v>
+      </c>
       <c r="D11" t="n">
         <v>2.01567e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>94.07499999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>952.4440738697936</v>
+      </c>
       <c r="D12" t="n">
         <v>2.01191e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>92.39700000000005</v>
       </c>
+      <c r="C13" t="n">
+        <v>959.3848490096508</v>
+      </c>
       <c r="D13" t="n">
         <v>2.00889e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>91.89999999999998</v>
       </c>
+      <c r="C14" t="n">
+        <v>1050.039145330683</v>
+      </c>
       <c r="D14" t="n">
         <v>2.00738e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>89.77200000000005</v>
       </c>
+      <c r="C15" t="n">
+        <v>1057.954116782328</v>
+      </c>
       <c r="D15" t="n">
         <v>2.00478e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>85.26999999999998</v>
       </c>
+      <c r="C16" t="n">
+        <v>861.8782044916696</v>
+      </c>
       <c r="D16" t="n">
         <v>2.0028e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>83.24000000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>834.2765177376612</v>
+      </c>
       <c r="D17" t="n">
         <v>2.0016e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>83.59900000000005</v>
       </c>
+      <c r="C18" t="n">
+        <v>951.1955742840935</v>
+      </c>
       <c r="D18" t="n">
         <v>2.00064e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>83.59100000000001</v>
       </c>
+      <c r="C19" t="n">
+        <v>1010.553686140195</v>
+      </c>
       <c r="D19" t="n">
         <v>1.99927e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>81.74299999999999</v>
       </c>
+      <c r="C20" t="n">
+        <v>941.8557749250386</v>
+      </c>
       <c r="D20" t="n">
         <v>1.99843e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>78.03699999999998</v>
       </c>
+      <c r="C21" t="n">
+        <v>853.5642724996794</v>
+      </c>
       <c r="D21" t="n">
         <v>1.99763e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>80.00599999999997</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1029.120076841184</v>
       </c>
       <c r="D22" t="n">
         <v>1.99554e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>220.98</v>
       </c>
+      <c r="C2" t="n">
+        <v>1904.433037625111</v>
+      </c>
       <c r="D2" t="n">
         <v>2.21037e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>163.473</v>
       </c>
+      <c r="C3" t="n">
+        <v>996.9913703961288</v>
+      </c>
       <c r="D3" t="n">
         <v>2.21752e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>149.741</v>
       </c>
+      <c r="C4" t="n">
+        <v>890.0957705495215</v>
+      </c>
       <c r="D4" t="n">
         <v>2.17976e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>142.8869999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>882.8140134526209</v>
+      </c>
       <c r="D5" t="n">
         <v>2.14361e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>138.543</v>
       </c>
+      <c r="C6" t="n">
+        <v>891.300559869536</v>
+      </c>
       <c r="D6" t="n">
         <v>2.11582e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>131.31</v>
       </c>
+      <c r="C7" t="n">
+        <v>857.871850474132</v>
+      </c>
       <c r="D7" t="n">
         <v>2.09581e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>129.036</v>
       </c>
+      <c r="C8" t="n">
+        <v>888.3021999675426</v>
+      </c>
       <c r="D8" t="n">
         <v>2.08005e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>123.597</v>
       </c>
+      <c r="C9" t="n">
+        <v>860.9940512848052</v>
+      </c>
       <c r="D9" t="n">
         <v>2.06787e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>119.544</v>
       </c>
+      <c r="C10" t="n">
+        <v>883.8309674063028</v>
+      </c>
       <c r="D10" t="n">
         <v>2.05925e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>117.968</v>
+      </c>
+      <c r="C11" t="n">
+        <v>910.5921661669329</v>
       </c>
       <c r="D11" t="n">
         <v>2.05354e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>140.104</v>
       </c>
+      <c r="C2" t="n">
+        <v>1311.711187679607</v>
+      </c>
       <c r="D2" t="n">
         <v>2.2279e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>120.864</v>
       </c>
+      <c r="C3" t="n">
+        <v>970.8721880929106</v>
+      </c>
       <c r="D3" t="n">
         <v>2.1518e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>116.357</v>
       </c>
+      <c r="C4" t="n">
+        <v>944.4752410796528</v>
+      </c>
       <c r="D4" t="n">
         <v>2.11094e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>111.87</v>
       </c>
+      <c r="C5" t="n">
+        <v>917.7758371606658</v>
+      </c>
       <c r="D5" t="n">
         <v>2.08667e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>105.504</v>
       </c>
+      <c r="C6" t="n">
+        <v>840.1363983239171</v>
+      </c>
       <c r="D6" t="n">
         <v>2.07064e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>107.727</v>
       </c>
+      <c r="C7" t="n">
+        <v>1026.424484293624</v>
+      </c>
       <c r="D7" t="n">
         <v>2.0586e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>103.9040000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>971.3384242135835</v>
+      </c>
       <c r="D8" t="n">
         <v>2.05e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>99.25</v>
       </c>
+      <c r="C9" t="n">
+        <v>889.4243373065341</v>
+      </c>
       <c r="D9" t="n">
         <v>2.04506e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>98.56200000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>946.2450047847452</v>
+      </c>
       <c r="D10" t="n">
         <v>2.03863e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>96.94099999999997</v>
       </c>
+      <c r="C11" t="n">
+        <v>977.3162770788132</v>
+      </c>
       <c r="D11" t="n">
         <v>2.03384e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>95.81400000000002</v>
       </c>
+      <c r="C12" t="n">
+        <v>988.1727181371408</v>
+      </c>
       <c r="D12" t="n">
         <v>2.03217e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>84.37900000000002</v>
       </c>
+      <c r="C13" t="n">
+        <v>739.324784816772</v>
+      </c>
       <c r="D13" t="n">
         <v>2.02792e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>87.34799999999996</v>
       </c>
+      <c r="C14" t="n">
+        <v>749.1342183482767</v>
+      </c>
       <c r="D14" t="n">
         <v>2.02749e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>90.81100000000004</v>
       </c>
+      <c r="C15" t="n">
+        <v>969.3735051407908</v>
+      </c>
       <c r="D15" t="n">
         <v>2.02581e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>89.00400000000002</v>
       </c>
+      <c r="C16" t="n">
+        <v>951.9399148035945</v>
+      </c>
       <c r="D16" t="n">
         <v>2.02478e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>86.20400000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>905.6851992657395</v>
+      </c>
       <c r="D17" t="n">
         <v>2.02314e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>79.41500000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>740.9742668842119</v>
+      </c>
       <c r="D18" t="n">
         <v>2.02081e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>86.541</v>
       </c>
+      <c r="C19" t="n">
+        <v>1078.400579727261</v>
+      </c>
       <c r="D19" t="n">
         <v>2.02006e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>77.87</v>
       </c>
+      <c r="C20" t="n">
+        <v>766.3644400935323</v>
+      </c>
       <c r="D20" t="n">
         <v>2.01904e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>80.19100000000003</v>
       </c>
+      <c r="C21" t="n">
+        <v>859.9825047100417</v>
+      </c>
       <c r="D21" t="n">
         <v>2.01896e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>75.30499999999995</v>
+      </c>
+      <c r="C22" t="n">
+        <v>774.0441228870425</v>
       </c>
       <c r="D22" t="n">
         <v>2.01866e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>221.4800000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>2207.337456758381</v>
+      </c>
       <c r="D2" t="n">
         <v>2.22512e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>159.005</v>
       </c>
+      <c r="C3" t="n">
+        <v>990.6278237908825</v>
+      </c>
       <c r="D3" t="n">
         <v>2.22012e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>142.913</v>
       </c>
+      <c r="C4" t="n">
+        <v>845.3013265219539</v>
+      </c>
       <c r="D4" t="n">
         <v>2.17361e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>136.63</v>
       </c>
+      <c r="C5" t="n">
+        <v>822.2570959623042</v>
+      </c>
       <c r="D5" t="n">
         <v>2.13532e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>135.7259999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>892.1915026291431</v>
+      </c>
       <c r="D6" t="n">
         <v>2.10868e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>129.151</v>
       </c>
+      <c r="C7" t="n">
+        <v>867.2787028956334</v>
+      </c>
       <c r="D7" t="n">
         <v>2.09044e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>126.192</v>
       </c>
+      <c r="C8" t="n">
+        <v>873.6647680699333</v>
+      </c>
       <c r="D8" t="n">
         <v>2.07551e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>121.662</v>
       </c>
+      <c r="C9" t="n">
+        <v>890.1579079359947</v>
+      </c>
       <c r="D9" t="n">
         <v>2.06564e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>117.721</v>
       </c>
+      <c r="C10" t="n">
+        <v>868.8881625183919</v>
+      </c>
       <c r="D10" t="n">
         <v>2.05665e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>114.834</v>
+      </c>
+      <c r="C11" t="n">
+        <v>862.2437942575193</v>
       </c>
       <c r="D11" t="n">
         <v>2.05115e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>139.05</v>
       </c>
+      <c r="C2" t="n">
+        <v>1301.278089571177</v>
+      </c>
       <c r="D2" t="n">
         <v>2.22285e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>120.947</v>
       </c>
+      <c r="C3" t="n">
+        <v>940.9387054219322</v>
+      </c>
       <c r="D3" t="n">
         <v>2.1491e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>115.583</v>
       </c>
+      <c r="C4" t="n">
+        <v>912.9301190935128</v>
+      </c>
       <c r="D4" t="n">
         <v>2.10827e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>111.215</v>
       </c>
+      <c r="C5" t="n">
+        <v>892.0217466808488</v>
+      </c>
       <c r="D5" t="n">
         <v>2.08546e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>108.997</v>
       </c>
+      <c r="C6" t="n">
+        <v>942.8411032221029</v>
+      </c>
       <c r="D6" t="n">
         <v>2.07034e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>104.198</v>
       </c>
+      <c r="C7" t="n">
+        <v>891.5610816888299</v>
+      </c>
       <c r="D7" t="n">
         <v>2.06051e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>102.777</v>
       </c>
+      <c r="C8" t="n">
+        <v>929.0049420155005</v>
+      </c>
       <c r="D8" t="n">
         <v>2.05404e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>99.59099999999995</v>
       </c>
+      <c r="C9" t="n">
+        <v>904.679120761935</v>
+      </c>
       <c r="D9" t="n">
         <v>2.04961e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>97.113</v>
       </c>
+      <c r="C10" t="n">
+        <v>897.925211109319</v>
+      </c>
       <c r="D10" t="n">
         <v>2.0466e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>94.43000000000001</v>
       </c>
+      <c r="C11" t="n">
+        <v>886.8729762132493</v>
+      </c>
       <c r="D11" t="n">
         <v>2.04342e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>95.286</v>
       </c>
+      <c r="C12" t="n">
+        <v>1020.13372924156</v>
+      </c>
       <c r="D12" t="n">
         <v>2.03987e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>92.65300000000002</v>
       </c>
+      <c r="C13" t="n">
+        <v>1029.415627428931</v>
+      </c>
       <c r="D13" t="n">
         <v>2.04002e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>90.47900000000004</v>
       </c>
+      <c r="C14" t="n">
+        <v>948.9749746057703</v>
+      </c>
       <c r="D14" t="n">
         <v>2.03873e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>87.19799999999998</v>
       </c>
+      <c r="C15" t="n">
+        <v>870.2405892861819</v>
+      </c>
       <c r="D15" t="n">
         <v>2.03755e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>86.45800000000003</v>
       </c>
+      <c r="C16" t="n">
+        <v>946.553467888187</v>
+      </c>
       <c r="D16" t="n">
         <v>2.03504e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>86.70999999999998</v>
       </c>
+      <c r="C17" t="n">
+        <v>999.294908602044</v>
+      </c>
       <c r="D17" t="n">
         <v>2.03351e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>83.69299999999998</v>
       </c>
+      <c r="C18" t="n">
+        <v>927.7786660360786</v>
+      </c>
       <c r="D18" t="n">
         <v>2.03396e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>81.37099999999998</v>
       </c>
+      <c r="C19" t="n">
+        <v>913.4185454055532</v>
+      </c>
       <c r="D19" t="n">
         <v>2.03227e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>81.685</v>
       </c>
+      <c r="C20" t="n">
+        <v>1024.555840843728</v>
+      </c>
       <c r="D20" t="n">
         <v>2.03251e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>80.19</v>
       </c>
+      <c r="C21" t="n">
+        <v>1008.101025040324</v>
+      </c>
       <c r="D21" t="n">
         <v>2.03131e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>78.18800000000005</v>
+      </c>
+      <c r="C22" t="n">
+        <v>943.1910877447787</v>
       </c>
       <c r="D22" t="n">
         <v>2.03144e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>214.316</v>
       </c>
+      <c r="C2" t="n">
+        <v>2775.420309901368</v>
+      </c>
       <c r="D2" t="n">
         <v>2.17122e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>148.211</v>
       </c>
+      <c r="C3" t="n">
+        <v>1077.194128102726</v>
+      </c>
       <c r="D3" t="n">
         <v>2.13894e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>132.58</v>
       </c>
+      <c r="C4" t="n">
+        <v>916.0761083864587</v>
+      </c>
       <c r="D4" t="n">
         <v>2.0923e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>127.028</v>
       </c>
+      <c r="C5" t="n">
+        <v>901.2275125754859</v>
+      </c>
       <c r="D5" t="n">
         <v>2.06293e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>121.155</v>
       </c>
+      <c r="C6" t="n">
+        <v>858.9891546676095</v>
+      </c>
       <c r="D6" t="n">
         <v>2.04438e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>119.134</v>
       </c>
+      <c r="C7" t="n">
+        <v>956.9288693922011</v>
+      </c>
       <c r="D7" t="n">
         <v>2.03261e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>111.013</v>
       </c>
+      <c r="C8" t="n">
+        <v>842.1176910828918</v>
+      </c>
       <c r="D8" t="n">
         <v>2.026e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>108.872</v>
       </c>
+      <c r="C9" t="n">
+        <v>873.6671160294553</v>
+      </c>
       <c r="D9" t="n">
         <v>2.02286e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>104.855</v>
       </c>
+      <c r="C10" t="n">
+        <v>858.9780063961674</v>
+      </c>
       <c r="D10" t="n">
         <v>2.01866e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>102.53</v>
+      </c>
+      <c r="C11" t="n">
+        <v>896.2470671650833</v>
       </c>
       <c r="D11" t="n">
         <v>2.01751e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
@@ -565,7 +565,7 @@
         <v>138.501</v>
       </c>
       <c r="C2" t="n">
-        <v>966.7349646646384</v>
+        <v>138.501</v>
       </c>
       <c r="D2" t="n">
         <v>1.95684e-07</v>
@@ -597,11 +597,10 @@
       <c r="X2" t="n">
         <v>-8917.560906360937</v>
       </c>
-      <c r="Y2" t="n">
-        <v>392.3852699213554</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9533.264975735194</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>2.438600227885863e-07</v>
@@ -618,7 +617,7 @@
         <v>129.59</v>
       </c>
       <c r="C3" t="n">
-        <v>908.873917928286</v>
+        <v>404.1039604490111</v>
       </c>
       <c r="D3" t="n">
         <v>1.93942e-07</v>
@@ -651,16 +650,13 @@
         <v>-9369.249437810791</v>
       </c>
       <c r="Y3" t="n">
-        <v>396.0456486697562</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9362.811443314769</v>
+        <v>98.33887810186131</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.78915101036418e-07</v>
+        <v>1.819675660387655e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9999204281533011</v>
+        <v>0.9745966193258595</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +667,7 @@
         <v>123.381</v>
       </c>
       <c r="C4" t="n">
-        <v>923.6094680434049</v>
+        <v>123.381</v>
       </c>
       <c r="D4" t="n">
         <v>1.93022e-07</v>
@@ -703,11 +699,10 @@
       <c r="X4" t="n">
         <v>-9930.846499784375</v>
       </c>
-      <c r="Y4" t="n">
-        <v>400.0436482782952</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>9220.651362595481</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>2.802709651195645e-07</v>
@@ -724,7 +719,7 @@
         <v>118.954</v>
       </c>
       <c r="C5" t="n">
-        <v>985.1002062585757</v>
+        <v>351.4208489407962</v>
       </c>
       <c r="D5" t="n">
         <v>1.92323e-07</v>
@@ -757,16 +752,13 @@
         <v>-10328.32300117538</v>
       </c>
       <c r="Y5" t="n">
-        <v>438.2503615064896</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>119712396.0346604</v>
+        <v>133.1041097350177</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.818973701837098e-07</v>
+        <v>1.697284005863347e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9411084336405583</v>
+        <v>0.99407679996889</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +769,7 @@
         <v>114.227</v>
       </c>
       <c r="C6" t="n">
-        <v>1007.698689013435</v>
+        <v>393.3372019909996</v>
       </c>
       <c r="D6" t="n">
         <v>1.91832e-07</v>
@@ -810,16 +802,13 @@
         <v>-10436.23635366751</v>
       </c>
       <c r="Y6" t="n">
-        <v>396.8350111428777</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5361.791099819091</v>
+        <v>85.97933915693741</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.615074796157945e-07</v>
+        <v>1.645821914936962e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.99486852195708</v>
+        <v>0.9819957006156264</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +819,7 @@
         <v>110.023</v>
       </c>
       <c r="C7" t="n">
-        <v>990.6259045432533</v>
+        <v>110.023</v>
       </c>
       <c r="D7" t="n">
         <v>1.91547e-07</v>
@@ -862,11 +851,10 @@
       <c r="X7" t="n">
         <v>-10820.7482676827</v>
       </c>
-      <c r="Y7" t="n">
-        <v>428.0516198845814</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>584645167.8581148</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>2.722918176483303e-07</v>
@@ -883,7 +871,7 @@
         <v>103.65</v>
       </c>
       <c r="C8" t="n">
-        <v>852.5885015717703</v>
+        <v>360.8110913962698</v>
       </c>
       <c r="D8" t="n">
         <v>1.91229e-07</v>
@@ -916,16 +904,13 @@
         <v>-10337.40422219515</v>
       </c>
       <c r="Y8" t="n">
-        <v>404.595726137393</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7008.41535739208</v>
+        <v>107.0367775256407</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.757651812312542e-07</v>
+        <v>1.591703281482044e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9997968082972996</v>
+        <v>0.9938716306206703</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +921,7 @@
         <v>104.213</v>
       </c>
       <c r="C9" t="n">
-        <v>987.9821862077644</v>
+        <v>310.1357111592491</v>
       </c>
       <c r="D9" t="n">
         <v>1.91113e-07</v>
@@ -969,16 +954,13 @@
         <v>-11034.89805168537</v>
       </c>
       <c r="Y9" t="n">
-        <v>396.344364468504</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3445.918760952376</v>
+        <v>146.2733653314408</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.674240548518478e-06</v>
+        <v>1.654457180286112e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.796426022002927</v>
+        <v>0.999996260403554</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +971,7 @@
         <v>103.201</v>
       </c>
       <c r="C10" t="n">
-        <v>1079.992084624996</v>
+        <v>103.201</v>
       </c>
       <c r="D10" t="n">
         <v>1.90915e-07</v>
@@ -1021,11 +1003,10 @@
       <c r="X10" t="n">
         <v>-11342.23762260074</v>
       </c>
-      <c r="Y10" t="n">
-        <v>416.6103328079388</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3414.342682673649</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>5.34341227999384e-07</v>
@@ -1042,7 +1023,7 @@
         <v>99.61799999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1016.052454862345</v>
+        <v>263.7208678429876</v>
       </c>
       <c r="D11" t="n">
         <v>1.90844e-07</v>
@@ -1075,16 +1056,13 @@
         <v>-11101.29796171167</v>
       </c>
       <c r="Y11" t="n">
-        <v>398.2819710877487</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3384.168171902844</v>
+        <v>189.5072315812574</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02322983282711e-06</v>
+        <v>2.274946339248479e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8546244248852769</v>
+        <v>0.9989692961580605</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1219,7 @@
         <v>141.597</v>
       </c>
       <c r="C2" t="n">
-        <v>1403.702084050206</v>
+        <v>322.2581138380917</v>
       </c>
       <c r="D2" t="n">
         <v>2.01573e-07</v>
@@ -1274,16 +1252,13 @@
         <v>-11454.311163739</v>
       </c>
       <c r="Y2" t="n">
-        <v>396.7494757253389</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9476.531367599982</v>
+        <v>182.3820021625344</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.882106739746401e-07</v>
+        <v>1.813575367725489e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9998892794082589</v>
+        <v>0.9995179416494323</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1269,7 @@
         <v>119.287</v>
       </c>
       <c r="C3" t="n">
-        <v>906.9684210794503</v>
+        <v>319.9067750171155</v>
       </c>
       <c r="D3" t="n">
         <v>2.01753e-07</v>
@@ -1327,16 +1302,13 @@
         <v>-11972.29840595214</v>
       </c>
       <c r="Y3" t="n">
-        <v>444.3248684806564</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>124542088.0869367</v>
+        <v>170.6174450550069</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.872969470109779e-07</v>
+        <v>2.002624094619353e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9455210549081215</v>
+        <v>0.9937310391099804</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1319,7 @@
         <v>112.807</v>
       </c>
       <c r="C4" t="n">
-        <v>918.0841593150506</v>
+        <v>315.5219111877312</v>
       </c>
       <c r="D4" t="n">
         <v>2.01569e-07</v>
@@ -1380,16 +1352,13 @@
         <v>-12293.22524157472</v>
       </c>
       <c r="Y4" t="n">
-        <v>438.6912072937703</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>180002047.1834024</v>
+        <v>168.4361583879571</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.833385558037288e-07</v>
+        <v>1.980545334892253e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9475143334988627</v>
+        <v>0.9953023968983734</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1369,7 @@
         <v>108.606</v>
       </c>
       <c r="C5" t="n">
-        <v>871.306455621668</v>
+        <v>313.8486457192402</v>
       </c>
       <c r="D5" t="n">
         <v>2.01135e-07</v>
@@ -1433,16 +1402,13 @@
         <v>-12220.46556277548</v>
       </c>
       <c r="Y5" t="n">
-        <v>417.8418410683744</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5838.71159234117</v>
+        <v>165.1801581050601</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.397371370064106e-07</v>
+        <v>1.934390986114771e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9529945128565545</v>
+        <v>0.9969035908494088</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1419,7 @@
         <v>107.688</v>
       </c>
       <c r="C6" t="n">
-        <v>957.5271999468957</v>
+        <v>107.688</v>
       </c>
       <c r="D6" t="n">
         <v>2.00886e-07</v>
@@ -1485,11 +1451,10 @@
       <c r="X6" t="n">
         <v>-13032.51340970559</v>
       </c>
-      <c r="Y6" t="n">
-        <v>407.3648962783021</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3541.201247124014</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.883231697752806e-06</v>
@@ -1506,7 +1471,7 @@
         <v>104.328</v>
       </c>
       <c r="C7" t="n">
-        <v>923.3383443510066</v>
+        <v>353.0617204901073</v>
       </c>
       <c r="D7" t="n">
         <v>2.00712e-07</v>
@@ -1539,16 +1504,13 @@
         <v>-12696.37825638546</v>
       </c>
       <c r="Y7" t="n">
-        <v>409.4310658951832</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3513.279001399675</v>
+        <v>118.8717490691882</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.832195786694801e-06</v>
+        <v>1.857513262394158e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7498059072504979</v>
+        <v>0.9849733258625379</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1521,7 @@
         <v>101.577</v>
       </c>
       <c r="C8" t="n">
-        <v>957.394322389359</v>
+        <v>338.7864062718298</v>
       </c>
       <c r="D8" t="n">
         <v>2.00704e-07</v>
@@ -1592,16 +1554,13 @@
         <v>-12867.18162016381</v>
       </c>
       <c r="Y8" t="n">
-        <v>410.3922897139009</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3480.175744170541</v>
+        <v>128.4765140552336</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.436075765014825e-06</v>
+        <v>1.803363695431059e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7459538723595734</v>
+        <v>0.9915014525205054</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1571,7 @@
         <v>100.219</v>
       </c>
       <c r="C9" t="n">
-        <v>994.39927794036</v>
+        <v>100.219</v>
       </c>
       <c r="D9" t="n">
         <v>2.00308e-07</v>
@@ -1644,11 +1603,10 @@
       <c r="X9" t="n">
         <v>-12859.53640128036</v>
       </c>
-      <c r="Y9" t="n">
-        <v>401.8272138803461</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3451.573212426066</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>2.042168233436052e-06</v>
@@ -1665,7 +1623,7 @@
         <v>95.584</v>
       </c>
       <c r="C10" t="n">
-        <v>904.893478330109</v>
+        <v>384.0125716316965</v>
       </c>
       <c r="D10" t="n">
         <v>2.00132e-07</v>
@@ -1698,16 +1656,13 @@
         <v>-12442.84112008396</v>
       </c>
       <c r="Y10" t="n">
-        <v>398.0725959979554</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3420.699389341019</v>
+        <v>75.0523537607382</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.163559562718493e-06</v>
+        <v>1.682074662612364e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7869633325249612</v>
+        <v>0.9792261986958503</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1673,7 @@
         <v>95.19200000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>965.0119477402844</v>
+        <v>95.19200000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.00153e-07</v>
@@ -1750,11 +1705,10 @@
       <c r="X11" t="n">
         <v>-12767.12813026552</v>
       </c>
-      <c r="Y11" t="n">
-        <v>394.9177349925651</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3391.415712651376</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>2.207869693961968e-06</v>
@@ -1771,7 +1725,7 @@
         <v>93.88599999999997</v>
       </c>
       <c r="C12" t="n">
-        <v>1053.368548941682</v>
+        <v>296.6987538640719</v>
       </c>
       <c r="D12" t="n">
         <v>2.00104e-07</v>
@@ -1804,16 +1758,13 @@
         <v>-12949.64916619227</v>
       </c>
       <c r="Y12" t="n">
-        <v>392.6016724387123</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3360.517903602971</v>
+        <v>148.1711482148679</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.052067875112602e-06</v>
+        <v>1.748177417864033e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.795707823975795</v>
+        <v>0.9999872842658929</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1775,7 @@
         <v>92.255</v>
       </c>
       <c r="C13" t="n">
-        <v>987.0776317389048</v>
+        <v>250.9789597013442</v>
       </c>
       <c r="D13" t="n">
         <v>2.0007e-07</v>
@@ -1857,16 +1808,13 @@
         <v>-12800.42298278033</v>
       </c>
       <c r="Y13" t="n">
-        <v>396.7291897181614</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5447.895109564663</v>
+        <v>192.2295843757745</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.086245210894876e-06</v>
+        <v>2.346739784181403e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8461773584740592</v>
+        <v>0.999207435673359</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1825,7 @@
         <v>89.22300000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>943.9417919169543</v>
+        <v>248.0360773346915</v>
       </c>
       <c r="D14" t="n">
         <v>2.00008e-07</v>
@@ -1910,16 +1858,13 @@
         <v>-12513.05546288944</v>
       </c>
       <c r="Y14" t="n">
-        <v>392.4449466826355</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6664.223827601112</v>
+        <v>196.1622332647971</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.80176729512535e-07</v>
+        <v>2.47783416016442e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9994292745609792</v>
+        <v>0.9999748467400523</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1875,7 @@
         <v>87.88100000000003</v>
       </c>
       <c r="C15" t="n">
-        <v>977.8057462004066</v>
+        <v>245.7389867318375</v>
       </c>
       <c r="D15" t="n">
         <v>1.99847e-07</v>
@@ -1963,16 +1908,13 @@
         <v>-12665.15693548672</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.7722451537153</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>109184778.3241984</v>
+        <v>197.8801829301575</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.641568219533586e-07</v>
+        <v>2.690753047071048e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9569485877414382</v>
+        <v>0.9989833213925445</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1925,7 @@
         <v>87.47899999999998</v>
       </c>
       <c r="C16" t="n">
-        <v>1055.713465070319</v>
+        <v>243.0236603489989</v>
       </c>
       <c r="D16" t="n">
         <v>1.99828e-07</v>
@@ -2016,16 +1958,13 @@
         <v>-12882.958399677</v>
       </c>
       <c r="Y16" t="n">
-        <v>396.4967727724966</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>433539134.4037449</v>
+        <v>194.4082507617709</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.636242338467464e-07</v>
+        <v>2.668793416758711e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9572436146272094</v>
+        <v>0.9963530614934706</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1975,7 @@
         <v>83.63200000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>925.4453826221197</v>
+        <v>238.1927251928782</v>
       </c>
       <c r="D17" t="n">
         <v>1.99709e-07</v>
@@ -2069,16 +2008,13 @@
         <v>-12228.12304005591</v>
       </c>
       <c r="Y17" t="n">
-        <v>393.2524944883046</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>214709801.261642</v>
+        <v>198.479096425497</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.629495894298315e-07</v>
+        <v>3.424907585877339e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9575580020846242</v>
+        <v>0.980907645152904</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2025,7 @@
         <v>82.82799999999997</v>
       </c>
       <c r="C18" t="n">
-        <v>973.3296052282029</v>
+        <v>235.8149895627695</v>
       </c>
       <c r="D18" t="n">
         <v>1.99687e-07</v>
@@ -2122,16 +2058,13 @@
         <v>-12471.71380696104</v>
       </c>
       <c r="Y18" t="n">
-        <v>389.9716284979895</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>213081000.0809783</v>
+        <v>197.2195565405797</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.615101207613322e-07</v>
+        <v>3.403351392816296e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9583742811641953</v>
+        <v>0.9820767351595519</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2075,7 @@
         <v>82.50600000000003</v>
       </c>
       <c r="C19" t="n">
-        <v>1044.965415462835</v>
+        <v>233.3800719172903</v>
       </c>
       <c r="D19" t="n">
         <v>1.99669e-07</v>
@@ -2175,16 +2108,13 @@
         <v>-12841.97133392083</v>
       </c>
       <c r="Y19" t="n">
-        <v>386.7074171342449</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>421719329.5008657</v>
+        <v>195.9879452990336</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.602481999857752e-07</v>
+        <v>3.382839559567667e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9590930828932677</v>
+        <v>0.9832961882343498</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2125,7 @@
         <v>81.18900000000002</v>
       </c>
       <c r="C20" t="n">
-        <v>1061.981477181439</v>
+        <v>230.6037322608561</v>
       </c>
       <c r="D20" t="n">
         <v>1.99708e-07</v>
@@ -2228,16 +2158,13 @@
         <v>-12743.90095813156</v>
       </c>
       <c r="Y20" t="n">
-        <v>383.4161594966821</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>156971907.8893668</v>
+        <v>191.8633312296448</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.596409672831079e-07</v>
+        <v>2.716060537530561e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9594810691287596</v>
+        <v>0.9990537751939497</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2175,7 @@
         <v>78.11099999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>934.8373786576835</v>
+        <v>78.11099999999999</v>
       </c>
       <c r="D21" t="n">
         <v>1.9952e-07</v>
@@ -2280,11 +2207,10 @@
       <c r="X21" t="n">
         <v>-12207.67305997291</v>
       </c>
-      <c r="Y21" t="n">
-        <v>380.0833278472551</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>417669598.8100793</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>2.59198318755664e-07</v>
@@ -2301,7 +2227,7 @@
         <v>77.51800000000003</v>
       </c>
       <c r="C22" t="n">
-        <v>1022.130042372366</v>
+        <v>224.4018290997645</v>
       </c>
       <c r="D22" t="n">
         <v>1.99644e-07</v>
@@ -2334,16 +2260,13 @@
         <v>-12408.9306361771</v>
       </c>
       <c r="Y22" t="n">
-        <v>376.7321260772224</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>821698538.8496218</v>
+        <v>197.5309432441054</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.583546293951973e-07</v>
+        <v>3.746621530877341e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9602034087251805</v>
+        <v>0.982299594660299</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2423,7 @@
         <v>144.443</v>
       </c>
       <c r="C2" t="n">
-        <v>1523.140629019508</v>
+        <v>359.1033787925725</v>
       </c>
       <c r="D2" t="n">
         <v>2.00357e-07</v>
@@ -2533,16 +2456,13 @@
         <v>-8443.835225751443</v>
       </c>
       <c r="Y2" t="n">
-        <v>389.2641854037344</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9438.734488921295</v>
+        <v>145.4585126435157</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.691687203878487e-07</v>
+        <v>1.714470066815772e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9999915846588626</v>
+        <v>0.9912215692609548</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2473,7 @@
         <v>122.482</v>
       </c>
       <c r="C3" t="n">
-        <v>962.8337508199561</v>
+        <v>393.3103959142057</v>
       </c>
       <c r="D3" t="n">
         <v>1.97585e-07</v>
@@ -2586,16 +2506,13 @@
         <v>-9732.232477525022</v>
       </c>
       <c r="Y3" t="n">
-        <v>444.3892088893612</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>275034535.7965506</v>
+        <v>100.0383032416097</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.978991088999044e-07</v>
+        <v>1.8305292907825e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9368204391709387</v>
+        <v>0.9744912567276055</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2523,7 @@
         <v>116.396</v>
       </c>
       <c r="C4" t="n">
-        <v>889.1978480225758</v>
+        <v>406.3500374276892</v>
       </c>
       <c r="D4" t="n">
         <v>1.95816e-07</v>
@@ -2639,16 +2556,13 @@
         <v>-10335.71761182124</v>
       </c>
       <c r="Y4" t="n">
-        <v>440.0568515880346</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>240621612.1324463</v>
+        <v>82.52322921554952</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.860956787255022e-07</v>
+        <v>1.830927046297197e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9415976713744054</v>
+        <v>0.9707889348805664</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2573,7 @@
         <v>114.402</v>
       </c>
       <c r="C5" t="n">
-        <v>965.0040557511979</v>
+        <v>348.6279892432388</v>
       </c>
       <c r="D5" t="n">
         <v>1.94808e-07</v>
@@ -2692,16 +2606,13 @@
         <v>-10994.98780652848</v>
       </c>
       <c r="Y5" t="n">
-        <v>398.2001340594994</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5406.38089737983</v>
+        <v>134.3576243159907</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.860492604380701e-07</v>
+        <v>1.789782543980521e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9977171249270285</v>
+        <v>0.991545714353061</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2623,7 @@
         <v>112.248</v>
       </c>
       <c r="C6" t="n">
-        <v>968.9116453602002</v>
+        <v>461.751594180986</v>
       </c>
       <c r="D6" t="n">
         <v>1.93611e-07</v>
@@ -2745,16 +2656,13 @@
         <v>-11392.26888037231</v>
       </c>
       <c r="Y6" t="n">
-        <v>432.9405962807775</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>177597871.0050992</v>
+        <v>18.80715922192942</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.740835969958982e-07</v>
+        <v>1.664900742836493e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9464005142652194</v>
+        <v>0.9602860093529327</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2673,7 @@
         <v>104.444</v>
       </c>
       <c r="C7" t="n">
-        <v>827.8846907544163</v>
+        <v>455.6273440883452</v>
       </c>
       <c r="D7" t="n">
         <v>1.92993e-07</v>
@@ -2798,16 +2706,13 @@
         <v>-10691.1573461141</v>
       </c>
       <c r="Y7" t="n">
-        <v>429.2720127468851</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>131379918.8100471</v>
+        <v>67.35632110554187</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.711191797803587e-07</v>
+        <v>1.853632059769889e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9475764609978318</v>
+        <v>0.7995832909690593</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2723,7 @@
         <v>106.312</v>
       </c>
       <c r="C8" t="n">
-        <v>943.8484478722378</v>
+        <v>106.312</v>
       </c>
       <c r="D8" t="n">
         <v>1.92702e-07</v>
@@ -2850,11 +2755,10 @@
       <c r="X8" t="n">
         <v>-11568.18492996886</v>
       </c>
-      <c r="Y8" t="n">
-        <v>400.6062179018882</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3497.323809068671</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>1.372327666852999e-06</v>
@@ -2871,7 +2775,7 @@
         <v>103.194</v>
       </c>
       <c r="C9" t="n">
-        <v>933.0623163200513</v>
+        <v>359.1297697314813</v>
       </c>
       <c r="D9" t="n">
         <v>1.92354e-07</v>
@@ -2904,16 +2808,13 @@
         <v>-11495.58480201084</v>
       </c>
       <c r="Y9" t="n">
-        <v>398.3053204553214</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3467.883491214865</v>
+        <v>106.621677190038</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.887831323794435e-06</v>
+        <v>1.622688592133027e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8276861352393354</v>
+        <v>0.9920943785689933</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2825,7 @@
         <v>101.917</v>
       </c>
       <c r="C10" t="n">
-        <v>974.5262067881015</v>
+        <v>101.917</v>
       </c>
       <c r="D10" t="n">
         <v>1.91975e-07</v>
@@ -2956,11 +2857,10 @@
       <c r="X10" t="n">
         <v>-11513.67109539355</v>
       </c>
-      <c r="Y10" t="n">
-        <v>396.1497307437309</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3438.441035097835</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.431068250308762e-06</v>
@@ -2977,7 +2877,7 @@
         <v>100.543</v>
       </c>
       <c r="C11" t="n">
-        <v>982.8799636306808</v>
+        <v>100.543</v>
       </c>
       <c r="D11" t="n">
         <v>1.91844e-07</v>
@@ -3009,11 +2909,10 @@
       <c r="X11" t="n">
         <v>-12010.66582961547</v>
       </c>
-      <c r="Y11" t="n">
-        <v>401.7231552261159</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3412.832673651475</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.456768027234675e-06</v>
@@ -3030,7 +2929,7 @@
         <v>99.43799999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>1008.073351985019</v>
+        <v>99.43799999999999</v>
       </c>
       <c r="D12" t="n">
         <v>1.91816e-07</v>
@@ -3062,11 +2961,10 @@
       <c r="X12" t="n">
         <v>-11829.41361215599</v>
       </c>
-      <c r="Y12" t="n">
-        <v>399.3818093506226</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3387.691293796541</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>2.383942218219332e-06</v>
@@ -3083,7 +2981,7 @@
         <v>97.267</v>
       </c>
       <c r="C13" t="n">
-        <v>989.6636415229151</v>
+        <v>261.2605888358228</v>
       </c>
       <c r="D13" t="n">
         <v>1.91696e-07</v>
@@ -3116,16 +3014,13 @@
         <v>-11915.85226544596</v>
       </c>
       <c r="Y13" t="n">
-        <v>389.5323363948127</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3360.216150151757</v>
+        <v>187.8951688090603</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.195862087507691e-07</v>
+        <v>2.2648700493786e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9070175407960126</v>
+        <v>0.9992806648820572</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3031,7 @@
         <v>93.57899999999995</v>
       </c>
       <c r="C14" t="n">
-        <v>917.050035084088</v>
+        <v>258.4067836172654</v>
       </c>
       <c r="D14" t="n">
         <v>1.91522e-07</v>
@@ -3169,16 +3064,13 @@
         <v>-11602.94415101687</v>
       </c>
       <c r="Y14" t="n">
-        <v>387.823236919842</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3336.477931899493</v>
+        <v>187.802499692675</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.338465187457495e-06</v>
+        <v>2.301476844229403e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.865753442133903</v>
+        <v>0.9993361368228277</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3081,7 @@
         <v>92.46599999999995</v>
       </c>
       <c r="C15" t="n">
-        <v>915.1229033648135</v>
+        <v>254.8489056802267</v>
       </c>
       <c r="D15" t="n">
         <v>1.91392e-07</v>
@@ -3222,16 +3114,13 @@
         <v>-11623.64944297491</v>
       </c>
       <c r="Y15" t="n">
-        <v>385.9210006002306</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3310.725987911137</v>
+        <v>190.8609654883036</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.278261324028647e-06</v>
+        <v>2.449975524369841e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.77288927840608</v>
+        <v>0.9983662204592667</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3131,7 @@
         <v>88.57900000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>857.667000833806</v>
+        <v>250.2869975341831</v>
       </c>
       <c r="D16" t="n">
         <v>1.91196e-07</v>
@@ -3275,16 +3164,13 @@
         <v>-11144.20187366029</v>
       </c>
       <c r="Y16" t="n">
-        <v>382.8073391755756</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3284.53309290317</v>
+        <v>191.0354966526693</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.036033224453668e-06</v>
+        <v>2.464742781318802e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.7812191704554601</v>
+        <v>0.9991758632407943</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3181,7 @@
         <v>91.46300000000002</v>
       </c>
       <c r="C17" t="n">
-        <v>1002.993553995279</v>
+        <v>247.2830186257725</v>
       </c>
       <c r="D17" t="n">
         <v>1.91286e-07</v>
@@ -3328,16 +3214,13 @@
         <v>-11978.88868680382</v>
       </c>
       <c r="Y17" t="n">
-        <v>380.5451129956429</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3256.532925106155</v>
+        <v>194.1320831631708</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.320747769681876e-06</v>
+        <v>2.633417361981143e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.751164802217363</v>
+        <v>0.9974672774603183</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3231,7 @@
         <v>88.37800000000004</v>
       </c>
       <c r="C18" t="n">
-        <v>973.412526539846</v>
+        <v>244.8384308295883</v>
       </c>
       <c r="D18" t="n">
         <v>1.91463e-07</v>
@@ -3381,16 +3264,13 @@
         <v>-11703.52185731023</v>
       </c>
       <c r="Y18" t="n">
-        <v>378.2082836349923</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3233.147256429379</v>
+        <v>192.5535134538863</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.495366725827964e-06</v>
+        <v>2.614896450386498e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.737177830170329</v>
+        <v>0.9980567920653578</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3281,7 @@
         <v>85.84299999999996</v>
       </c>
       <c r="C19" t="n">
-        <v>898.7146910221624</v>
+        <v>242.0535003852923</v>
       </c>
       <c r="D19" t="n">
         <v>1.91275e-07</v>
@@ -3434,16 +3314,13 @@
         <v>-11613.07042188007</v>
       </c>
       <c r="Y19" t="n">
-        <v>381.0013491713657</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6456.10592856806</v>
+        <v>189.516600512488</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.300741278904517e-07</v>
+        <v>2.55278479192917e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9817457185723493</v>
+        <v>0.9995426016347961</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3331,7 @@
         <v>84.73099999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>902.171545790713</v>
+        <v>84.73099999999999</v>
       </c>
       <c r="D20" t="n">
         <v>1.91232e-07</v>
@@ -3486,11 +3363,10 @@
       <c r="X20" t="n">
         <v>-11474.17973212605</v>
       </c>
-      <c r="Y20" t="n">
-        <v>387.8804115815154</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>211750724.108005</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>2.525816888742271e-07</v>
@@ -3507,7 +3383,7 @@
         <v>85.08499999999998</v>
       </c>
       <c r="C21" t="n">
-        <v>1036.441531195201</v>
+        <v>85.08499999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.91346e-07</v>
@@ -3539,11 +3415,10 @@
       <c r="X21" t="n">
         <v>-11847.35195363607</v>
       </c>
-      <c r="Y21" t="n">
-        <v>384.7771348296757</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>839146429.5784309</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>2.52074311950449e-07</v>
@@ -3560,7 +3435,7 @@
         <v>82.61000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>979.1045299897343</v>
+        <v>82.61000000000001</v>
       </c>
       <c r="D22" t="n">
         <v>1.91362e-07</v>
@@ -3592,11 +3467,10 @@
       <c r="X22" t="n">
         <v>-11786.01441180474</v>
       </c>
-      <c r="Y22" t="n">
-        <v>381.7412887030474</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>420170915.8172156</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>2.508632464002284e-07</v>
@@ -3759,7 +3633,7 @@
         <v>230.682</v>
       </c>
       <c r="C2" t="n">
-        <v>2255.069829421123</v>
+        <v>230.682</v>
       </c>
       <c r="D2" t="n">
         <v>2.15998e-07</v>
@@ -3791,11 +3665,10 @@
       <c r="X2" t="n">
         <v>-5401.071129848235</v>
       </c>
-      <c r="Y2" t="n">
-        <v>514.5894486391926</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>285869104.6976956</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>5.772404767762741e-07</v>
@@ -3812,7 +3685,7 @@
         <v>164.109</v>
       </c>
       <c r="C3" t="n">
-        <v>1020.280386468572</v>
+        <v>550.6380378063353</v>
       </c>
       <c r="D3" t="n">
         <v>2.20096e-07</v>
@@ -3845,16 +3718,13 @@
         <v>-6178.567879544428</v>
       </c>
       <c r="Y3" t="n">
-        <v>483.0142044814073</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>268188951.6084123</v>
+        <v>0.1419235541111719</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.537211082018327e-07</v>
+        <v>2.648475863163013e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8899330000803782</v>
+        <v>0.9086961856818599</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3735,7 @@
         <v>149.1220000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>912.2721961556513</v>
+        <v>412.4973860085217</v>
       </c>
       <c r="D4" t="n">
         <v>2.17127e-07</v>
@@ -3898,16 +3768,13 @@
         <v>-7064.023934502686</v>
       </c>
       <c r="Y4" t="n">
-        <v>473.6879955288285</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>390715133.1608049</v>
+        <v>117.8080488661367</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.025617682073349e-07</v>
+        <v>2.382473165087734e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9058043978599836</v>
+        <v>0.953306403752528</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3785,7 @@
         <v>142.2090000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>904.5847994891204</v>
+        <v>355.8665963292669</v>
       </c>
       <c r="D5" t="n">
         <v>2.13877e-07</v>
@@ -3951,16 +3818,13 @@
         <v>-7877.713155714914</v>
       </c>
       <c r="Y5" t="n">
-        <v>468.1671033032571</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>193121447.887839</v>
+        <v>166.9245442836881</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.716303751517951e-07</v>
+        <v>2.434399898859493e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9155322562876601</v>
+        <v>0.9702151279764304</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3835,7 @@
         <v>136.679</v>
       </c>
       <c r="C6" t="n">
-        <v>874.1852419063313</v>
+        <v>342.3045309437439</v>
       </c>
       <c r="D6" t="n">
         <v>2.1135e-07</v>
@@ -4004,16 +3868,13 @@
         <v>-8563.418396649791</v>
       </c>
       <c r="Y6" t="n">
-        <v>463.1888459470676</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>412945724.0501981</v>
+        <v>173.1038773202364</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.493779008537029e-07</v>
+        <v>2.355363905414422e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9230168367433877</v>
+        <v>0.9754628659399882</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3885,7 @@
         <v>131.244</v>
       </c>
       <c r="C7" t="n">
-        <v>878.295980157101</v>
+        <v>131.244</v>
       </c>
       <c r="D7" t="n">
         <v>2.09211e-07</v>
@@ -4056,11 +3917,10 @@
       <c r="X7" t="n">
         <v>-8990.945290288122</v>
       </c>
-      <c r="Y7" t="n">
-        <v>458.0781117823967</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>251336372.6764174</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>3.355757330395731e-07</v>
@@ -4077,7 +3937,7 @@
         <v>127.628</v>
       </c>
       <c r="C8" t="n">
-        <v>879.8765319173681</v>
+        <v>323.5161155105779</v>
       </c>
       <c r="D8" t="n">
         <v>2.07505e-07</v>
@@ -4110,16 +3970,13 @@
         <v>-9548.56906772902</v>
       </c>
       <c r="Y8" t="n">
-        <v>453.1056739293182</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>248391625.5926813</v>
+        <v>178.4320744635027</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.227873529410139e-07</v>
+        <v>2.18909794780188e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9321849308159753</v>
+        <v>0.9861356342886891</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3987,7 @@
         <v>123.512</v>
       </c>
       <c r="C9" t="n">
-        <v>901.098218785148</v>
+        <v>322.2811218833756</v>
       </c>
       <c r="D9" t="n">
         <v>2.06022e-07</v>
@@ -4163,16 +4020,13 @@
         <v>-9704.214409331875</v>
       </c>
       <c r="Y9" t="n">
-        <v>448.1286515640717</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>321752148.2150379</v>
+        <v>174.2583093422677</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.147105274599211e-07</v>
+        <v>2.123916754791915e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9349488997125096</v>
+        <v>0.9894562384638026</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4037,7 @@
         <v>117.948</v>
       </c>
       <c r="C10" t="n">
-        <v>847.0306868210185</v>
+        <v>314.0878591048981</v>
       </c>
       <c r="D10" t="n">
         <v>2.04932e-07</v>
@@ -4216,16 +4070,13 @@
         <v>-9930.241038703818</v>
       </c>
       <c r="Y10" t="n">
-        <v>443.3643763277236</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>364039937.4832708</v>
+        <v>176.9739947874384</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.068180290307751e-07</v>
+        <v>2.086506894129291e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9379835186312472</v>
+        <v>0.993544861701483</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4087,7 @@
         <v>117.15</v>
       </c>
       <c r="C11" t="n">
-        <v>885.0039045711052</v>
+        <v>117.15</v>
       </c>
       <c r="D11" t="n">
         <v>2.03996e-07</v>
@@ -4268,11 +4119,10 @@
       <c r="X11" t="n">
         <v>-10483.1173978412</v>
       </c>
-      <c r="Y11" t="n">
-        <v>438.8792344827597</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>241205774.9745677</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.006781957533359e-07</v>
@@ -4435,7 +4285,7 @@
         <v>136.706</v>
       </c>
       <c r="C2" t="n">
-        <v>1320.691826857443</v>
+        <v>586.9234660627964</v>
       </c>
       <c r="D2" t="n">
         <v>2.17316e-07</v>
@@ -4468,16 +4318,13 @@
         <v>-6760.275873835084</v>
       </c>
       <c r="Y2" t="n">
-        <v>450.8678769253131</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>123242275.114243</v>
+        <v>0.801978203408435</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.884791817255893e-07</v>
+        <v>1.966751008494591e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9113499642088377</v>
+        <v>0.6077321142146948</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4335,7 @@
         <v>119.534</v>
       </c>
       <c r="C3" t="n">
-        <v>1000.069379908184</v>
+        <v>321.9432464507748</v>
       </c>
       <c r="D3" t="n">
         <v>2.11682e-07</v>
@@ -4521,16 +4368,13 @@
         <v>-8375.07279202027</v>
       </c>
       <c r="Y3" t="n">
-        <v>439.6563681340648</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>180977512.9080008</v>
+        <v>165.0193322075762</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.366011558935878e-07</v>
+        <v>2.071084915647505e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9289216952549978</v>
+        <v>0.989718303570739</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4385,7 @@
         <v>114.835</v>
       </c>
       <c r="C4" t="n">
-        <v>975.8467179586069</v>
+        <v>310.5228603367948</v>
       </c>
       <c r="D4" t="n">
         <v>2.08477e-07</v>
@@ -4574,16 +4418,13 @@
         <v>-9418.213977467049</v>
       </c>
       <c r="Y4" t="n">
-        <v>395.293628619102</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5395.605148669591</v>
+        <v>170.4556768759313</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.798345134825952e-07</v>
+        <v>2.061385542229933e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8725147479809059</v>
+        <v>0.9942220239996201</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4435,7 @@
         <v>111.529</v>
       </c>
       <c r="C5" t="n">
-        <v>1028.845286873228</v>
+        <v>365.4492776393831</v>
       </c>
       <c r="D5" t="n">
         <v>2.06316e-07</v>
@@ -4627,16 +4468,13 @@
         <v>-10235.1003737776</v>
       </c>
       <c r="Y5" t="n">
-        <v>431.024296780722</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>241022262.4156938</v>
+        <v>110.7232053468565</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.036202999131847e-07</v>
+        <v>1.875053427428916e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9406032166263536</v>
+        <v>0.9786608047753196</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4485,7 @@
         <v>107.625</v>
       </c>
       <c r="C6" t="n">
-        <v>979.8606459270776</v>
+        <v>390.9029367925189</v>
       </c>
       <c r="D6" t="n">
         <v>2.04785e-07</v>
@@ -4680,16 +4518,13 @@
         <v>-10519.78062742743</v>
       </c>
       <c r="Y6" t="n">
-        <v>402.2937102302833</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3512.599583949087</v>
+        <v>81.44095339148818</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.287681571068858e-06</v>
+        <v>1.811338575376071e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8166519810821551</v>
+        <v>0.9722594631901967</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4535,7 @@
         <v>103.759</v>
       </c>
       <c r="C7" t="n">
-        <v>927.1184177431016</v>
+        <v>333.3493184616344</v>
       </c>
       <c r="D7" t="n">
         <v>2.03659e-07</v>
@@ -4733,16 +4568,13 @@
         <v>-10653.12477143453</v>
       </c>
       <c r="Y7" t="n">
-        <v>405.4904995387254</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3480.233216384322</v>
+        <v>133.3232934452444</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.353391950136328e-06</v>
+        <v>1.815832178988152e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7818828453287834</v>
+        <v>0.9924916594606266</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4585,7 @@
         <v>99.08500000000004</v>
       </c>
       <c r="C8" t="n">
-        <v>873.5877452197328</v>
+        <v>327.6285199334545</v>
       </c>
       <c r="D8" t="n">
         <v>2.03039e-07</v>
@@ -4786,16 +4618,13 @@
         <v>-10653.92286913183</v>
       </c>
       <c r="Y8" t="n">
-        <v>402.3831554181585</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3451.586194284745</v>
+        <v>135.7441653605228</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05675726637929e-06</v>
+        <v>1.805126776956085e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7842147816995064</v>
+        <v>0.9950368260318636</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4635,7 @@
         <v>100.075</v>
       </c>
       <c r="C9" t="n">
-        <v>984.3312479759579</v>
+        <v>413.2048630038339</v>
       </c>
       <c r="D9" t="n">
         <v>2.02408e-07</v>
@@ -4839,16 +4668,13 @@
         <v>-11004.72459310727</v>
       </c>
       <c r="Y9" t="n">
-        <v>403.8965751825108</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3427.772219435024</v>
+        <v>47.43122704615386</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.826980749065107e-06</v>
+        <v>1.66505714371513e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7954648330292199</v>
+        <v>0.9708532616030385</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4685,7 @@
         <v>97.40600000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>988.1383306659585</v>
+        <v>349.9971200821049</v>
       </c>
       <c r="D10" t="n">
         <v>2.01857e-07</v>
@@ -4892,16 +4718,13 @@
         <v>-11176.69561498338</v>
       </c>
       <c r="Y10" t="n">
-        <v>394.3707398400769</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3400.063772847948</v>
+        <v>106.1840421479831</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.130406602422708e-06</v>
+        <v>1.709398969553669e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7519618202728146</v>
+        <v>0.9893026673017612</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4735,7 @@
         <v>94.82400000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>934.6908420437614</v>
+        <v>345.7958277195239</v>
       </c>
       <c r="D11" t="n">
         <v>2.01567e-07</v>
@@ -4945,16 +4768,13 @@
         <v>-11078.25843263301</v>
       </c>
       <c r="Y11" t="n">
-        <v>392.2629985923898</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3373.167806019072</v>
+        <v>106.7209446595753</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.190957564552214e-06</v>
+        <v>1.684817561746661e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.7844817338121756</v>
+        <v>0.9920540136619173</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4785,7 @@
         <v>94.07499999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>952.4440738697936</v>
+        <v>296.1850890080167</v>
       </c>
       <c r="D12" t="n">
         <v>2.01191e-07</v>
@@ -4998,16 +4818,13 @@
         <v>-11416.58527712284</v>
       </c>
       <c r="Y12" t="n">
-        <v>389.4832884581104</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3345.463254356214</v>
+        <v>146.6895071022695</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.44109590473631e-07</v>
+        <v>1.745290027028289e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8688694029003797</v>
+        <v>0.9999942643179299</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4835,7 @@
         <v>92.39700000000005</v>
       </c>
       <c r="C13" t="n">
-        <v>959.3848490096508</v>
+        <v>250.3042300308541</v>
       </c>
       <c r="D13" t="n">
         <v>2.00889e-07</v>
@@ -5051,16 +4868,13 @@
         <v>-11422.21325459859</v>
       </c>
       <c r="Y13" t="n">
-        <v>387.1864115939476</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3315.766509785056</v>
+        <v>194.7789831251841</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.085072054046103e-06</v>
+        <v>2.53535497224077e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.7928592603596168</v>
+        <v>0.9972749815273829</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4885,7 @@
         <v>91.89999999999998</v>
       </c>
       <c r="C14" t="n">
-        <v>1050.039145330683</v>
+        <v>247.2516486377238</v>
       </c>
       <c r="D14" t="n">
         <v>2.00738e-07</v>
@@ -5104,16 +4918,13 @@
         <v>-11779.8479738181</v>
       </c>
       <c r="Y14" t="n">
-        <v>391.6978607263177</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5379.752486957718</v>
+        <v>193.3906948219399</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.064923145243585e-06</v>
+        <v>2.501626091832477e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8489207620657759</v>
+        <v>0.9984621992971464</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4935,7 @@
         <v>89.77200000000005</v>
       </c>
       <c r="C15" t="n">
-        <v>1057.954116782328</v>
+        <v>243.3924905030906</v>
       </c>
       <c r="D15" t="n">
         <v>2.00478e-07</v>
@@ -5157,16 +4968,13 @@
         <v>-11687.95348266325</v>
       </c>
       <c r="Y15" t="n">
-        <v>387.3264559726508</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6582.322267194906</v>
+        <v>194.4493043914055</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.872510354953958e-07</v>
+        <v>2.553970966589171e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9999185374315883</v>
+        <v>0.9983528323525173</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4985,7 @@
         <v>85.26999999999998</v>
       </c>
       <c r="C16" t="n">
-        <v>861.8782044916696</v>
+        <v>241.2326834729534</v>
       </c>
       <c r="D16" t="n">
         <v>2.0028e-07</v>
@@ -5210,16 +5018,13 @@
         <v>-10906.62431198059</v>
       </c>
       <c r="Y16" t="n">
-        <v>395.0548991229824</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>215610645.3962327</v>
+        <v>200.2664959947423</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.698851289753131e-07</v>
+        <v>3.647022501887303e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9540178891906357</v>
+        <v>0.9767945277514558</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5035,7 @@
         <v>83.24000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>834.2765177376612</v>
+        <v>239.1019337615452</v>
       </c>
       <c r="D17" t="n">
         <v>2.0016e-07</v>
@@ -5263,16 +5068,13 @@
         <v>-10929.05680077098</v>
       </c>
       <c r="Y17" t="n">
-        <v>391.9623220307058</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>110429064.5540533</v>
+        <v>189.7759149989107</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.681525107923475e-07</v>
+        <v>2.463947899057909e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9548998996271583</v>
+        <v>0.9996841152128429</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5085,7 @@
         <v>83.59900000000005</v>
       </c>
       <c r="C18" t="n">
-        <v>951.1955742840935</v>
+        <v>236.5857016262562</v>
       </c>
       <c r="D18" t="n">
         <v>2.00064e-07</v>
@@ -5316,16 +5118,13 @@
         <v>-11299.12688764321</v>
       </c>
       <c r="Y18" t="n">
-        <v>388.9329620833877</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>424417102.6382215</v>
+        <v>188.9600261187884</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.664634351187337e-07</v>
+        <v>2.485259295776098e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9557804722578245</v>
+        <v>0.9997743089086573</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5135,7 @@
         <v>83.59100000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>1010.553686140195</v>
+        <v>233.8376048038061</v>
       </c>
       <c r="D19" t="n">
         <v>1.99927e-07</v>
@@ -5369,16 +5168,13 @@
         <v>-11597.27597952438</v>
       </c>
       <c r="Y19" t="n">
-        <v>385.8920534170926</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>421248590.2657109</v>
+        <v>200.4562127660792</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.654126478313937e-07</v>
+        <v>4.039635751343622e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9562841296332386</v>
+        <v>0.9742512614220549</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5185,7 @@
         <v>81.74299999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>941.8557749250386</v>
+        <v>231.6551658603199</v>
       </c>
       <c r="D20" t="n">
         <v>1.99843e-07</v>
@@ -5422,16 +5218,13 @@
         <v>-11485.19132452939</v>
       </c>
       <c r="Y20" t="n">
-        <v>382.817670241769</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>208983998.0971246</v>
+        <v>188.8403382541988</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.644063102284988e-07</v>
+        <v>2.587743735905604e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9568018018580203</v>
+        <v>0.9996354522295099</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5235,7 @@
         <v>78.03699999999998</v>
       </c>
       <c r="C21" t="n">
-        <v>853.5642724996794</v>
+        <v>78.03699999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.99763e-07</v>
@@ -5474,11 +5267,10 @@
       <c r="X21" t="n">
         <v>-11047.96890203932</v>
       </c>
-      <c r="Y21" t="n">
-        <v>379.7669731489552</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>414165340.4579787</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>2.632497046580194e-07</v>
@@ -5495,7 +5287,7 @@
         <v>80.00599999999997</v>
       </c>
       <c r="C22" t="n">
-        <v>1029.120076841184</v>
+        <v>80.00599999999997</v>
       </c>
       <c r="D22" t="n">
         <v>1.99554e-07</v>
@@ -5527,11 +5319,10 @@
       <c r="X22" t="n">
         <v>-11809.65080898267</v>
       </c>
-      <c r="Y22" t="n">
-        <v>376.7423984880032</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>308630477.7942852</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>2.615821687966625e-07</v>
@@ -5694,7 +5485,7 @@
         <v>220.98</v>
       </c>
       <c r="C2" t="n">
-        <v>1904.433037625111</v>
+        <v>371.22066097703</v>
       </c>
       <c r="D2" t="n">
         <v>2.21037e-07</v>
@@ -5727,16 +5518,13 @@
         <v>-5528.900488859498</v>
       </c>
       <c r="Y2" t="n">
-        <v>510.0230643160938</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>280240702.0054348</v>
+        <v>198.9476640510364</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.747730760022037e-07</v>
+        <v>1.969650335772923e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8551690128015379</v>
+        <v>0.9785424695443491</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5535,7 @@
         <v>163.473</v>
       </c>
       <c r="C3" t="n">
-        <v>996.9913703961288</v>
+        <v>427.3213367854112</v>
       </c>
       <c r="D3" t="n">
         <v>2.21752e-07</v>
@@ -5780,16 +5568,13 @@
         <v>-6517.297981851735</v>
       </c>
       <c r="Y3" t="n">
-        <v>482.4254909750563</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>805207626.7345194</v>
+        <v>114.6106386328538</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.462534064680492e-07</v>
+        <v>2.50222593508252e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8934832853792555</v>
+        <v>0.9446879424298011</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5585,7 @@
         <v>149.741</v>
       </c>
       <c r="C4" t="n">
-        <v>890.0957705495215</v>
+        <v>434.2212570188897</v>
       </c>
       <c r="D4" t="n">
         <v>2.17976e-07</v>
@@ -5833,16 +5618,13 @@
         <v>-7611.660186011932</v>
       </c>
       <c r="Y4" t="n">
-        <v>473.7800385816096</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>260510951.643348</v>
+        <v>97.4038305325449</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.942887961099986e-07</v>
+        <v>2.489679616551764e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9094445245033568</v>
+        <v>0.9437696428304067</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5635,7 @@
         <v>142.8869999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>882.8140134526209</v>
+        <v>350.241106507789</v>
       </c>
       <c r="D5" t="n">
         <v>2.14361e-07</v>
@@ -5886,16 +5668,13 @@
         <v>-8509.876928372587</v>
       </c>
       <c r="Y5" t="n">
-        <v>468.275077592011</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>128529960.5918365</v>
+        <v>172.3485381938929</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.631311019853731e-07</v>
+        <v>2.477175096361777e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9192954304947233</v>
+        <v>0.9710429086633239</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5685,7 @@
         <v>138.543</v>
       </c>
       <c r="C6" t="n">
-        <v>891.300559869536</v>
+        <v>340.3360962105041</v>
       </c>
       <c r="D6" t="n">
         <v>2.11582e-07</v>
@@ -5939,16 +5718,13 @@
         <v>-9225.697987366791</v>
       </c>
       <c r="Y6" t="n">
-        <v>463.1657707101388</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>190577286.1824888</v>
+        <v>175.4391744966847</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.433202917606022e-07</v>
+        <v>2.38726970407346e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9257882025619144</v>
+        <v>0.9771221840575662</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5735,7 @@
         <v>131.31</v>
       </c>
       <c r="C7" t="n">
-        <v>857.871850474132</v>
+        <v>131.31</v>
       </c>
       <c r="D7" t="n">
         <v>2.09581e-07</v>
@@ -5991,11 +5767,10 @@
       <c r="X7" t="n">
         <v>-9608.468929090981</v>
       </c>
-      <c r="Y7" t="n">
-        <v>458.1120111061471</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>754170482.2608846</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>3.28840568000323e-07</v>
@@ -6012,7 +5787,7 @@
         <v>129.036</v>
       </c>
       <c r="C8" t="n">
-        <v>888.3021999675426</v>
+        <v>327.8772699007665</v>
       </c>
       <c r="D8" t="n">
         <v>2.08005e-07</v>
@@ -6045,16 +5820,13 @@
         <v>-10257.96468520767</v>
       </c>
       <c r="Y8" t="n">
-        <v>453.0741271720851</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>496407696.4325032</v>
+        <v>175.553451858661</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.179195488138277e-07</v>
+        <v>2.247788787938579e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9348194406595822</v>
+        <v>0.9848625939994827</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5837,7 @@
         <v>123.597</v>
       </c>
       <c r="C9" t="n">
-        <v>860.9940512848052</v>
+        <v>319.317028124485</v>
       </c>
       <c r="D9" t="n">
         <v>2.06787e-07</v>
@@ -6098,16 +5870,13 @@
         <v>-10444.71707993587</v>
       </c>
       <c r="Y9" t="n">
-        <v>403.7724355794147</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>9304.183362649805</v>
+        <v>176.8628691801932</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.894594238925443e-07</v>
+        <v>2.183641595344833e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9998268003986831</v>
+        <v>0.9880675031526746</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5887,7 @@
         <v>119.544</v>
       </c>
       <c r="C10" t="n">
-        <v>883.8309674063028</v>
+        <v>119.544</v>
       </c>
       <c r="D10" t="n">
         <v>2.05925e-07</v>
@@ -6150,11 +5919,10 @@
       <c r="X10" t="n">
         <v>-10705.66882549406</v>
       </c>
-      <c r="Y10" t="n">
-        <v>443.4328412523989</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>485106620.7304722</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.037941546175563e-07</v>
@@ -6171,7 +5939,7 @@
         <v>117.968</v>
       </c>
       <c r="C11" t="n">
-        <v>910.5921661669329</v>
+        <v>314.0465075807097</v>
       </c>
       <c r="D11" t="n">
         <v>2.05354e-07</v>
@@ -6204,16 +5972,13 @@
         <v>-11014.7101948853</v>
       </c>
       <c r="Y11" t="n">
-        <v>438.9773628255097</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>720381305.7444178</v>
+        <v>171.2320208278514</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.994258849657866e-07</v>
+        <v>2.067476447721786e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9419561149497139</v>
+        <v>0.9934155857128242</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6135,7 @@
         <v>140.104</v>
       </c>
       <c r="C2" t="n">
-        <v>1311.711187679607</v>
+        <v>331.9453690944703</v>
       </c>
       <c r="D2" t="n">
         <v>2.2279e-07</v>
@@ -6403,16 +6168,13 @@
         <v>-6545.016377602506</v>
       </c>
       <c r="Y2" t="n">
-        <v>452.3508453541294</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>248183263.2253623</v>
+        <v>169.0538063906275</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.112824161963975e-07</v>
+        <v>2.083274834786174e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9065260216129608</v>
+        <v>0.9835771575405228</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6185,7 @@
         <v>120.864</v>
       </c>
       <c r="C3" t="n">
-        <v>970.8721880929106</v>
+        <v>322.77090983439</v>
       </c>
       <c r="D3" t="n">
         <v>2.1518e-07</v>
@@ -6456,16 +6218,13 @@
         <v>-8261.791834220494</v>
       </c>
       <c r="Y3" t="n">
-        <v>441.1915900308161</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>241859846.0119839</v>
+        <v>165.6173284118534</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.463548461689567e-07</v>
+        <v>2.128761204108913e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.927080734629527</v>
+        <v>0.9870562667077204</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6235,7 @@
         <v>116.357</v>
       </c>
       <c r="C4" t="n">
-        <v>944.4752410796528</v>
+        <v>116.357</v>
       </c>
       <c r="D4" t="n">
         <v>2.11094e-07</v>
@@ -6508,11 +6267,10 @@
       <c r="X4" t="n">
         <v>-9490.960038724663</v>
       </c>
-      <c r="Y4" t="n">
-        <v>436.3548310285325</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>119278596.0502252</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>3.208848820771064e-07</v>
@@ -6529,7 +6287,7 @@
         <v>111.87</v>
       </c>
       <c r="C5" t="n">
-        <v>917.7758371606658</v>
+        <v>304.8568558184012</v>
       </c>
       <c r="D5" t="n">
         <v>2.08667e-07</v>
@@ -6562,16 +6320,13 @@
         <v>-10121.65857072952</v>
       </c>
       <c r="Y5" t="n">
-        <v>432.4205249758801</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>118581029.3885973</v>
+        <v>172.6815246041655</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.079512572913859e-07</v>
+        <v>2.052326540001499e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9401622021827061</v>
+        <v>0.9962790779425826</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6337,7 @@
         <v>105.504</v>
       </c>
       <c r="C6" t="n">
-        <v>840.1363983239171</v>
+        <v>537.3412072643537</v>
       </c>
       <c r="D6" t="n">
         <v>2.07064e-07</v>
@@ -6615,16 +6370,13 @@
         <v>-10176.59073855654</v>
       </c>
       <c r="Y6" t="n">
-        <v>408.3964641392536</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7101.422942289118</v>
+        <v>0.5481291857062298</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.6379726903005e-07</v>
+        <v>2.798961166990494e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9947722685128367</v>
+        <v>0.7516743179826856</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6387,7 @@
         <v>107.727</v>
       </c>
       <c r="C7" t="n">
-        <v>1026.424484293624</v>
+        <v>394.2427383148049</v>
       </c>
       <c r="D7" t="n">
         <v>2.0586e-07</v>
@@ -6668,16 +6420,13 @@
         <v>-11045.04798626547</v>
       </c>
       <c r="Y7" t="n">
-        <v>401.966931862572</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3492.649307771641</v>
+        <v>74.75421991388968</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.058865907241843e-07</v>
+        <v>1.787294006794156e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9756267818283836</v>
+        <v>0.9726351742963568</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6437,7 @@
         <v>103.9040000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>971.3384242135835</v>
+        <v>331.9293083417847</v>
       </c>
       <c r="D8" t="n">
         <v>2.05e-07</v>
@@ -6721,16 +6470,13 @@
         <v>-10977.46229465216</v>
       </c>
       <c r="Y8" t="n">
-        <v>398.597674306599</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3459.703656614961</v>
+        <v>132.4076013847351</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.541397465901892e-06</v>
+        <v>1.842614087194141e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8219042449566987</v>
+        <v>0.9921836705262389</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6487,7 @@
         <v>99.25</v>
       </c>
       <c r="C9" t="n">
-        <v>889.4243373065341</v>
+        <v>325.7809631366728</v>
       </c>
       <c r="D9" t="n">
         <v>2.04506e-07</v>
@@ -6774,16 +6520,13 @@
         <v>-10924.74103120476</v>
       </c>
       <c r="Y9" t="n">
-        <v>403.8846045701454</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3428.99574492553</v>
+        <v>133.739579383694</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.308474421580248e-06</v>
+        <v>1.805996953443864e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7741987323164977</v>
+        <v>0.9947643057071957</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6537,7 @@
         <v>98.56200000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>946.2450047847452</v>
+        <v>409.8978970447143</v>
       </c>
       <c r="D10" t="n">
         <v>2.03863e-07</v>
@@ -6827,16 +6570,13 @@
         <v>-11256.99445885403</v>
       </c>
       <c r="Y10" t="n">
-        <v>395.6985124484585</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3402.37693829069</v>
+        <v>46.71983255614903</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.028570739946239e-06</v>
+        <v>1.650310747655999e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7921343136142551</v>
+        <v>0.9701824190617165</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6587,7 @@
         <v>96.94099999999997</v>
       </c>
       <c r="C11" t="n">
-        <v>977.3162770788132</v>
+        <v>348.0382745336089</v>
       </c>
       <c r="D11" t="n">
         <v>2.03384e-07</v>
@@ -6880,16 +6620,13 @@
         <v>-11388.270789623</v>
       </c>
       <c r="Y11" t="n">
-        <v>392.3154123634241</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3372.865831297919</v>
+        <v>104.6747309040696</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.186959869851276e-06</v>
+        <v>1.722758584939679e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.7851787481194796</v>
+        <v>0.989792371838589</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6637,7 @@
         <v>95.81400000000002</v>
       </c>
       <c r="C12" t="n">
-        <v>988.1727181371408</v>
+        <v>342.820656977598</v>
       </c>
       <c r="D12" t="n">
         <v>2.03217e-07</v>
@@ -6933,16 +6670,13 @@
         <v>-11587.93137669101</v>
       </c>
       <c r="Y12" t="n">
-        <v>389.145647422873</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3348.019978078831</v>
+        <v>106.228060412514</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.896212750669811e-07</v>
+        <v>1.703579233680836e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8744375434577657</v>
+        <v>0.9920498250199279</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6687,7 @@
         <v>84.37900000000002</v>
       </c>
       <c r="C13" t="n">
-        <v>739.324784816772</v>
+        <v>292.2330805506637</v>
       </c>
       <c r="D13" t="n">
         <v>2.02792e-07</v>
@@ -6986,16 +6720,13 @@
         <v>-9948.766866542572</v>
       </c>
       <c r="Y13" t="n">
-        <v>387.430774162167</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3322.767583093016</v>
+        <v>147.4454692789028</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.689040659125571e-06</v>
+        <v>1.770665649848497e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.761613722176729</v>
+        <v>0.9999941434639785</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6737,7 @@
         <v>87.34799999999996</v>
       </c>
       <c r="C14" t="n">
-        <v>749.1342183482767</v>
+        <v>87.34799999999996</v>
       </c>
       <c r="D14" t="n">
         <v>2.02749e-07</v>
@@ -7038,11 +6769,10 @@
       <c r="X14" t="n">
         <v>-10693.15704751849</v>
       </c>
-      <c r="Y14" t="n">
-        <v>385.2630321057063</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3298.72348165928</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>2.092965923134083e-06</v>
@@ -7059,7 +6789,7 @@
         <v>90.81100000000004</v>
       </c>
       <c r="C15" t="n">
-        <v>969.3735051407908</v>
+        <v>246.558088854887</v>
       </c>
       <c r="D15" t="n">
         <v>2.02581e-07</v>
@@ -7092,16 +6822,13 @@
         <v>-11615.39179086089</v>
       </c>
       <c r="Y15" t="n">
-        <v>387.811655867922</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6597.83021612438</v>
+        <v>190.9818858298107</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.87374654933605e-07</v>
+        <v>2.48386059858105e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9999185116922792</v>
+        <v>0.9985390196904563</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6839,7 @@
         <v>89.00400000000002</v>
       </c>
       <c r="C16" t="n">
-        <v>951.9399148035945</v>
+        <v>89.00400000000002</v>
       </c>
       <c r="D16" t="n">
         <v>2.02478e-07</v>
@@ -7144,11 +6871,10 @@
       <c r="X16" t="n">
         <v>-11609.43019424543</v>
       </c>
-      <c r="Y16" t="n">
-        <v>396.1033591762223</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>216015388.1743194</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>2.724884697611362e-07</v>
@@ -7165,7 +6891,7 @@
         <v>86.20400000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>905.6851992657395</v>
+        <v>241.26532961034</v>
       </c>
       <c r="D17" t="n">
         <v>2.02314e-07</v>
@@ -7198,16 +6924,13 @@
         <v>-11429.52742617746</v>
       </c>
       <c r="Y17" t="n">
-        <v>393.1878154747255</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>214757656.8707898</v>
+        <v>189.6551749359162</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.70843335055864e-07</v>
+        <v>2.506129714602157e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9549917941196892</v>
+        <v>0.9992126375826894</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6941,7 @@
         <v>79.41500000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>740.9742668842119</v>
+        <v>237.7887970917623</v>
       </c>
       <c r="D18" t="n">
         <v>2.02081e-07</v>
@@ -7251,16 +6974,13 @@
         <v>-10346.71251131366</v>
       </c>
       <c r="Y18" t="n">
-        <v>390.1497452323471</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>212996290.450841</v>
+        <v>197.2002547817569</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.699984214560284e-07</v>
+        <v>3.592610798131391e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9553067099821752</v>
+        <v>0.9781331708550061</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6991,7 @@
         <v>86.541</v>
       </c>
       <c r="C19" t="n">
-        <v>1078.400579727261</v>
+        <v>235.3860696663631</v>
       </c>
       <c r="D19" t="n">
         <v>2.02006e-07</v>
@@ -7304,16 +7024,13 @@
         <v>-12029.67002916425</v>
       </c>
       <c r="Y19" t="n">
-        <v>387.1222911284498</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>211564676.3490336</v>
+        <v>196.2718476846026</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.685623821567904e-07</v>
+        <v>3.563954965114094e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9560561345612519</v>
+        <v>0.9794825422117318</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +7041,7 @@
         <v>77.87</v>
       </c>
       <c r="C20" t="n">
-        <v>766.3644400935323</v>
+        <v>232.9165024560443</v>
       </c>
       <c r="D20" t="n">
         <v>2.01904e-07</v>
@@ -7357,16 +7074,13 @@
         <v>-10489.71513985551</v>
       </c>
       <c r="Y20" t="n">
-        <v>384.0414995523008</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>836933480.7986488</v>
+        <v>189.1236542405576</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.681501399578432e-07</v>
+        <v>2.598325460895175e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.956230592041715</v>
+        <v>0.9993746195947115</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7091,7 @@
         <v>80.19100000000003</v>
       </c>
       <c r="C21" t="n">
-        <v>859.9825047100417</v>
+        <v>230.4286899621536</v>
       </c>
       <c r="D21" t="n">
         <v>2.01896e-07</v>
@@ -7410,16 +7124,13 @@
         <v>-11335.91746104349</v>
       </c>
       <c r="Y21" t="n">
-        <v>381.0114202350169</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>158367121.1464663</v>
+        <v>196.785624058104</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.664095332736867e-07</v>
+        <v>3.197165927646515e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9572016161535086</v>
+        <v>0.993899567690085</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7141,7 @@
         <v>75.30499999999995</v>
       </c>
       <c r="C22" t="n">
-        <v>774.0441228870425</v>
+        <v>75.30499999999995</v>
       </c>
       <c r="D22" t="n">
         <v>2.01866e-07</v>
@@ -7462,11 +7173,10 @@
       <c r="X22" t="n">
         <v>-10590.83304695597</v>
       </c>
-      <c r="Y22" t="n">
-        <v>377.9163953705417</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>824009950.5852665</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>2.654781821075532e-07</v>
@@ -7629,7 +7339,7 @@
         <v>221.4800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2207.337456758381</v>
+        <v>368.6096082814205</v>
       </c>
       <c r="D2" t="n">
         <v>2.22512e-07</v>
@@ -7662,16 +7372,13 @@
         <v>-5603.649728868509</v>
       </c>
       <c r="Y2" t="n">
-        <v>510.3035093823291</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>560170766.6245534</v>
+        <v>200.6871210763598</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.747546682862158e-07</v>
+        <v>1.939781204984354e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8562031265119606</v>
+        <v>0.9799731114276149</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7389,7 @@
         <v>159.005</v>
       </c>
       <c r="C3" t="n">
-        <v>990.6278237908825</v>
+        <v>447.9416230442206</v>
       </c>
       <c r="D3" t="n">
         <v>2.22012e-07</v>
@@ -7715,16 +7422,13 @@
         <v>-6714.69197562406</v>
       </c>
       <c r="Y3" t="n">
-        <v>481.2660958168094</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>49650136.99958347</v>
+        <v>91.58709126933101</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.350575643664988e-07</v>
+        <v>2.347428301541757e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.897507102159935</v>
+        <v>0.9430690832150115</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7439,7 @@
         <v>142.913</v>
       </c>
       <c r="C4" t="n">
-        <v>845.3013265219539</v>
+        <v>359.6900030185662</v>
       </c>
       <c r="D4" t="n">
         <v>2.17361e-07</v>
@@ -7768,16 +7472,13 @@
         <v>-7842.536772160747</v>
       </c>
       <c r="Y4" t="n">
-        <v>472.8891771331856</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>28408239.65208392</v>
+        <v>168.6963487154129</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.804381518473373e-07</v>
+        <v>2.550427015889858e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9144283937340101</v>
+        <v>0.9660918865748274</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7489,7 @@
         <v>136.63</v>
       </c>
       <c r="C5" t="n">
-        <v>822.2570959623042</v>
+        <v>344.2215156393774</v>
       </c>
       <c r="D5" t="n">
         <v>2.13532e-07</v>
@@ -7821,16 +7522,13 @@
         <v>-8893.673459773989</v>
       </c>
       <c r="Y5" t="n">
-        <v>467.7896614165775</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>127512352.6531525</v>
+        <v>176.2111285711865</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.504288151220924e-07</v>
+        <v>2.45936575316767e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9241056821068518</v>
+        <v>0.9731068856418037</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7539,7 @@
         <v>135.7259999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>892.1915026291431</v>
+        <v>135.7259999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2.10868e-07</v>
@@ -7873,11 +7571,10 @@
       <c r="X6" t="n">
         <v>-10116.13588290864</v>
       </c>
-      <c r="Y6" t="n">
-        <v>463.0239290112445</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>381339097.4644856</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>3.319013594846779e-07</v>
@@ -7894,7 +7591,7 @@
         <v>129.151</v>
       </c>
       <c r="C7" t="n">
-        <v>867.2787028956334</v>
+        <v>330.6447826420469</v>
       </c>
       <c r="D7" t="n">
         <v>2.09044e-07</v>
@@ -7927,16 +7624,13 @@
         <v>-10551.99627331281</v>
       </c>
       <c r="Y7" t="n">
-        <v>458.0798676900543</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>188651834.3147243</v>
+        <v>178.5038667713485</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.191725725384624e-07</v>
+        <v>2.395015651612653e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9349918180524557</v>
+        <v>0.9796601808069511</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7641,7 @@
         <v>126.192</v>
       </c>
       <c r="C8" t="n">
-        <v>873.6647680699333</v>
+        <v>126.192</v>
       </c>
       <c r="D8" t="n">
         <v>2.07551e-07</v>
@@ -7979,11 +7673,10 @@
       <c r="X8" t="n">
         <v>-10865.60988569405</v>
       </c>
-      <c r="Y8" t="n">
-        <v>453.0595149208056</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>422324301.2284553</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>3.11056400521917e-07</v>
@@ -8000,7 +7693,7 @@
         <v>121.662</v>
       </c>
       <c r="C9" t="n">
-        <v>890.1579079359947</v>
+        <v>319.5027715640009</v>
       </c>
       <c r="D9" t="n">
         <v>2.06564e-07</v>
@@ -8033,16 +7726,13 @@
         <v>-11525.19590796948</v>
       </c>
       <c r="Y9" t="n">
-        <v>448.2523363095118</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>491171586.2060832</v>
+        <v>175.6986931830304</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.01938652258721e-07</v>
+        <v>2.156534570704438e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9415819661731251</v>
+        <v>0.988382338006209</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7743,7 @@
         <v>117.721</v>
       </c>
       <c r="C10" t="n">
-        <v>868.8881625183919</v>
+        <v>321.0284741146884</v>
       </c>
       <c r="D10" t="n">
         <v>2.05665e-07</v>
@@ -8086,16 +7776,13 @@
         <v>-11537.7280858147</v>
       </c>
       <c r="Y10" t="n">
-        <v>443.4853755438477</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>485784741.1051268</v>
+        <v>169.448840293537</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.974394904184702e-07</v>
+        <v>2.114776480616906e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9432194539486946</v>
+        <v>0.9896269837907006</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7793,7 @@
         <v>114.834</v>
       </c>
       <c r="C11" t="n">
-        <v>862.2437942575193</v>
+        <v>114.834</v>
       </c>
       <c r="D11" t="n">
         <v>2.05115e-07</v>
@@ -8138,11 +7825,10 @@
       <c r="X11" t="n">
         <v>-11766.05015049437</v>
       </c>
-      <c r="Y11" t="n">
-        <v>438.8706743763116</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>360109425.4336346</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>2.931007929726052e-07</v>
@@ -8305,7 +7991,7 @@
         <v>139.05</v>
       </c>
       <c r="C2" t="n">
-        <v>1301.278089571177</v>
+        <v>381.9785992760624</v>
       </c>
       <c r="D2" t="n">
         <v>2.22285e-07</v>
@@ -8338,16 +8024,13 @@
         <v>-6830.028950954207</v>
       </c>
       <c r="Y2" t="n">
-        <v>457.4997079118085</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>312612632.3179682</v>
+        <v>125.4826574409117</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.043693871259796e-07</v>
+        <v>2.069837255985361e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9087480537130986</v>
+        <v>0.9659470432720613</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +8041,7 @@
         <v>120.947</v>
       </c>
       <c r="C3" t="n">
-        <v>940.9387054219322</v>
+        <v>322.2103160215734</v>
       </c>
       <c r="D3" t="n">
         <v>2.1491e-07</v>
@@ -8391,16 +8074,13 @@
         <v>-8632.903832591566</v>
       </c>
       <c r="Y3" t="n">
-        <v>403.3609078212102</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9279.368412308988</v>
+        <v>172.5653558099628</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.675247436031156e-07</v>
+        <v>2.222710953717177e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9988156554213184</v>
+        <v>0.985043166607556</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8091,7 @@
         <v>115.583</v>
       </c>
       <c r="C4" t="n">
-        <v>912.9301190935128</v>
+        <v>311.4832923096353</v>
       </c>
       <c r="D4" t="n">
         <v>2.10827e-07</v>
@@ -8444,16 +8124,13 @@
         <v>-9838.498825688595</v>
       </c>
       <c r="Y4" t="n">
-        <v>441.7997160107934</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>362464404.8865823</v>
+        <v>177.4449824750121</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.181633620200979e-07</v>
+        <v>2.215973065123271e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9368092617042773</v>
+        <v>0.9894163861556823</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8141,7 @@
         <v>111.215</v>
       </c>
       <c r="C5" t="n">
-        <v>892.0217466808488</v>
+        <v>305.7681494253922</v>
       </c>
       <c r="D5" t="n">
         <v>2.08546e-07</v>
@@ -8497,16 +8174,13 @@
         <v>-10368.1116933688</v>
       </c>
       <c r="Y5" t="n">
-        <v>437.6099678784668</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>239907240.0106749</v>
+        <v>177.5158231448743</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.061414370027394e-07</v>
+        <v>2.083872427008064e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9409937211675136</v>
+        <v>0.9951843823306668</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8191,7 @@
         <v>108.997</v>
       </c>
       <c r="C6" t="n">
-        <v>942.8411032221029</v>
+        <v>307.1927008213704</v>
       </c>
       <c r="D6" t="n">
         <v>2.07034e-07</v>
@@ -8550,16 +8224,13 @@
         <v>-10926.86794640467</v>
       </c>
       <c r="Y6" t="n">
-        <v>413.9216791495396</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7181.639270335022</v>
+        <v>170.419685311101</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.801008221149333e-07</v>
+        <v>2.011412941479421e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9984205476257983</v>
+        <v>0.9962012267188957</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8241,7 @@
         <v>104.198</v>
       </c>
       <c r="C7" t="n">
-        <v>891.5610816888299</v>
+        <v>364.4671135981185</v>
       </c>
       <c r="D7" t="n">
         <v>2.06051e-07</v>
@@ -8603,16 +8274,13 @@
         <v>-11031.72547674831</v>
       </c>
       <c r="Y7" t="n">
-        <v>405.7518897540633</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3530.122982021144</v>
+        <v>108.7853540336899</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.746351472270337e-06</v>
+        <v>1.863387372075352e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8405277647447856</v>
+        <v>0.9783801099203739</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8291,7 @@
         <v>102.777</v>
       </c>
       <c r="C8" t="n">
-        <v>929.0049420155005</v>
+        <v>102.777</v>
       </c>
       <c r="D8" t="n">
         <v>2.05404e-07</v>
@@ -8655,11 +8323,10 @@
       <c r="X8" t="n">
         <v>-11395.35855692168</v>
       </c>
-      <c r="Y8" t="n">
-        <v>407.5285837146329</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3497.19075329124</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>2.435726347952618e-06</v>
@@ -8676,7 +8343,7 @@
         <v>99.59099999999995</v>
       </c>
       <c r="C9" t="n">
-        <v>904.679120761935</v>
+        <v>330.4095268850262</v>
       </c>
       <c r="D9" t="n">
         <v>2.04961e-07</v>
@@ -8709,16 +8376,13 @@
         <v>-11315.45057022371</v>
       </c>
       <c r="Y9" t="n">
-        <v>412.6356352748284</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3466.283946499125</v>
+        <v>133.5833325394963</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.559443951561254e-07</v>
+        <v>1.825112794119669e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9792420809295083</v>
+        <v>0.9925577269345046</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8393,7 @@
         <v>97.113</v>
       </c>
       <c r="C10" t="n">
-        <v>897.925211109319</v>
+        <v>325.2429445117943</v>
       </c>
       <c r="D10" t="n">
         <v>2.0466e-07</v>
@@ -8762,16 +8426,13 @@
         <v>-11341.20189378039</v>
       </c>
       <c r="Y10" t="n">
-        <v>398.0667829807337</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3436.279317545162</v>
+        <v>134.7318008756691</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.445688758224025e-06</v>
+        <v>1.810846377635226e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7797991419828746</v>
+        <v>0.9945528675275557</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8443,7 @@
         <v>94.43000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>886.8729762132493</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.04342e-07</v>
@@ -8814,11 +8475,10 @@
       <c r="X11" t="n">
         <v>-11416.13996383517</v>
       </c>
-      <c r="Y11" t="n">
-        <v>397.396766860261</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3404.429639909844</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.910935847238245e-06</v>
@@ -8835,7 +8495,7 @@
         <v>95.286</v>
       </c>
       <c r="C12" t="n">
-        <v>1020.13372924156</v>
+        <v>95.286</v>
       </c>
       <c r="D12" t="n">
         <v>2.03987e-07</v>
@@ -8867,11 +8527,10 @@
       <c r="X12" t="n">
         <v>-12062.4157865</v>
       </c>
-      <c r="Y12" t="n">
-        <v>393.4547150869861</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3376.897137777153</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>2.316767111265437e-06</v>
@@ -8888,7 +8547,7 @@
         <v>92.65300000000002</v>
       </c>
       <c r="C13" t="n">
-        <v>1029.415627428931</v>
+        <v>92.65300000000002</v>
       </c>
       <c r="D13" t="n">
         <v>2.04002e-07</v>
@@ -8920,11 +8579,10 @@
       <c r="X13" t="n">
         <v>-11996.18885363217</v>
       </c>
-      <c r="Y13" t="n">
-        <v>391.0891370872379</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3350.051935983317</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>2.047276587104414e-06</v>
@@ -8941,7 +8599,7 @@
         <v>90.47900000000004</v>
       </c>
       <c r="C14" t="n">
-        <v>948.9749746057703</v>
+        <v>90.47900000000004</v>
       </c>
       <c r="D14" t="n">
         <v>2.03873e-07</v>
@@ -8973,11 +8631,10 @@
       <c r="X14" t="n">
         <v>-11820.66809178136</v>
       </c>
-      <c r="Y14" t="n">
-        <v>393.6635995248881</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6693.224436311711</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>3.734491907564514e-07</v>
@@ -8994,7 +8651,7 @@
         <v>87.19799999999998</v>
       </c>
       <c r="C15" t="n">
-        <v>870.2405892861819</v>
+        <v>87.19799999999998</v>
       </c>
       <c r="D15" t="n">
         <v>2.03755e-07</v>
@@ -9026,11 +8683,10 @@
       <c r="X15" t="n">
         <v>-11618.53853203202</v>
       </c>
-      <c r="Y15" t="n">
-        <v>401.7714964571455</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>110136818.9024218</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>2.738074642512763e-07</v>
@@ -9047,7 +8703,7 @@
         <v>86.45800000000003</v>
       </c>
       <c r="C16" t="n">
-        <v>946.553467888187</v>
+        <v>243.6886181559918</v>
       </c>
       <c r="D16" t="n">
         <v>2.03504e-07</v>
@@ -9080,16 +8736,13 @@
         <v>-11837.10365352957</v>
       </c>
       <c r="Y16" t="n">
-        <v>398.604764654611</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>217461088.2834669</v>
+        <v>195.6426207860939</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.724765264228142e-07</v>
+        <v>2.53195639452743e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9549944994411119</v>
+        <v>0.9999308486211247</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8753,7 @@
         <v>86.70999999999998</v>
       </c>
       <c r="C17" t="n">
-        <v>999.294908602044</v>
+        <v>240.1538023655772</v>
       </c>
       <c r="D17" t="n">
         <v>2.03351e-07</v>
@@ -9133,16 +8786,13 @@
         <v>-11856.62252356277</v>
       </c>
       <c r="Y17" t="n">
-        <v>395.4786579321065</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>218565100.2905012</v>
+        <v>192.375573573078</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.717446277148552e-07</v>
+        <v>2.499101839320083e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9553056574385524</v>
+        <v>0.9992854198412028</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8803,7 @@
         <v>83.69299999999998</v>
       </c>
       <c r="C18" t="n">
-        <v>927.7786660360786</v>
+        <v>236.6991322358573</v>
       </c>
       <c r="D18" t="n">
         <v>2.03396e-07</v>
@@ -9186,16 +8836,13 @@
         <v>-11709.90918424021</v>
       </c>
       <c r="Y18" t="n">
-        <v>392.3821265747468</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>320922055.6702399</v>
+        <v>198.9929226894102</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.706710776409562e-07</v>
+        <v>3.512304410336217e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9559371910029408</v>
+        <v>0.979658616999567</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8853,7 @@
         <v>81.37099999999998</v>
       </c>
       <c r="C19" t="n">
-        <v>913.4185454055532</v>
+        <v>234.1877135482524</v>
       </c>
       <c r="D19" t="n">
         <v>2.03227e-07</v>
@@ -9239,16 +8886,13 @@
         <v>-11602.87499830767</v>
       </c>
       <c r="Y19" t="n">
-        <v>389.2297349092733</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>424392238.0302437</v>
+        <v>198.4149181187792</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.695351437307313e-07</v>
+        <v>3.518960516405787e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9564556629632146</v>
+        <v>0.9804027952215804</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8903,7 @@
         <v>81.685</v>
       </c>
       <c r="C20" t="n">
-        <v>1024.555840843728</v>
+        <v>232.0906815017022</v>
       </c>
       <c r="D20" t="n">
         <v>2.03251e-07</v>
@@ -9292,16 +8936,13 @@
         <v>-12183.94804322583</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.1861154748777</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>423121026.1880721</v>
+        <v>196.5883079525884</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.674479118209682e-07</v>
+        <v>3.447014762662984e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9576380706450214</v>
+        <v>0.9823369487468016</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8953,7 @@
         <v>80.19</v>
       </c>
       <c r="C21" t="n">
-        <v>1008.101025040324</v>
+        <v>229.2060797084101</v>
       </c>
       <c r="D21" t="n">
         <v>2.03131e-07</v>
@@ -9345,16 +8986,13 @@
         <v>-11829.63864477345</v>
       </c>
       <c r="Y21" t="n">
-        <v>383.0878902717469</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1043691509.916825</v>
+        <v>192.2427682472158</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.6718394981589e-07</v>
+        <v>2.696717715188143e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9577174277947021</v>
+        <v>0.9992319221585318</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +9003,7 @@
         <v>78.18800000000005</v>
       </c>
       <c r="C22" t="n">
-        <v>943.1910877447787</v>
+        <v>78.18800000000005</v>
       </c>
       <c r="D22" t="n">
         <v>2.03144e-07</v>
@@ -9397,11 +9035,10 @@
       <c r="X22" t="n">
         <v>-11793.20759591702</v>
       </c>
-      <c r="Y22" t="n">
-        <v>379.979431224596</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>104725804.1511465</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>2.660548930483863e-07</v>
@@ -9564,7 +9201,7 @@
         <v>214.316</v>
       </c>
       <c r="C2" t="n">
-        <v>2775.420309901368</v>
+        <v>560.8787060277713</v>
       </c>
       <c r="D2" t="n">
         <v>2.17122e-07</v>
@@ -9597,16 +9234,13 @@
         <v>-6202.506470869546</v>
       </c>
       <c r="Y2" t="n">
-        <v>496.4300008690061</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>270503285.953953</v>
+        <v>0.5841874448926816</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.971412741518568e-07</v>
+        <v>1.870857934015208e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8741619200281474</v>
+        <v>0.9290384478740646</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9251,7 @@
         <v>148.211</v>
       </c>
       <c r="C3" t="n">
-        <v>1077.194128102726</v>
+        <v>399.0360522010185</v>
       </c>
       <c r="D3" t="n">
         <v>2.13894e-07</v>
@@ -9650,16 +9284,13 @@
         <v>-8055.542724286479</v>
       </c>
       <c r="Y3" t="n">
-        <v>462.2924872699581</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>386408749.5787792</v>
+        <v>115.8061394859474</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.696957143001951e-07</v>
+        <v>2.117194039701654e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9163403427526926</v>
+        <v>0.9628110834102601</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9301,7 @@
         <v>132.58</v>
       </c>
       <c r="C4" t="n">
-        <v>916.0761083864587</v>
+        <v>327.0512683838844</v>
       </c>
       <c r="D4" t="n">
         <v>2.0923e-07</v>
@@ -9703,16 +9334,13 @@
         <v>-9600.724840700765</v>
       </c>
       <c r="Y4" t="n">
-        <v>452.7040384209214</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>372439264.3355919</v>
+        <v>175.918851135965</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.284121272966834e-07</v>
+        <v>2.275352162100322e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9308259589892216</v>
+        <v>0.983853259658795</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9351,7 @@
         <v>127.028</v>
       </c>
       <c r="C5" t="n">
-        <v>901.2275125754859</v>
+        <v>321.6853875223459</v>
       </c>
       <c r="D5" t="n">
         <v>2.06293e-07</v>
@@ -9756,16 +9384,13 @@
         <v>-10692.07200967175</v>
       </c>
       <c r="Y5" t="n">
-        <v>446.8893871986931</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>443629263.2080497</v>
+        <v>173.1704750586732</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.097473312523191e-07</v>
+        <v>2.13385788589463e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9375291038585979</v>
+        <v>0.9892575836647314</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9401,7 @@
         <v>121.155</v>
       </c>
       <c r="C6" t="n">
-        <v>858.9891546676095</v>
+        <v>317.1148830754445</v>
       </c>
       <c r="D6" t="n">
         <v>2.04438e-07</v>
@@ -9809,16 +9434,13 @@
         <v>-11363.75009103374</v>
       </c>
       <c r="Y6" t="n">
-        <v>441.2957596951944</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>120762018.9660457</v>
+        <v>170.421549226897</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.973416487429197e-07</v>
+        <v>2.051362902344458e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9423403938295931</v>
+        <v>0.9926993224055367</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9451,7 @@
         <v>119.134</v>
       </c>
       <c r="C7" t="n">
-        <v>956.9288693922011</v>
+        <v>119.134</v>
       </c>
       <c r="D7" t="n">
         <v>2.03261e-07</v>
@@ -9861,11 +9483,10 @@
       <c r="X7" t="n">
         <v>-11997.67667630151</v>
       </c>
-      <c r="Y7" t="n">
-        <v>399.5036448819612</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5394.212979040413</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>9.208391941885388e-07</v>
@@ -9882,7 +9503,7 @@
         <v>111.013</v>
       </c>
       <c r="C8" t="n">
-        <v>842.1176910828918</v>
+        <v>111.013</v>
       </c>
       <c r="D8" t="n">
         <v>2.026e-07</v>
@@ -9914,11 +9535,10 @@
       <c r="X8" t="n">
         <v>-11557.95890420135</v>
       </c>
-      <c r="Y8" t="n">
-        <v>429.3846945898102</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>469373915.0184879</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>2.853134075543249e-07</v>
@@ -9935,7 +9555,7 @@
         <v>108.872</v>
       </c>
       <c r="C9" t="n">
-        <v>873.6671160294553</v>
+        <v>108.872</v>
       </c>
       <c r="D9" t="n">
         <v>2.02286e-07</v>
@@ -9967,11 +9587,10 @@
       <c r="X9" t="n">
         <v>-11937.19550199226</v>
       </c>
-      <c r="Y9" t="n">
-        <v>401.5191020089013</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3481.605398927772</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>4.721666061233418e-07</v>
@@ -9988,7 +9607,7 @@
         <v>104.855</v>
       </c>
       <c r="C10" t="n">
-        <v>858.9780063961674</v>
+        <v>333.9475304297176</v>
       </c>
       <c r="D10" t="n">
         <v>2.01866e-07</v>
@@ -10021,16 +9640,13 @@
         <v>-12032.78076299674</v>
       </c>
       <c r="Y10" t="n">
-        <v>400.259534994683</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3438.919964037749</v>
+        <v>127.2049193323063</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.928901445658376e-06</v>
+        <v>1.780616682596537e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7696462191807913</v>
+        <v>0.9934762938908093</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9657,7 @@
         <v>102.53</v>
       </c>
       <c r="C11" t="n">
-        <v>896.2470671650833</v>
+        <v>328.8673424194193</v>
       </c>
       <c r="D11" t="n">
         <v>2.01751e-07</v>
@@ -10074,16 +9690,13 @@
         <v>-12231.93795227585</v>
       </c>
       <c r="Y11" t="n">
-        <v>393.1229108155648</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3401.468041000346</v>
+        <v>126.9310374215676</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.658440801982039e-06</v>
+        <v>1.752981684906989e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.7879378883207873</v>
+        <v>0.995907963184242</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 56.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1684,6 +1684,566 @@
         <v>1.02322983282711e-06</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.8546244248852769</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>138.501</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>932.2444440402812</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.95684e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-83.229</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3208127548787971</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.073190683722449</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.877088444242726</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.234522444400748</v>
+      </c>
+      <c r="L22" t="n">
+        <v>20.31029355783512</v>
+      </c>
+      <c r="M22" t="n">
+        <v>86.59898046193919</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>16.82685717222788</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-8917.560906360937</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-341.0237266246452</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.438600227885863e-07</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9994679136179709</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>129.59</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9356611143601847</v>
+      </c>
+      <c r="D23" t="n">
+        <v>887.2145484317082</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9516973301407765</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.93942e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-83.654</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1231714171600944</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7130234854191176</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.702595518853785</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.885321865869633</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22.50477610680859</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.84187794720729</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>18.12398063236787</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-9369.249437810791</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-315.249199843495</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.78915101036418e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9999204281533011</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>123.381</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8908311131327572</v>
+      </c>
+      <c r="D24" t="n">
+        <v>901.5674164162446</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9670933650287208</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.93022e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.976</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1753272424821282</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8738414020778685</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.865122512914454</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.18940407417868</v>
+      </c>
+      <c r="L24" t="n">
+        <v>24.74606660616811</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.07381138958991</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>19.56331713381845</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9930.846499784375</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-337.4557782207683</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.802709651195645e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9998357885914216</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>118.954</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8588674450003969</v>
+      </c>
+      <c r="D25" t="n">
+        <v>985.6109480995178</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.057245183278272</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.92323e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.145</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3648508373970669</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.039597550228843</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.885255374837915</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.21940974697796</v>
+      </c>
+      <c r="L25" t="n">
+        <v>25.78714942178529</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.22672167315558</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>20.64380885308847</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10328.32300117538</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-418.5331650137493</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.818973701837098e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9411084336405583</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>114.227</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8247377275254331</v>
+      </c>
+      <c r="D26" t="n">
+        <v>992.8405347253259</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.065000216490887</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.91832e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.27500000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4321565143512269</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.023357505890349</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.955316327773355</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.182214669039217</v>
+      </c>
+      <c r="L26" t="n">
+        <v>26.37599565327824</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.29904299341725</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>21.19742428818224</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10436.23635366751</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-433.4291945441255</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.615074796157945e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.99486852195708</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>110.023</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7943841560710753</v>
+      </c>
+      <c r="D27" t="n">
+        <v>386.1596275422525</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.414225721602227</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.91547e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.476</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3172675111350877</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.157184541831332</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.217424748782278</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.717595493427388</v>
+      </c>
+      <c r="L27" t="n">
+        <v>28.8774494467614</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.43089619523025</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>22.28690615880484</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10820.7482676827</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>87.60670069901001</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.622799823850319e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9846372485145306</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7483700478696905</v>
+      </c>
+      <c r="D28" t="n">
+        <v>923.2332650251616</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9903338882063316</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.91229e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.533</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.771941403216189</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.822827469753552</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.256847868231681</v>
+      </c>
+      <c r="L28" t="n">
+        <v>28.61904033384828</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.36127043195773</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>21.69804211984916</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10337.40422219515</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-387.0054111838755</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.757651812312542e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9997968082972996</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>104.213</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7524350004693107</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1005.593235489714</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.078679783954029</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.91113e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2723414596402358</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.171441207398501</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.994259193936862</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.67011912879991</v>
+      </c>
+      <c r="L29" t="n">
+        <v>30.16440290734911</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.54139385253745</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>23.28986623510717</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-11034.89805168537</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-464.3942318570803</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.674240548518478e-06</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.796426022002927</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>103.201</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7451281940202593</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1036.927648553564</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.112291583159878</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.90915e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.752</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6357019505659253</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.547274509438579</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.058392608206847</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.571404123191046</v>
+      </c>
+      <c r="L30" t="n">
+        <v>30.65718330154114</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.62724237395334</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>24.13353190833924</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-11342.23762260074</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-496.4913587260029</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.34341227999384e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9473352648101334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99.61799999999999</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7192583447050922</v>
+      </c>
+      <c r="D31" t="n">
+        <v>980.111467953377</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.051346000739509</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.90844e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.788</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3736837694569778</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.072550711670762</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.991903264101188</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.516652578434989</v>
+      </c>
+      <c r="L31" t="n">
+        <v>30.71783060294778</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.60634959575397</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>23.92264229159832</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-11101.29796171167</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-451.8924576017179</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.02322983282711e-06</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.8546244248852769</v>
       </c>
     </row>
@@ -1698,7 +2258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4192,6 +4752,1182 @@
         <v>2.583546293951973e-07</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.9602034087251805</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>141.597</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>322.2581138380917</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.01573e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-84.004</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1973444488350379</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.7450374900498935</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.630163528485135</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.004800302825428</v>
+      </c>
+      <c r="L44" t="n">
+        <v>30.15869574676302</v>
+      </c>
+      <c r="M44" t="n">
+        <v>87.32876199545412</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>21.43360519357709</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-11454.311163739</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>182.3820021625344</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.813575367725489e-09</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.9995179416494323</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>119.287</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.8424401646927547</v>
+      </c>
+      <c r="D45" t="n">
+        <v>917.2049107709742</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.846180969183586</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.01753e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-84.39700000000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.2669793922304137</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.996773199233175</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.9093100171525</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.356563851811438</v>
+      </c>
+      <c r="L45" t="n">
+        <v>33.34009071916551</v>
+      </c>
+      <c r="M45" t="n">
+        <v>87.58173862750681</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>23.67889340159697</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-11972.29840595214</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-357.4058297380253</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.872969470109779e-07</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.9455210549081215</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>112.807</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.7966764832588263</v>
+      </c>
+      <c r="D46" t="n">
+        <v>917.034612815124</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.845652517149215</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.01569e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-84.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.2008975940625089</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.142305461833156</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.743142955932948</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.169077616921518</v>
+      </c>
+      <c r="L46" t="n">
+        <v>33.25341463845149</v>
+      </c>
+      <c r="M46" t="n">
+        <v>87.68526055021523</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>24.73911456287036</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-12293.22524157472</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-368.1328731087483</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.833385558037288e-07</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.9475143334988627</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>108.606</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.7670077755884659</v>
+      </c>
+      <c r="D47" t="n">
+        <v>861.665587922037</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.673836750484282</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.01135e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.2214127413421912</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.9873065204646287</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.714687729024932</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.169189576661888</v>
+      </c>
+      <c r="L47" t="n">
+        <v>34.0357884436017</v>
+      </c>
+      <c r="M47" t="n">
+        <v>87.70455818397799</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>24.94732026064058</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-12220.46556277548</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-326.6139761551484</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>4.397371370064106e-07</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.9529945128565545</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>107.688</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.7605245873853264</v>
+      </c>
+      <c r="D48" t="n">
+        <v>942.8189656319264</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.92566401014069</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.00886e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.70699999999999</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.538483946385534</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.337492807460235</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.316388193132781</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4.050052934375221</v>
+      </c>
+      <c r="L48" t="n">
+        <v>36.42125127999422</v>
+      </c>
+      <c r="M48" t="n">
+        <v>87.85913255689807</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>26.75042426324197</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-13032.51340970559</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-402.299540973466</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.883231697752806e-06</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8258834609808883</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>104.328</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7367952710862518</v>
+      </c>
+      <c r="D49" t="n">
+        <v>923.4995510644528</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.865713884021662</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.00712e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.732</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.4768385044457272</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.236902936544507</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.888587925159335</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.432730300854617</v>
+      </c>
+      <c r="L49" t="n">
+        <v>34.88413502844951</v>
+      </c>
+      <c r="M49" t="n">
+        <v>87.83021175901268</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>26.39353734569671</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-12696.37825638546</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-390.5002811570503</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.832195786694801e-06</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.7498059072504979</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101.577</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7173668933663849</v>
+      </c>
+      <c r="D50" t="n">
+        <v>928.969868938971</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.882688841795004</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.00704e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.816</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3555475116455878</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.156112556268354</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.180534955360806</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.294954640284571</v>
+      </c>
+      <c r="L50" t="n">
+        <v>36.00464037839883</v>
+      </c>
+      <c r="M50" t="n">
+        <v>87.87954763265597</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>27.00820800647183</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-12867.18162016381</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-399.6879225700768</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.436075765014825e-06</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.7459538723595734</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>100.219</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7077762946955092</v>
+      </c>
+      <c r="D51" t="n">
+        <v>977.1536705501708</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3.032208123209926</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.00308e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.82599999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.6815285601655351</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.369749149690351</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.291140218530405</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.654963697958912</v>
+      </c>
+      <c r="L51" t="n">
+        <v>35.82657295016472</v>
+      </c>
+      <c r="M51" t="n">
+        <v>87.89616406398055</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>27.22171727486583</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-12859.53640128036</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-446.4364546043653</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>2.042168233436052e-06</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.7916368027510712</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>95.584</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.6750425503365185</v>
+      </c>
+      <c r="D52" t="n">
+        <v>904.8934783301078</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.8079773308198</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.00132e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.895</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.3220914925148843</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.018200756246153</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.212228721164762</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.634529431393978</v>
+      </c>
+      <c r="L52" t="n">
+        <v>36.50354400646423</v>
+      </c>
+      <c r="M52" t="n">
+        <v>87.85680783890082</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>26.72138107005438</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-12442.84112008396</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-387.9588470896278</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.163559562718493e-06</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.7869633325249612</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>95.19200000000001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.6722741301016266</v>
+      </c>
+      <c r="D53" t="n">
+        <v>919.4242670716477</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.853067859553051</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.00153e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.94799999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.4140890652588683</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.048196960216098</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.178056140698877</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.768079421076786</v>
+      </c>
+      <c r="L53" t="n">
+        <v>36.96248592113697</v>
+      </c>
+      <c r="M53" t="n">
+        <v>87.92552157173371</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>27.60729638093326</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-12767.12813026552</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-404.6745544345663</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2.207869693961968e-06</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.7810813294218094</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>93.88599999999997</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6630507708496648</v>
+      </c>
+      <c r="D54" t="n">
+        <v>995.6747099243854</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.089680809168487</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.00104e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-85.002</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.3818977973897687</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.285837919843958</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.131334312531441</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.571764856366669</v>
+      </c>
+      <c r="L54" t="n">
+        <v>36.89826129426142</v>
+      </c>
+      <c r="M54" t="n">
+        <v>87.97173264315612</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>28.23683169947766</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-12949.64916619227</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-475.7097490827675</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.052067875112602e-06</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.795707823975795</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92.255</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6515321652294894</v>
+      </c>
+      <c r="D55" t="n">
+        <v>986.9202958202471</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3.062514963753849</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.0007e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-85.023</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5719288948432788</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.226464275904343</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.180517210987698</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.117896929490184</v>
+      </c>
+      <c r="L55" t="n">
+        <v>37.32525620129778</v>
+      </c>
+      <c r="M55" t="n">
+        <v>87.96799672088163</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>28.18487367697258</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-12800.42298278033</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-472.317580531778</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.086245210894876e-06</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8461773584740592</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>89.22300000000001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6301192821881821</v>
+      </c>
+      <c r="D56" t="n">
+        <v>943.9417919169539</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.929148255336737</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.00008e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-85.05500000000001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1671338949635031</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.109456345501684</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.854168367762323</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.587545724580339</v>
+      </c>
+      <c r="L56" t="n">
+        <v>36.41396014280187</v>
+      </c>
+      <c r="M56" t="n">
+        <v>87.94510256937021</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>27.87059365664241</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-12513.05546288944</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-438.5156870576092</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.80176729512535e-07</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.9994292745609792</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87.88100000000003</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6206416802615877</v>
+      </c>
+      <c r="D57" t="n">
+        <v>957.8390859648543</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.972272985021224</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.99847e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-85.129</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.5522716539548969</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.8756803119590779</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.822040944279355</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.267424899597334</v>
+      </c>
+      <c r="L57" t="n">
+        <v>37.40476728743956</v>
+      </c>
+      <c r="M57" t="n">
+        <v>87.98725928861322</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>28.454837107926</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-12665.15693548672</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-454.7470903889841</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>2.641568219533586e-07</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.9569485877414382</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>87.47899999999998</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6178026370615196</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1056.940675821216</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.279795388960299</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.99828e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-85.151</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.5821713873484994</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.515801907208131</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.608937138086306</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4.254066757998615</v>
+      </c>
+      <c r="L58" t="n">
+        <v>38.0757470789155</v>
+      </c>
+      <c r="M58" t="n">
+        <v>88.03368550909551</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>29.12722468905563</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-12882.958399677</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-545.5167120319664</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.636242338467464e-07</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.9572436146272094</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>83.63200000000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.5906339823583834</v>
+      </c>
+      <c r="D59" t="n">
+        <v>995.1836030438914</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3.088156854116913</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.99709e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-85.16800000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1331185763013006</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.9276342485835093</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.875408226955208</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.28334969042427</v>
+      </c>
+      <c r="L59" t="n">
+        <v>36.66507694654916</v>
+      </c>
+      <c r="M59" t="n">
+        <v>87.95778491032624</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>28.04382062056042</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-12228.12304005591</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-494.7326169149741</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.629495894298315e-07</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.9575580020846242</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>82.82799999999997</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.5849558959582476</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1034.230833365146</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3.209324417149548</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.99687e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-85.238</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.2704190300572111</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.9399521303582564</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.989830441980188</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.742935163026497</v>
+      </c>
+      <c r="L60" t="n">
+        <v>38.08565181491034</v>
+      </c>
+      <c r="M60" t="n">
+        <v>88.01332091202561</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>28.82841819886061</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-12471.71380696104</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-533.1035750656689</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.615101207613322e-07</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.9583742811641953</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>82.50600000000003</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.5826818364795867</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1022.73486744237</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3.173651255081233</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.99669e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-85.29900000000001</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.4606534340731671</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.14839136197544</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.179031513525538</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.692117001731308</v>
+      </c>
+      <c r="L61" t="n">
+        <v>38.8640899585908</v>
+      </c>
+      <c r="M61" t="n">
+        <v>88.08313119401684</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>29.87914510773695</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-12841.97133392083</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-526.7314848194709</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>2.602481999857752e-07</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.9590930828932677</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>81.18900000000002</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.5733807919659317</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1061.98147718144</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3.29543751290929</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.99708e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-85.328</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.4698725138888062</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.281375745596727</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.009875500980757</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.651785864586149</v>
+      </c>
+      <c r="L62" t="n">
+        <v>38.65888997638589</v>
+      </c>
+      <c r="M62" t="n">
+        <v>88.08689395371252</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>29.93795622124546</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-12743.90095813156</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-564.612838516999</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.596409672831079e-07</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.9594810691287596</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78.11099999999999</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5516430432848154</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1036.267616694573</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3.215644764852105</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.9952e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-85.331</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1379497959015523</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.9096311074646574</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.024270725708462</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.886034037267473</v>
+      </c>
+      <c r="L63" t="n">
+        <v>38.25152479647706</v>
+      </c>
+      <c r="M63" t="n">
+        <v>88.02856032291847</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>29.05144256795678</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-12207.67305997291</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-545.8758272455912</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.59198318755664e-07</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.9596183020566957</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>77.51800000000003</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.5474551014498897</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1422.012981121247</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4.412652219008805</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.99644e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-85.38200000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.2874436474306723</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.9406848639163014</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.930238840130045</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.456310670646253</v>
+      </c>
+      <c r="L64" t="n">
+        <v>38.46050775793957</v>
+      </c>
+      <c r="M64" t="n">
+        <v>88.07628340723382</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>29.77270581049706</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-12408.9306361771</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-889.3027011291235</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.583546293951973e-07</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.9602034087251805</v>
       </c>
     </row>
@@ -4206,7 +5942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6700,6 +8436,1182 @@
         <v>2.508632464002284e-07</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.9581466573941858</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>144.443</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>359.1033787925725</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.00357e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-82.938</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.4200011734694252</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9940472693558702</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.746159550582137</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.223935769902778</v>
+      </c>
+      <c r="L44" t="n">
+        <v>19.43501072245498</v>
+      </c>
+      <c r="M44" t="n">
+        <v>86.38020420064518</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>15.80739154497107</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-8443.835225751443</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>145.4585126435157</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.714470066815772e-09</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.9912215692609548</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>122.482</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.847960787300181</v>
+      </c>
+      <c r="D45" t="n">
+        <v>950.0318337200471</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.645566401837756</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.97585e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-83.81999999999999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.2610396645436801</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9536879091524775</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.79275854437065</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.387927028194629</v>
+      </c>
+      <c r="L45" t="n">
+        <v>24.36001526537238</v>
+      </c>
+      <c r="M45" t="n">
+        <v>87.01377844719572</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>19.16933793413983</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-9732.232477525022</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-381.8854485978243</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.978991088999044e-07</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.9368204391709387</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>116.396</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8058265198036594</v>
+      </c>
+      <c r="D46" t="n">
+        <v>406.3500374276892</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.13156840460253</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.95816e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-84.15900000000001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1470599752502239</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.8098500558071156</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.77566232502651</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.967191458864904</v>
+      </c>
+      <c r="L46" t="n">
+        <v>26.60964515202612</v>
+      </c>
+      <c r="M46" t="n">
+        <v>87.23446466668166</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>20.70169799323632</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-10335.71761182124</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>82.52322921554952</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.830927046297197e-09</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.9707889348805664</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>114.402</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.7920217663715099</v>
+      </c>
+      <c r="D47" t="n">
+        <v>937.5974743386201</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.610940274333093</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.94808e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-84.361</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.4618229172716094</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.028033940687215</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.024578423614556</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.552723677713138</v>
+      </c>
+      <c r="L47" t="n">
+        <v>29.18547583600702</v>
+      </c>
+      <c r="M47" t="n">
+        <v>87.41994073913304</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>22.19214418862437</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-10994.98780652848</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-385.3879772734684</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>4.860492604380701e-07</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.9977171249270285</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>112.248</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.777109309554634</v>
+      </c>
+      <c r="D48" t="n">
+        <v>983.9710139145561</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.740077292569624</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.93611e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.4406566577300882</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.224184212609088</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.980234040924987</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.362890998537315</v>
+      </c>
+      <c r="L48" t="n">
+        <v>29.93763837413455</v>
+      </c>
+      <c r="M48" t="n">
+        <v>87.53032833875157</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>23.18538607941273</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-11392.26888037231</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-430.0008351574644</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.740835969958982e-07</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.9464005142652194</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>104.444</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7230810769646157</v>
+      </c>
+      <c r="D49" t="n">
+        <v>911.9514571910374</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.539523466076337</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.92993e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.57899999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.4409145931804097</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.483459448980113</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.918185676655043</v>
+      </c>
+      <c r="L49" t="n">
+        <v>29.74914148719506</v>
+      </c>
+      <c r="M49" t="n">
+        <v>87.41936889334809</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>22.18721994445826</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-10691.1573461141</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-373.0152469088844</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.711191797803587e-07</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.9475764609978318</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>106.312</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7360135139812938</v>
+      </c>
+      <c r="D50" t="n">
+        <v>929.3028969371678</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.587842253285947</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.92702e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.688</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3555821745237654</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.01892165317923</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.098937101313518</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.63449850937999</v>
+      </c>
+      <c r="L50" t="n">
+        <v>31.85563833481953</v>
+      </c>
+      <c r="M50" t="n">
+        <v>87.61896829912003</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>24.04957186161613</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-11568.18492996886</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-392.317578170691</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.372327666852999e-06</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8122906554785371</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>103.194</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7144271442714425</v>
+      </c>
+      <c r="D51" t="n">
+        <v>933.0623163200506</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.598311158912854</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.92354e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.779</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2538486486890528</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.078896447741263</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.912195124435945</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.545770803606079</v>
+      </c>
+      <c r="L51" t="n">
+        <v>32.81621361214628</v>
+      </c>
+      <c r="M51" t="n">
+        <v>87.63267641090459</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>24.18899217225247</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-11495.58480201084</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-400.2283684512013</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.887831323794435e-06</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8276861352393354</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101.917</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7055862866320973</v>
+      </c>
+      <c r="D52" t="n">
+        <v>927.1145095497562</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.58174822154843</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.91975e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.809</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.2284271559336333</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.066283491837474</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.754211385509747</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.162314727567449</v>
+      </c>
+      <c r="L52" t="n">
+        <v>31.89781039037618</v>
+      </c>
+      <c r="M52" t="n">
+        <v>87.65642212767953</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>24.43435884322485</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-11513.67109539355</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-399.3386007150779</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.431068250308762e-06</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8343893934695371</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>100.543</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.6960738838157614</v>
+      </c>
+      <c r="D53" t="n">
+        <v>949.7566183766926</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.644800005976264</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.91844e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.93600000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.4938271616686675</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.111066459321754</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.189362207831645</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.679355763108733</v>
+      </c>
+      <c r="L53" t="n">
+        <v>34.48164743078598</v>
+      </c>
+      <c r="M53" t="n">
+        <v>87.76719803237502</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>25.64794079284616</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-12010.66582961547</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-422.9424086627425</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.456768027234675e-06</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.885752725635782</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99.43799999999999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6884238073149962</v>
+      </c>
+      <c r="D54" t="n">
+        <v>971.2781591200898</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.704731329417887</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.91816e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-84.922</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.4947257992760141</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.099528210342078</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.245421529545161</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.947758798134435</v>
+      </c>
+      <c r="L54" t="n">
+        <v>33.61806720268441</v>
+      </c>
+      <c r="M54" t="n">
+        <v>87.75235859302603</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>25.47843512937785</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-11829.41361215599</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-445.5876096342332</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.383942218219332e-06</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.7488318759247224</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97.267</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6733936570134933</v>
+      </c>
+      <c r="D55" t="n">
+        <v>972.3845967057123</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.707812441016844</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.91696e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-84.986</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.4390437822853679</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.190577909762701</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.1365858216495</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.631496692370797</v>
+      </c>
+      <c r="L55" t="n">
+        <v>33.99677059479588</v>
+      </c>
+      <c r="M55" t="n">
+        <v>87.78795154004231</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>25.88881323306629</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-11915.85226544596</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-449.9726877743756</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>9.195862087507691e-07</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.9070175407960126</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>93.57899999999995</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.647861093995555</v>
+      </c>
+      <c r="D56" t="n">
+        <v>258.4067836172654</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7195888395317157</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.91522e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-85.05200000000001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.07428125808921056</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.7621182230113378</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.661652042756442</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.102370154811961</v>
+      </c>
+      <c r="L56" t="n">
+        <v>33.9949937823656</v>
+      </c>
+      <c r="M56" t="n">
+        <v>87.75696375283815</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>25.53079835059791</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-11602.94415101687</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>187.802499692675</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>2.301476844229403e-09</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.9993361368228277</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92.46599999999995</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6401556323255537</v>
+      </c>
+      <c r="D57" t="n">
+        <v>993.4300052690256</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.766417872784362</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.91392e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-85.06</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1561381419973648</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.8682838816269173</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.027847680292711</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.434234717493796</v>
+      </c>
+      <c r="L57" t="n">
+        <v>34.03108187241908</v>
+      </c>
+      <c r="M57" t="n">
+        <v>87.77691167013957</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>25.76012107080732</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-11623.64944297491</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-475.423164991941</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>2.278261324028647e-06</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.77288927840608</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>88.57900000000001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6132453632228632</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1019.256201678221</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.838336428649896</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.91196e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-85.111</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5406235753610936</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.604850120855607</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.045549583949026</v>
+      </c>
+      <c r="L58" t="n">
+        <v>33.96892950447808</v>
+      </c>
+      <c r="M58" t="n">
+        <v>87.71409752347942</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>25.05153960857943</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-11144.20187366029</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-501.6269824650778</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.036033224453668e-06</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.7812191704554601</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91.46300000000002</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.6332117167325522</v>
+      </c>
+      <c r="D59" t="n">
+        <v>983.196825971109</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.737921401009789</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.91286e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-85.16800000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.650749816330784</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.166208192314804</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.179828495566464</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.54213652614677</v>
+      </c>
+      <c r="L59" t="n">
+        <v>35.15004559538603</v>
+      </c>
+      <c r="M59" t="n">
+        <v>87.87357340832048</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>26.93225865162789</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-11978.88868680382</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-473.3397349849079</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.320747769681876e-06</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.751164802217363</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>88.37800000000004</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6118538108458011</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1057.866662466917</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.945855497165814</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.91463e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-85.21599999999999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.05420246270827726</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.9927384045948704</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.061011591951937</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.190229444078986</v>
+      </c>
+      <c r="L60" t="n">
+        <v>35.14029471201894</v>
+      </c>
+      <c r="M60" t="n">
+        <v>87.8496137014821</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>26.63190085723615</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-11703.52185731023</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-542.2691711454474</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.495366725827964e-06</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.737177830170329</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>85.84299999999996</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.5943036353440455</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1041.861056368235</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.901284470982496</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.91275e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-85.255</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.02074758537599437</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.8791161195569749</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.003659716593457</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.566232325911919</v>
+      </c>
+      <c r="L61" t="n">
+        <v>35.80680584834101</v>
+      </c>
+      <c r="M61" t="n">
+        <v>87.85397681378903</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>26.68609740727373</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-11613.07042188007</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-532.1997536905216</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>3.300741278904517e-07</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.9817457185723493</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>84.73099999999999</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.586605096820199</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1050.232677207507</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.92459703592527</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.91232e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-85.26600000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.02091128691412585</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.854479775133777</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.746977837737144</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.312514852597034</v>
+      </c>
+      <c r="L62" t="n">
+        <v>35.2493281205692</v>
+      </c>
+      <c r="M62" t="n">
+        <v>87.84760266490638</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>26.60699463907108</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-11474.17973212605</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-543.055551258476</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.525816888742271e-07</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.95700397432562</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>85.08499999999998</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5890558905589055</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1058.150693212886</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.946646441397316</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.91346e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-85.298</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.5495179612628041</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.224370708847964</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.227174929898299</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.14077312965572</v>
+      </c>
+      <c r="L63" t="n">
+        <v>36.03113036579494</v>
+      </c>
+      <c r="M63" t="n">
+        <v>87.92485720785696</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>27.598450082704</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-11847.35195363607</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-553.6329586101749</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.52074311950449e-07</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.9573990661956717</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>82.61000000000001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.571921103826423</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1038.021465370993</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.890592310384753</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.91362e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-85.358</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.2979968033085993</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.028356861479891</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.029766236861083</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.551030700104907</v>
+      </c>
+      <c r="L64" t="n">
+        <v>36.1762515043449</v>
+      </c>
+      <c r="M64" t="n">
+        <v>87.93518090933146</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>27.73655751015672</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-11786.01441180474</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-539.5438499212155</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.508632464002284e-07</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.9581466573941858</v>
       </c>
     </row>
@@ -6714,7 +9626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7976,6 +10888,566 @@
         <v>3.006781957533359e-07</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.9403546345120315</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>230.682</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>475.4830442150853</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.15998e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-78.503</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.08820852647624562</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4447991162463117</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.083302873472932</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.998489834818301</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9.308809082899344</v>
+      </c>
+      <c r="M22" t="n">
+        <v>83.18999817840536</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.373818569362371</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-5401.071129848235</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>101.8861025018445</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.70611793608231e-09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9581034251608215</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>164.109</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.711407912190808</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1008.623744335805</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.121261223942937</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.20096e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.515</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2506897046118307</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.009559198020658</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.767060631246263</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.93472413806754</v>
+      </c>
+      <c r="L23" t="n">
+        <v>12.14854864781429</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.75512454019101</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.89361439320064</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6178.567879544428</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-368.100778119269</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.537211082018327e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8899330000803782</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>149.1220000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.646439687535222</v>
+      </c>
+      <c r="D24" t="n">
+        <v>902.6342043339548</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.898352034453719</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.17127e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-81.535</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4111860165552653</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9574295637088668</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.935069670580428</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.019215330571425</v>
+      </c>
+      <c r="L24" t="n">
+        <v>14.56391866251832</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.55562048662085</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.86587200254209</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7064.023934502686</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-301.4817534438432</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.025617682073349e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9058043978599836</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>142.2090000000001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6164720264259892</v>
+      </c>
+      <c r="D25" t="n">
+        <v>895.0837108759011</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.8824724073042</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.13877e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-82.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3738743717002503</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.014589615539844</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.863434745368294</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.116373997595697</v>
+      </c>
+      <c r="L25" t="n">
+        <v>16.80525315108842</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.07531142267271</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.57596909182956</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-7877.713155714914</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-304.9122900932475</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.716303751517951e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9155322562876601</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>136.679</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5924996315273842</v>
+      </c>
+      <c r="D26" t="n">
+        <v>874.1852419063322</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.838520326943338</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.1135e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-82.736</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2336104066420534</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9233871023952122</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.858458949076669</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.128576849150017</v>
+      </c>
+      <c r="L26" t="n">
+        <v>19.19423925094863</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.44645856337118</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.10289255334038</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8563.418396649791</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-294.924242498627</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.493779008537029e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9230168367433877</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>131.244</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5689390589642883</v>
+      </c>
+      <c r="D27" t="n">
+        <v>861.280646767285</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.811380357819203</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.09211e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.044</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1938119586115925</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.035348009225888</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.777688336615365</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.216446664981048</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20.62872153529186</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.65975374096946</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>17.13372312763676</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8990.945290288122</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-290.9903598188998</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.355757330395731e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.927569774174188</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>127.628</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.5532638003832114</v>
+      </c>
+      <c r="D28" t="n">
+        <v>870.4776996546775</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.830722904308058</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.07505e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.383</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3418183045411953</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9616112785318057</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.824613700204597</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.187439072835225</v>
+      </c>
+      <c r="L28" t="n">
+        <v>22.5414674043494</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.89567991017859</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.43872482002768</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9548.56906772902</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-305.619539443047</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.227873529410139e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9321849308159753</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>123.512</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5354210558257688</v>
+      </c>
+      <c r="D29" t="n">
+        <v>861.5110319740259</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.811864886572738</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.06022e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-83.565</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1324248945431294</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.824904243736298</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.787086570243024</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.046825535055615</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23.16851832929142</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.9898135424009</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>19.01644783826014</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9704.214409331875</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-304.7621068396024</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.147105274599211e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9349488997125096</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>117.948</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5113012718807708</v>
+      </c>
+      <c r="D30" t="n">
+        <v>839.2193525248581</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.764982711234675</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.04932e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-83.788</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7128775371894374</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.664314256101519</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.933470792565861</v>
+      </c>
+      <c r="L30" t="n">
+        <v>24.69259515562757</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.10116706600029</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.74825195082037</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-9930.241038703818</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-292.2714459438</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.068180290307751e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9379835186312472</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>117.15</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5078419642624913</v>
+      </c>
+      <c r="D31" t="n">
+        <v>884.910603798413</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.861077097416165</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.03996e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-83.959</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4217644677324958</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.1500071958039</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.977231890651065</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.306780985718539</v>
+      </c>
+      <c r="L31" t="n">
+        <v>26.21705563390539</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.27482393024709</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>21.00875885158368</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-10483.1173978412</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-337.1917917155538</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.006781957533359e-07</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.9403546345120315</v>
       </c>
     </row>
@@ -7990,7 +11462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10484,6 +13956,1182 @@
         <v>2.615821687966625e-07</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.9582188621066603</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>136.706</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1274.956750414671</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.17316e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-81.855</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1589966308973626</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.7434827609713527</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.320545325742608</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.413564379349952</v>
+      </c>
+      <c r="L44" t="n">
+        <v>14.93351470251674</v>
+      </c>
+      <c r="M44" t="n">
+        <v>85.57652688229666</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>12.92692322836171</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-6760.275873835084</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-631.5852753497254</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.884791817255893e-07</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.9113499642088377</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>119.534</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.8743873714394396</v>
+      </c>
+      <c r="D45" t="n">
+        <v>985.9210426668569</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.7732976372305909</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.11682e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-83.08</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.498058424431033</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.073370072916201</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.999711834595777</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.224685542264359</v>
+      </c>
+      <c r="L45" t="n">
+        <v>19.91439950070653</v>
+      </c>
+      <c r="M45" t="n">
+        <v>86.57243820920476</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>16.69624606476608</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-8375.07279202027</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-420.1621035912333</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.366011558935878e-07</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.9289216952549978</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>114.835</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8400143373370592</v>
+      </c>
+      <c r="D46" t="n">
+        <v>960.5160861834506</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.7533715052460013</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.08477e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-83.61799999999999</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5966808199647685</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.263355329852837</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.132102546152328</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.726067132447885</v>
+      </c>
+      <c r="L46" t="n">
+        <v>23.3641140244456</v>
+      </c>
+      <c r="M46" t="n">
+        <v>86.99561876236625</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>19.05326003383767</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-9418.213977467049</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-407.5392040108048</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>8.798345134825952e-07</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8725147479809059</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>111.529</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8158310535016753</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1011.461943007054</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7933303954648525</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.06316e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-83.946</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.7239329115084142</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.113850167464755</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.134214831744694</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.367362543963505</v>
+      </c>
+      <c r="L47" t="n">
+        <v>25.57292010750326</v>
+      </c>
+      <c r="M47" t="n">
+        <v>87.26124801782844</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>20.90446143731829</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-10235.1003737776</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-458.0597291318026</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.036202999131847e-07</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.9406032166263536</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>107.625</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.7872734188696914</v>
+      </c>
+      <c r="D48" t="n">
+        <v>964.8234692782893</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.7567499595295977</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.04785e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.15900000000001</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.6428711357087948</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.198950865638251</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.941786706364579</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.364240143112697</v>
+      </c>
+      <c r="L48" t="n">
+        <v>27.32234471910459</v>
+      </c>
+      <c r="M48" t="n">
+        <v>87.37059469986423</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>21.77509536669055</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-10519.78062742743</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-422.7829380875888</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.287681571068858e-06</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8166519810821551</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>103.759</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7589937530174246</v>
+      </c>
+      <c r="D49" t="n">
+        <v>940.6127312684496</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.7377605012581973</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.03659e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.30500000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.378797995590998</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.229075498406854</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.10620337349713</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.722142668458165</v>
+      </c>
+      <c r="L49" t="n">
+        <v>28.65074771852751</v>
+      </c>
+      <c r="M49" t="n">
+        <v>87.4355951855562</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>22.32779920786768</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-10653.12477143453</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-407.8796418879771</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.353391950136328e-06</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.7818828453287834</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99.08500000000004</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7248035931122268</v>
+      </c>
+      <c r="D50" t="n">
+        <v>898.1598139158947</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7044629659976894</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.03039e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.443</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.03551805697344007</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.8114860434439487</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.764605855598119</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.248625269654075</v>
+      </c>
+      <c r="L50" t="n">
+        <v>29.65195526046964</v>
+      </c>
+      <c r="M50" t="n">
+        <v>87.46913154353524</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>22.62405618989666</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-10653.92286913183</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-375.6925572593942</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.05675726637929e-06</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.7842147816995064</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>100.075</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7320454113206444</v>
+      </c>
+      <c r="D51" t="n">
+        <v>948.7104895645417</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.7441118996828563</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.02408e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.47799999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4933019676876122</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.041986659014513</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.933331973496651</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.25470898901645</v>
+      </c>
+      <c r="L51" t="n">
+        <v>29.3619081403828</v>
+      </c>
+      <c r="M51" t="n">
+        <v>87.55871172853033</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>23.45528086937025</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-11004.72459310727</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-423.3742295003107</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.826980749065107e-06</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.7954648330292199</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97.40600000000001</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7125217620294649</v>
+      </c>
+      <c r="D52" t="n">
+        <v>943.1333947804113</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7397375593122386</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.01857e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.60899999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.3223141101112555</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.079258077155339</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.383442456148816</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.539786123313053</v>
+      </c>
+      <c r="L52" t="n">
+        <v>30.9768642462386</v>
+      </c>
+      <c r="M52" t="n">
+        <v>87.62033215672666</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>24.06337125574727</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-11176.69561498338</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-422.5561996772637</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.130406602422708e-06</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.7519618202728146</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>94.82400000000001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.6936345149444797</v>
+      </c>
+      <c r="D53" t="n">
+        <v>934.6908420437603</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7331157247018448</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.01567e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.667</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1646341102990112</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.9852257548693608</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.088078650336183</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.630599303399414</v>
+      </c>
+      <c r="L53" t="n">
+        <v>31.54235066895993</v>
+      </c>
+      <c r="M53" t="n">
+        <v>87.62493867185771</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>24.11009667570395</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-11078.25843263301</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-418.903900808551</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2.190957564552214e-06</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.7844817338121756</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>94.07499999999999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6881556039968986</v>
+      </c>
+      <c r="D54" t="n">
+        <v>967.8909204266706</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.7591558851795334</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.01191e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-84.742</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.5219617829552574</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.294852257055502</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.195780574330948</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.863008443147893</v>
+      </c>
+      <c r="L54" t="n">
+        <v>32.19529497151549</v>
+      </c>
+      <c r="M54" t="n">
+        <v>87.7093320023989</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>24.99936681393503</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-11416.58527712284</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-451.7812718794578</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>9.44109590473631e-07</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8688694029003797</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92.39700000000005</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6758810878820247</v>
+      </c>
+      <c r="D55" t="n">
+        <v>958.4273545149181</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7517332287571296</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.00889e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-84.819</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.2985675904808944</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.044034907042573</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.892519021102931</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.431893267174817</v>
+      </c>
+      <c r="L55" t="n">
+        <v>32.54823124320753</v>
+      </c>
+      <c r="M55" t="n">
+        <v>87.73285262931817</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>25.25899907213341</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-11422.21325459859</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-447.5400323225579</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.085072054046103e-06</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.7928592603596168</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91.89999999999998</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6722455488420406</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1030.142610249373</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8079823961984018</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.00738e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-84.889</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5328275766590981</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.239571189727722</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.039948581961155</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.582801945579332</v>
+      </c>
+      <c r="L56" t="n">
+        <v>33.25845623528761</v>
+      </c>
+      <c r="M56" t="n">
+        <v>87.81481647224859</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>26.20740826126609</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-11779.8479738181</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-513.554647975908</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.064923145243585e-06</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8489207620657759</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>89.77200000000005</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.656679297177886</v>
+      </c>
+      <c r="D57" t="n">
+        <v>997.0433270035967</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.7820212934119651</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.00478e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-84.946</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.4708361237466108</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.110551760203663</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.249121355828976</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.72959508313734</v>
+      </c>
+      <c r="L57" t="n">
+        <v>33.92776259497656</v>
+      </c>
+      <c r="M57" t="n">
+        <v>87.82043187161247</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>26.27499398236535</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-11687.95348266325</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-488.5199098472085</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.872510354953958e-07</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.9999185374315883</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>85.26999999999998</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6237473117493014</v>
+      </c>
+      <c r="D58" t="n">
+        <v>996.8880883318824</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7818995334607638</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.0028e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-84.92700000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.649537018670474</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.754989562205785</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.218025233904749</v>
+      </c>
+      <c r="L58" t="n">
+        <v>32.35154057688209</v>
+      </c>
+      <c r="M58" t="n">
+        <v>87.69925981326088</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>24.88980752708708</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-10906.62431198059</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-491.8785639436834</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.698851289753131e-07</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.9540178891906357</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>83.24000000000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.608897926938101</v>
+      </c>
+      <c r="D59" t="n">
+        <v>977.2233969939712</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7664757229420812</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.0016e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-84.999</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.007690041579432116</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.7131577743502023</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.657799295980089</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.30135869497418</v>
+      </c>
+      <c r="L59" t="n">
+        <v>33.54431255461084</v>
+      </c>
+      <c r="M59" t="n">
+        <v>87.72580019033398</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>25.18058735259119</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-10929.05680077098</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-478.2515858520692</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.681525107923475e-07</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.9548998996271583</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>83.59900000000005</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6115240004096387</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1028.901175184149</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8070086886080698</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.00064e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-85.077</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1152193708537342</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.7321369995612019</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.737919833372013</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.464162833720077</v>
+      </c>
+      <c r="L60" t="n">
+        <v>34.50981367059094</v>
+      </c>
+      <c r="M60" t="n">
+        <v>87.81287807470544</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>26.18415866924689</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-11299.12688764321</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-527.0746403117636</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.664634351187337e-07</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.9557804722578245</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>83.59100000000001</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.6114654806665402</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1401.008976486962</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.098867844757317</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.99927e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-85.11499999999999</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.3361162372660874</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.227217626908485</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.137206772453854</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.789174652368978</v>
+      </c>
+      <c r="L61" t="n">
+        <v>35.11635834637911</v>
+      </c>
+      <c r="M61" t="n">
+        <v>87.8797697509733</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>27.01104000958359</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-11597.27597952438</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-856.2880349323032</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>2.654126478313937e-07</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.9562841296332386</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>81.74299999999999</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.5979474200108262</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1040.86866404522</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8163952727860654</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.99843e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-85.152</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.2464762090725707</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.9327381618058768</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.971681954600668</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.407453100247873</v>
+      </c>
+      <c r="L62" t="n">
+        <v>34.67821897109189</v>
+      </c>
+      <c r="M62" t="n">
+        <v>87.88074814245793</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>27.02352154036311</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-11485.19132452939</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-544.2767862828259</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.644063102284988e-07</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.9568018018580203</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78.03699999999998</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5708381490205258</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1057.068277198505</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8291012827334738</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.99763e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-85.202</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.02158508760614425</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.5589134083189419</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.761634177686389</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.145065181151164</v>
+      </c>
+      <c r="L63" t="n">
+        <v>34.72287068301465</v>
+      </c>
+      <c r="M63" t="n">
+        <v>87.82758369754721</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>26.36157743039207</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-11047.96890203932</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-562.1678480773196</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.632497046580194e-07</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.9574126781426855</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80.00599999999997</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.5852413207906016</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1050.598649429132</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8240268927455247</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.99554e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-85.268</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.5065454221942527</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.124589816198246</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.482540566158105</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4.203496687758305</v>
+      </c>
+      <c r="L64" t="n">
+        <v>36.48069246148265</v>
+      </c>
+      <c r="M64" t="n">
+        <v>87.9701621601189</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>28.21496662817601</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-11809.65080898267</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-559.6493918251648</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.615821687966625e-07</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.9582188621066603</v>
       </c>
     </row>
@@ -10498,7 +15146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11760,6 +16408,566 @@
         <v>2.994258849657866e-07</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.9419561149497139</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>220.98</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>371.22066097703</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.21037e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-78.718</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2419395143513107</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6836433619823946</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.329890620662158</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.385374777245058</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9.723177956082333</v>
+      </c>
+      <c r="M22" t="n">
+        <v>83.45949046664951</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.722055810969508</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-5528.900488859498</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>198.9476640510364</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.969650335772923e-09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9785424695443491</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>163.473</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7397637795275592</v>
+      </c>
+      <c r="D23" t="n">
+        <v>985.9169918086965</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.655878552701845</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.21752e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.791</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3157981966496224</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9202807094299617</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.792409966999563</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.211635879690772</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13.03648345404301</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.03443553300878</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.5097206749733</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6517.297981851735</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-351.6030433568584</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.462534064680492e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8934832853792555</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>149.741</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6776224092678074</v>
+      </c>
+      <c r="D24" t="n">
+        <v>897.9973305512807</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.419039199455674</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.17976e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-81.836</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4109089579599934</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9807436062473478</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.041498666356232</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.328932665533806</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.01497847855696</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.86524912306481</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.83306641960545</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7611.660186011932</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-297.5554790379578</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.942887961099986e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9094445245033568</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>142.8869999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6466060276948139</v>
+      </c>
+      <c r="D25" t="n">
+        <v>882.5148171214485</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.377332163567415</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.14361e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-82.515</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4043895921112611</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.03263452902021</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.950760047316217</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.124689142862113</v>
+      </c>
+      <c r="L25" t="n">
+        <v>18.59341116313811</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.3631281959031</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.7329736383577</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8509.876928372587</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-294.1621894435173</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.631311019853731e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9192954304947233</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>138.543</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6269481401031769</v>
+      </c>
+      <c r="D26" t="n">
+        <v>891.3005598695363</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.400999334260351</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.11582e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-82.96299999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4643559296173638</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.192479608931269</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.962206514137083</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.235150946503587</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.82564279223162</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.68943968421829</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.28770910974309</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-9225.697987366791</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-309.1728930773006</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.433202917606022e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9257882025619144</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>131.31</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5942166711919632</v>
+      </c>
+      <c r="D27" t="n">
+        <v>842.1591159783961</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.268621347103593</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.09581e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.319</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1560719221421459</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8657298223159873</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.716597799563078</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.940095731310978</v>
+      </c>
+      <c r="L27" t="n">
+        <v>22.68008642215301</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.87646964071794</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.32510044780342</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9608.468929090981</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-274.9021909804718</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.28840568000323e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9308548232196515</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>129.036</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.5839261471626392</v>
+      </c>
+      <c r="D28" t="n">
+        <v>877.3341268836252</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.363376339491815</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.08005e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.598</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3858259278993429</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.216262341469251</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.0510112522173</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.503781115179806</v>
+      </c>
+      <c r="L28" t="n">
+        <v>25.0616407410469</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.10560889338865</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>19.77861000535064</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10257.96468520767</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-311.6407423286141</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.179195488138277e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9348194406595822</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>123.597</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5593130600054304</v>
+      </c>
+      <c r="D29" t="n">
+        <v>851.9532340169565</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.295004894864062</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.06787e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-83.797</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1384403634363479</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9420539905199823</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.831289267100855</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.050148985471261</v>
+      </c>
+      <c r="L29" t="n">
+        <v>25.89498778952024</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.20011358068641</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>20.44731682148933</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10444.71707993587</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-296.7088984104775</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.894594238925443e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9998268003986831</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>119.544</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5409720336682056</v>
+      </c>
+      <c r="D30" t="n">
+        <v>855.2653026743917</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.303926997014083</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.05925e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-83.973</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1916562175136638</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8817201168580782</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.70637415092634</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.082879569868378</v>
+      </c>
+      <c r="L30" t="n">
+        <v>26.99901495575602</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.30416266343487</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>21.23774000284141</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-10705.66882549406</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-306.2551431778491</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.037941546175563e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9401836813729093</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>117.968</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5338401665309079</v>
+      </c>
+      <c r="D31" t="n">
+        <v>923.1662180675395</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.486839540767539</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.05354e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.09699999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3929808702485166</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.104028109150762</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.968645657111501</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.269549942202687</v>
+      </c>
+      <c r="L31" t="n">
+        <v>28.30706506193646</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.40591634175149</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>22.07200399026673</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-11014.7101948853</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-370.4759188365218</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.994258849657866e-07</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.9419561149497139</v>
       </c>
     </row>
@@ -11774,7 +16982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14268,6 +19476,1182 @@
         <v>2.654781821075532e-07</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.9577150497867044</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>140.104</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1311.615950388532</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.2279e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-81.51600000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.344064277659561</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.02116908200836</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.778107205017853</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.985254314816214</v>
+      </c>
+      <c r="L44" t="n">
+        <v>14.39163777440432</v>
+      </c>
+      <c r="M44" t="n">
+        <v>85.40007102497242</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>12.42902375371085</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-6545.016377602506</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-659.4169332607826</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>4.112824161963975e-07</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.9065260216129608</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>120.864</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.8626734425855083</v>
+      </c>
+      <c r="D45" t="n">
+        <v>958.6283737782658</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.7308758127669135</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.1518e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-82.953</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.211868110274113</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.101027905648077</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.827916444428982</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.216523030193073</v>
+      </c>
+      <c r="L45" t="n">
+        <v>19.61485873387916</v>
+      </c>
+      <c r="M45" t="n">
+        <v>86.51054109016846</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>16.39936863863073</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-8261.791834220494</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-394.3772268503122</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.463548461689567e-07</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.927080734629527</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>116.357</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8305044823845142</v>
+      </c>
+      <c r="D46" t="n">
+        <v>929.9531180503615</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.7090132731116051</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.11094e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-83.589</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.4952333540888252</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.26303849146077</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.149772610038327</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.610655360771308</v>
+      </c>
+      <c r="L46" t="n">
+        <v>23.71250639878987</v>
+      </c>
+      <c r="M46" t="n">
+        <v>87.00645554276082</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>19.12236015249242</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-9490.960038724663</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-379.2122764928819</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.208848820771064e-07</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.9356944585156446</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>111.87</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.7984782732827044</v>
+      </c>
+      <c r="D47" t="n">
+        <v>918.2388365349273</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7000820905410027</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.08667e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-83.91800000000001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.3338274566290925</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.9828530062674787</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.084929809776971</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.297804502401517</v>
+      </c>
+      <c r="L47" t="n">
+        <v>25.92299983848542</v>
+      </c>
+      <c r="M47" t="n">
+        <v>87.22812280110165</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>20.65426019363998</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-10121.65857072952</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-375.3367361687385</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.079512572913859e-07</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.9401622021827061</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>105.504</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.753040598412608</v>
+      </c>
+      <c r="D48" t="n">
+        <v>861.5207300738556</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6568391683698668</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.07064e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.155</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.6597874039103194</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.704472177847332</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.990697747128618</v>
+      </c>
+      <c r="L48" t="n">
+        <v>27.61741906852401</v>
+      </c>
+      <c r="M48" t="n">
+        <v>87.2890872318856</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>21.11946159826942</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-10176.59073855654</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-331.6311563221046</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.6379726903005e-07</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.9947722685128367</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>107.727</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7689073830868497</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1008.018812478889</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.7685319869587509</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.0586e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.26600000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.6666288403196496</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.37938242697057</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.049298768923853</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.541369847774445</v>
+      </c>
+      <c r="L49" t="n">
+        <v>28.71533160815539</v>
+      </c>
+      <c r="M49" t="n">
+        <v>87.50462129892919</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>22.94623584966731</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-11045.04798626547</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-463.2858972581049</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>6.058865907241843e-07</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.9756267818283836</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>103.9040000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7416205104779311</v>
+      </c>
+      <c r="D50" t="n">
+        <v>956.0451192197978</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7289062922241794</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.05e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.366</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.5433696039329577</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.377852189678077</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.287103175132971</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.470470990304249</v>
+      </c>
+      <c r="L50" t="n">
+        <v>29.42901704662881</v>
+      </c>
+      <c r="M50" t="n">
+        <v>87.52145584907113</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>23.10228585324511</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-10977.46229465216</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-423.5073722678172</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.541397465901892e-06</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8219042449566987</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7084023296979387</v>
+      </c>
+      <c r="D51" t="n">
+        <v>900.7916000291506</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6867799981864469</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.04506e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.505</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2371795159159547</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.8594941183048749</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.735001738608295</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.94183993455372</v>
+      </c>
+      <c r="L51" t="n">
+        <v>30.20135175259545</v>
+      </c>
+      <c r="M51" t="n">
+        <v>87.54544948096554</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>23.32839508007688</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-10924.74103120476</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-380.628951200719</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>2.308474421580248e-06</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.7741987323164977</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98.56200000000001</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7034916918860277</v>
+      </c>
+      <c r="D52" t="n">
+        <v>932.6195965788114</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7110462451318523</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.03863e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.599</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.4532238388966155</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.084860522011715</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.231416291084194</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.537165432351892</v>
+      </c>
+      <c r="L52" t="n">
+        <v>31.66574973887193</v>
+      </c>
+      <c r="M52" t="n">
+        <v>87.63493727598764</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>24.21214179417457</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-11256.99445885403</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-412.7426145313846</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.028570739946239e-06</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.7921343136142551</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>96.94099999999997</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.6919217152972077</v>
+      </c>
+      <c r="D53" t="n">
+        <v>960.2784607190962</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7321338692432331</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.03384e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.661</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.4203710966716218</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.206035999465931</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.148835629407271</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.836405888051458</v>
+      </c>
+      <c r="L53" t="n">
+        <v>32.25084933593374</v>
+      </c>
+      <c r="M53" t="n">
+        <v>87.68112606702171</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>24.69495738355592</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-11388.270789623</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-440.7023661078813</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2.186959869851276e-06</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.7851787481194796</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>95.81400000000002</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6838776908582198</v>
+      </c>
+      <c r="D54" t="n">
+        <v>342.820656977598</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.2613727416749136</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.03217e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-84.739</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.4613066447193263</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.117795046439185</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.94841769176275</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.512937988671994</v>
+      </c>
+      <c r="L54" t="n">
+        <v>32.41564744738827</v>
+      </c>
+      <c r="M54" t="n">
+        <v>87.73860685571304</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>25.32333889373832</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-11587.93137669101</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>106.228060412514</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.703579233680836e-09</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.9920498250199279</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>84.37900000000002</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6022597499000745</v>
+      </c>
+      <c r="D55" t="n">
+        <v>917.3571792981203</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.6994098989314497</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.02792e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-84.82599999999999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.8613062043191407</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.391797827834696</v>
+      </c>
+      <c r="L55" t="n">
+        <v>32.21113388199785</v>
+      </c>
+      <c r="M55" t="n">
+        <v>87.43887800715753</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>22.35645699874262</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-9948.766866542572</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-411.00439435485</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.689040659125571e-06</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.761613722176729</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>87.34799999999996</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6234511505738591</v>
+      </c>
+      <c r="D56" t="n">
+        <v>910.3741044955523</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.6940858749284635</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.02749e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-84.83199999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.4207312073421638</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.487442345568135</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.820962908315295</v>
+      </c>
+      <c r="L56" t="n">
+        <v>32.28785022531749</v>
+      </c>
+      <c r="M56" t="n">
+        <v>87.61504044963438</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>24.00991834519344</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-10693.15704751849</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-408.2279136236165</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>2.092965923134083e-06</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.7939652896558055</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>90.81100000000004</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6481685033974764</v>
+      </c>
+      <c r="D57" t="n">
+        <v>969.295810467543</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.7390088616873062</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.02581e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-84.881</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.4370695070022121</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.176831735344071</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.268598840545317</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.948083568485353</v>
+      </c>
+      <c r="L57" t="n">
+        <v>33.73472926800861</v>
+      </c>
+      <c r="M57" t="n">
+        <v>87.80000684725178</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>26.0308169005995</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-11615.39179086089</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-463.1473740060862</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.87374654933605e-07</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.9999185116922792</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>89.00400000000002</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6352709415862504</v>
+      </c>
+      <c r="D58" t="n">
+        <v>949.1131905898434</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7236212629990461</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.02478e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-84.952</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.19007462518868</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.9870451921734733</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.904164269555052</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.418234383125347</v>
+      </c>
+      <c r="L58" t="n">
+        <v>33.93760634056244</v>
+      </c>
+      <c r="M58" t="n">
+        <v>87.81973538823236</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>26.26659235722757</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-11609.43019424543</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-448.8047080542825</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.724884697611362e-07</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.9541916668591555</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>86.20400000000001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.6152857877005654</v>
+      </c>
+      <c r="D59" t="n">
+        <v>972.1720246392141</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7412017399996041</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.02314e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-85.014</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.06152741611271256</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8557027305477052</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.818856024088006</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.089084734269747</v>
+      </c>
+      <c r="L59" t="n">
+        <v>34.3550431275999</v>
+      </c>
+      <c r="M59" t="n">
+        <v>87.80958887751102</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>26.14480137958938</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-11429.52742617746</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-472.1382391156941</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.70843335055864e-07</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.9549917941196892</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79.41500000000002</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.5668289270827388</v>
+      </c>
+      <c r="D60" t="n">
+        <v>949.1626060782777</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7236589382716132</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.02081e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-85.032</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.08160848432130344</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.253254636452201</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.792407922780852</v>
+      </c>
+      <c r="L60" t="n">
+        <v>33.8918018433255</v>
+      </c>
+      <c r="M60" t="n">
+        <v>87.62649270100589</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>24.12590060204456</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-10346.71251131366</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-455.4454808550475</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.699984214560284e-07</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.9553067099821752</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>86.541</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.6176911437218067</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1077.182361751112</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8212635424508411</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.02006e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-85.095</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.6711085370714951</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.273100752825741</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.206985496078668</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.696443390072759</v>
+      </c>
+      <c r="L61" t="n">
+        <v>35.26272114298408</v>
+      </c>
+      <c r="M61" t="n">
+        <v>87.94026050456966</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>27.80501878660194</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-12029.67002916425</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-570.7125955404902</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>2.685623821567904e-07</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.9560561345612519</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>77.87</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.5558014046708161</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1001.179794062604</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.763317794180553</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.01904e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-85.101</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.1869623488434732</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.287170588975514</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.692045825842893</v>
+      </c>
+      <c r="L62" t="n">
+        <v>33.98001770452366</v>
+      </c>
+      <c r="M62" t="n">
+        <v>87.69417283319656</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>24.83483796277044</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-10489.71513985551</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-507.9384180891976</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.681501399578432e-07</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.956230592041715</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80.19100000000003</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5723676697310572</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1144.892150405346</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8728867242474456</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.01896e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-85.18600000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1276305058101053</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8825506483908083</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.667847470498626</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.275334793257701</v>
+      </c>
+      <c r="L63" t="n">
+        <v>35.57127648434289</v>
+      </c>
+      <c r="M63" t="n">
+        <v>87.86886394465913</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>26.87268799886095</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-11335.91746104349</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-636.9115921496916</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.664095332736867e-07</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.9572016161535086</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>75.30499999999995</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.5374935762005364</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1016.056856784378</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7746603390141737</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.01866e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-85.22799999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.1825123084849544</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.099233275955284</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.592188967708458</v>
+      </c>
+      <c r="L64" t="n">
+        <v>35.04735653502429</v>
+      </c>
+      <c r="M64" t="n">
+        <v>87.75691782074087</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>25.53027501616125</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-10590.83304695597</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-527.9003878032574</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.654781821075532e-07</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.9577150497867044</v>
       </c>
     </row>
@@ -14282,7 +20666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15544,6 +21928,566 @@
         <v>2.931007929726052e-07</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.9450493901569904</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>221.4800000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>368.6096082814205</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.22512e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-78.753</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.184426970816433</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6323302754709929</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.294531888600593</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.400600637356927</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9.863173848471527</v>
+      </c>
+      <c r="M22" t="n">
+        <v>83.53400045001383</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.823436581631196</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-5603.649728868509</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>200.6871210763598</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.939781204984354e-09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9799731114276149</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>159.005</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7179203539823006</v>
+      </c>
+      <c r="D23" t="n">
+        <v>980.1859949882033</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.659143909889255</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.22012e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2984099085137235</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8791336755986013</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.594035941763847</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.873597310332431</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13.47236306307091</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.2135347838045</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.94251466375319</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6714.69197562406</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-351.3920607924156</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.350575643664988e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.897507102159935</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>142.913</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6452636806935159</v>
+      </c>
+      <c r="D24" t="n">
+        <v>839.162952223757</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.276562882167427</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.17361e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.124</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1742624290108125</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7372918313219549</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.521771812932162</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.811644344688933</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.83663410297559</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.0328088599905</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.41931702309659</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7842.536772160747</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-252.2492548561816</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.804381518473373e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9144283937340101</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>136.63</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6168954307386669</v>
+      </c>
+      <c r="D25" t="n">
+        <v>815.4678601110571</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.212280531462641</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.13532e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-82.81100000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.03792359626600208</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7331182729724244</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.472825614000463</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.748206522146763</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.88483657007108</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.55257332379307</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.59980777479657</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8893.673459773989</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-241.0481103361984</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.504288151220924e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9241056821068518</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>135.7259999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6128137980856054</v>
+      </c>
+      <c r="D26" t="n">
+        <v>881.3455339581213</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.390999892995857</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.10868e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.258</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6389322190557999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.29395187117923</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.238708351055914</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.858394566081011</v>
+      </c>
+      <c r="L26" t="n">
+        <v>23.25996704074455</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.9861017701369</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.99298491695694</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10116.13588290864</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-303.6493793535549</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.319013594846779e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9303974673699865</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>129.151</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5831271446631748</v>
+      </c>
+      <c r="D27" t="n">
+        <v>330.6447826420469</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.897005328167168</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.09044e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.58499999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2174102017086053</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.088029671062537</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.038927741645087</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.68303614252538</v>
+      </c>
+      <c r="L27" t="n">
+        <v>25.55913431298514</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.15739869539549</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>20.13956791849008</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10551.99627331281</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>178.5038667713485</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.395015651612653e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9796601808069511</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>126.192</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.5697670218529888</v>
+      </c>
+      <c r="D28" t="n">
+        <v>863.5402536086068</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.342695996544192</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.07551e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.771</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2789375891047515</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.199250926770966</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.248095214433262</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.70736160640064</v>
+      </c>
+      <c r="L28" t="n">
+        <v>26.76594286231919</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.27536092498359</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>21.01290568482053</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10865.60988569405</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-302.230091092704</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.11056400521917e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9378244514291909</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>121.662</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5493137077839982</v>
+      </c>
+      <c r="D29" t="n">
+        <v>870.4495217782701</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.361440131299324</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.06564e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.06100000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2726719933297478</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.055623614632268</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.101175354086276</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.463055107101084</v>
+      </c>
+      <c r="L29" t="n">
+        <v>29.5499022628461</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.46431559652837</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>22.58103102183825</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-11525.19590796948</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-314.6722242824646</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.01938652258721e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9415819661731251</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>117.721</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5315197760520136</v>
+      </c>
+      <c r="D30" t="n">
+        <v>850.0801255243583</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.306180051810673</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.05665e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.15900000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.222616817627816</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.106832256456649</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.911767326299603</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.229979974930675</v>
+      </c>
+      <c r="L30" t="n">
+        <v>29.56351252774681</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.50165181635789</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>22.91892791072446</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-11537.7280858147</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-303.0995004168763</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.974394904184702e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9432194539486946</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>114.834</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5184847390283546</v>
+      </c>
+      <c r="D31" t="n">
+        <v>852.2423153650592</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.312045850726718</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.05115e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.285</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2659321263301174</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.152235822457563</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.942005816562692</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.184999579354628</v>
+      </c>
+      <c r="L31" t="n">
+        <v>30.66232521441981</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.57951358152002</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>23.6571005595406</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-11766.05015049437</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-311.2175065093109</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.931007929726052e-07</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.9450493901569904</v>
       </c>
     </row>
@@ -15558,7 +22502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18052,6 +24996,1182 @@
         <v>2.660548930483863e-07</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.9583700677178829</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>139.05</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1278.793551024229</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.22285e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-81.63200000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.2727336068863681</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8698393476826706</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.608084537460634</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.589735431929222</v>
+      </c>
+      <c r="L44" t="n">
+        <v>14.69059711550178</v>
+      </c>
+      <c r="M44" t="n">
+        <v>85.55460818823437</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>12.86293041747631</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-6830.028950954207</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-631.5488360573381</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>4.043693871259796e-07</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.9087480537130986</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>120.947</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.8698094210715569</v>
+      </c>
+      <c r="D45" t="n">
+        <v>929.5350624807662</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.7268843839072149</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.1491e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-83.053</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.3958112980760272</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.8765642391622859</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.800995321214326</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.074226612318605</v>
+      </c>
+      <c r="L45" t="n">
+        <v>20.44456479499822</v>
+      </c>
+      <c r="M45" t="n">
+        <v>86.62761733792514</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>16.97007864582658</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-8632.903832591566</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-365.9722916498478</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.675247436031156e-07</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.9988156554213184</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>115.583</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8312333692916214</v>
+      </c>
+      <c r="D46" t="n">
+        <v>925.2837071833582</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.7235598791081385</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.10827e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-83.63800000000001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.4784614325994419</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.300495520323005</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.009112106615301</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.477540110191591</v>
+      </c>
+      <c r="L46" t="n">
+        <v>24.38716907986659</v>
+      </c>
+      <c r="M46" t="n">
+        <v>87.08333961834244</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>19.62733821795843</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-9838.498825688595</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-371.9176925912502</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.181633620200979e-07</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.9368092617042773</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>111.215</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.7998202085580723</v>
+      </c>
+      <c r="D47" t="n">
+        <v>925.2327307277969</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7235200161798961</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.08546e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-83.941</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5085153186148947</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.017928047727818</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.666709834826022</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.005408346354286</v>
+      </c>
+      <c r="L47" t="n">
+        <v>26.26801112372376</v>
+      </c>
+      <c r="M47" t="n">
+        <v>87.26957672282155</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>20.96832412855604</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-10368.1116933688</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-377.4659709562414</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.061414370027394e-07</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.9409937211675136</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>108.997</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.783869111830277</v>
+      </c>
+      <c r="D48" t="n">
+        <v>970.5759912459733</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.7589778588331215</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.07034e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.149</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.4106064055111844</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.076895569296044</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.133439375887749</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.436671396366434</v>
+      </c>
+      <c r="L48" t="n">
+        <v>28.37176007734292</v>
+      </c>
+      <c r="M48" t="n">
+        <v>87.43468155584721</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>22.31983660425665</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-10926.86794640467</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-422.9346778965074</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.801008221149333e-07</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.9984205476257983</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>104.198</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7493563466378999</v>
+      </c>
+      <c r="D49" t="n">
+        <v>880.7633692800514</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6887455512851298</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.06051e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.318</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.2247783854365876</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.9420812597613175</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.796989685216409</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.226006776159974</v>
+      </c>
+      <c r="L49" t="n">
+        <v>29.78371348462237</v>
+      </c>
+      <c r="M49" t="n">
+        <v>87.49497990291154</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>22.85780769787742</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-11031.72547674831</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-350.708912561771</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.746351472270337e-06</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8405277647447856</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>102.777</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7391370010787485</v>
+      </c>
+      <c r="D50" t="n">
+        <v>915.2954491426098</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7157491906410685</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.05404e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.416</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.4858896500989283</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.246049735318378</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.949304017107382</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.409348568570824</v>
+      </c>
+      <c r="L50" t="n">
+        <v>30.53295388773145</v>
+      </c>
+      <c r="M50" t="n">
+        <v>87.59416461102664</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>23.80133833854714</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-11395.35855692168</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-385.6314706430053</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.435726347952618e-06</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.7784829378881105</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99.59099999999995</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7162243797195249</v>
+      </c>
+      <c r="D51" t="n">
+        <v>880.3058637524599</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6883877878860065</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.04961e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.52200000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.09847322629938747</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9243186369749968</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.828073945252128</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.112744126261214</v>
+      </c>
+      <c r="L51" t="n">
+        <v>31.2803411373005</v>
+      </c>
+      <c r="M51" t="n">
+        <v>87.60864652955547</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>23.94564712269023</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-11315.45057022371</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-360.1447501214666</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>5.559443951561254e-07</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.9792420809295083</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97.113</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.698403451995685</v>
+      </c>
+      <c r="D52" t="n">
+        <v>897.9252111093186</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7021658893964081</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.0466e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.578</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.2538001115545359</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9842765939257518</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.976379855157723</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.059520054268474</v>
+      </c>
+      <c r="L52" t="n">
+        <v>31.29164892220447</v>
+      </c>
+      <c r="M52" t="n">
+        <v>87.6386457399631</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>24.25020971670905</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-11341.20189378039</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-380.1289963457397</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.445688758224025e-06</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.7797991419828746</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>94.43000000000001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.6791082344480402</v>
+      </c>
+      <c r="D53" t="n">
+        <v>899.3711644954973</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7032966062232333</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.04342e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.661</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.2129077917083431</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.070612087741861</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.98681041543249</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.62128448619094</v>
+      </c>
+      <c r="L53" t="n">
+        <v>32.78802215592863</v>
+      </c>
+      <c r="M53" t="n">
+        <v>87.67719434439918</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>24.65311147250479</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-11416.13996383517</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-385.9779667247654</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.910935847238245e-06</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.7744668085293805</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>95.286</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6852642934196331</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1228.597453791122</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9607473018667455</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.03987e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-84.752</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.613263766501153</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.261639875322701</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.305253206345751</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.806485475902905</v>
+      </c>
+      <c r="L54" t="n">
+        <v>33.76448618335485</v>
+      </c>
+      <c r="M54" t="n">
+        <v>87.81009305977385</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>26.15082656531312</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-12062.4157865</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-677.7992708354501</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.316767111265437e-06</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.7529243354056714</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92.65300000000002</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6663286587558434</v>
+      </c>
+      <c r="D55" t="n">
+        <v>954.1716666181019</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7461498893655458</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.04002e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-84.804</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3722886007709775</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.395146977259223</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.359847920868554</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.318396579603955</v>
+      </c>
+      <c r="L55" t="n">
+        <v>33.69892292556712</v>
+      </c>
+      <c r="M55" t="n">
+        <v>87.8205424696433</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>26.27632861166523</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-11996.18885363217</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-442.0396656344597</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.047276587104414e-06</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.7955704223007315</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>90.47900000000004</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6506939949658399</v>
+      </c>
+      <c r="D56" t="n">
+        <v>932.1373372432405</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7289193290790842</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.03873e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-84.83799999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.354044236440671</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.228885902515347</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.162738266499807</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.585393898011672</v>
+      </c>
+      <c r="L56" t="n">
+        <v>33.99439767109963</v>
+      </c>
+      <c r="M56" t="n">
+        <v>87.81078071201776</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>26.15904876452573</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-11820.66809178136</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-426.5516481119403</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.734491907564514e-07</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.9998477806299197</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87.19799999999998</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6270981661272922</v>
+      </c>
+      <c r="D57" t="n">
+        <v>925.169176870762</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.7234703178865446</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.03755e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-84.923</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1138258593208402</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.9904127030817002</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.795755995533814</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.114755631809096</v>
+      </c>
+      <c r="L57" t="n">
+        <v>34.34160662694209</v>
+      </c>
+      <c r="M57" t="n">
+        <v>87.80126866914307</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>26.04577032008059</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-11618.53853203202</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-424.0330887429075</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>2.738074642512763e-07</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.9544302529760966</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>86.45800000000003</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6217763394462426</v>
+      </c>
+      <c r="D58" t="n">
+        <v>963.0720692294942</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7531098889716306</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.03504e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-84.964</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1654709225932478</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.243660192253664</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.961076126071156</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.95384570279446</v>
+      </c>
+      <c r="L58" t="n">
+        <v>35.4428691564582</v>
+      </c>
+      <c r="M58" t="n">
+        <v>87.85506756801165</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>26.69968068263704</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-11837.10365352957</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-461.4405370314866</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.724765264228142e-07</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.9549944994411119</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>86.70999999999998</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.62358863718087</v>
+      </c>
+      <c r="D59" t="n">
+        <v>979.5915179496626</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7660278839888383</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.03351e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-84.98</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.4689263664283869</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.09383119965625</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.171182420792224</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.477711087984271</v>
+      </c>
+      <c r="L59" t="n">
+        <v>34.64000641714301</v>
+      </c>
+      <c r="M59" t="n">
+        <v>87.87431166686969</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>26.94162090673175</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-11856.62252356277</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-479.1791111327327</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.717446277148552e-07</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.9553056574385524</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>83.69299999999998</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6018914059690758</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1325.111336164243</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.036219908290057</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.03396e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-85.03400000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.2590507331233595</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.097233807556352</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.840785113532157</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.537842367716643</v>
+      </c>
+      <c r="L60" t="n">
+        <v>35.19008420517838</v>
+      </c>
+      <c r="M60" t="n">
+        <v>87.87075907823763</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>26.89662813360137</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-11709.90918424021</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-786.4266745298473</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.706710776409562e-07</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.9559371910029408</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>81.37099999999998</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.5851923768428621</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1004.355340763581</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7853928728051208</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.03227e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-85.072</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.179263955957194</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.8502379229694961</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.882994969455472</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.262700247347318</v>
+      </c>
+      <c r="L61" t="n">
+        <v>34.92074830151425</v>
+      </c>
+      <c r="M61" t="n">
+        <v>87.87213590775382</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>26.91404756260455</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-11602.87499830767</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-508.1720430749009</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>2.695351437307313e-07</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.9564556629632146</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>81.685</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.58745055735347</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1024.555840843728</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8011894023262214</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.03251e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-85.179</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.3704925876254813</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.336372605556543</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.151956238112274</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.37506092115072</v>
+      </c>
+      <c r="L62" t="n">
+        <v>36.88059889262986</v>
+      </c>
+      <c r="M62" t="n">
+        <v>87.98453019173634</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>28.41627539185486</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-12183.94804322583</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-529.530321681711</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.674479118209682e-07</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.9576380706450214</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80.19</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5766990291262135</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1029.416735301703</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8049905588569857</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.03131e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-85.175</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.3994804786415376</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.146492231588173</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.290161651375075</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.658428291943398</v>
+      </c>
+      <c r="L63" t="n">
+        <v>36.39426736182816</v>
+      </c>
+      <c r="M63" t="n">
+        <v>87.94558538440631</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>27.87714924002999</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-11829.63864477345</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-537.0307857001696</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.6718394981589e-07</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.9577174277947021</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78.18800000000005</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.5623013304566705</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1028.457143706444</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8042401706535957</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.03144e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-85.227</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.2128092192072268</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.8987857300538579</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.96662963401963</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.459431524946105</v>
+      </c>
+      <c r="L64" t="n">
+        <v>36.52333326679923</v>
+      </c>
+      <c r="M64" t="n">
+        <v>87.95924052707389</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>28.06384044051653</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-11793.20759591702</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-540.0745475625663</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.660548930483863e-07</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.9583700677178829</v>
       </c>
     </row>
@@ -18066,7 +26186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19331,6 +27451,566 @@
         <v>0.7879378883207873</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>214.316</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>560.8787060277713</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.17122e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-79.84</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.22368219778042</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5176941506163643</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.232181209490716</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.665603301512612</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11.57533922269205</v>
+      </c>
+      <c r="M22" t="n">
+        <v>84.30135020506781</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>10.02109749397026</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-6202.506470869546</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.5841874448926816</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.870857934015208e-09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9290384478740646</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>148.211</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.6915535937587489</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1076.756903112335</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.919767842031465</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.13894e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-82.291</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5775538096748181</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.107257940958444</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.946663922396656</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.548398968201671</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17.38649034700869</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.16611206061488</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.9222515967568</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8055.542724286479</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-452.7537978173253</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.696957143001951e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9163403427526926</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>132.58</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.618619235148099</v>
+      </c>
+      <c r="D24" t="n">
+        <v>896.00160844145</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.597496212304208</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.0923e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.303</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3451219304581013</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9832540586188205</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.948404961926173</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.032810017928474</v>
+      </c>
+      <c r="L24" t="n">
+        <v>22.07642996612148</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.89790606768399</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>18.45198293498987</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9600.724840700765</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-323.3532145430299</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.284121272966834e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9308259589892216</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>127.028</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5927135631497417</v>
+      </c>
+      <c r="D25" t="n">
+        <v>889.9427420118332</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.586693758289637</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.06293e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.782</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5014116526935954</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.083349003992867</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.953325131456958</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.344098879667673</v>
+      </c>
+      <c r="L25" t="n">
+        <v>25.69663370893696</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.25868349814803</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>20.88487534099069</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10692.07200967175</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-327.6978349773237</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.097473312523191e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9375291038585979</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>121.155</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.565310102838799</v>
+      </c>
+      <c r="D26" t="n">
+        <v>858.1243891477894</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.529964286262813</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.04438e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.137</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3186688345224311</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.197259631775435</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.988602461542484</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.281872821617615</v>
+      </c>
+      <c r="L26" t="n">
+        <v>29.10508064868849</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.46486275737671</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>22.58591107401257</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-11363.75009103374</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-307.9616331218871</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.973416487429197e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9423403938295931</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>119.134</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5558801022788781</v>
+      </c>
+      <c r="D27" t="n">
+        <v>913.9807362869991</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.629551499217987</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.03261e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.327</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6217782950061154</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.378947597215335</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.293908828987977</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.489335476302424</v>
+      </c>
+      <c r="L27" t="n">
+        <v>30.78389211918288</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.62832172715183</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>24.14452766787483</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-11997.67667630151</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-363.2306092906304</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.208391941885388e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.867647384897354</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>111.013</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.517987457772635</v>
+      </c>
+      <c r="D28" t="n">
+        <v>842.1176910828918</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.501425677303562</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.026e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.488</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.07148547961386087</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9090159341521014</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.875570720310376</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.406821273157866</v>
+      </c>
+      <c r="L28" t="n">
+        <v>32.33331500372852</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.5960437431378</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>23.8199653221709</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-11557.95890420135</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-309.3067548875002</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.853134075543249e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9472507494403682</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>108.872</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.507997536348196</v>
+      </c>
+      <c r="D29" t="n">
+        <v>841.3917835769589</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.500131444703658</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.02286e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.614</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2961373587062034</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7134114230285462</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.839951526979798</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.360662519324279</v>
+      </c>
+      <c r="L29" t="n">
+        <v>33.27114953299792</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.70247041294871</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>24.92462628024174</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-11937.19550199226</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-316.0242509366445</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.721666061233418e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.995610285704855</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>104.855</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.4892541854084624</v>
+      </c>
+      <c r="D30" t="n">
+        <v>849.3060873498806</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.514241988904867</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.01866e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.71299999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2868318821391643</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.028715070618016</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.737793072629829</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.454932504043695</v>
+      </c>
+      <c r="L30" t="n">
+        <v>34.05470114037922</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.75258186234397</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>25.48096887808072</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-12032.78076299674</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-329.2958608656376</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.928901445658376e-06</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.7696462191807913</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>102.53</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.4784057186584298</v>
+      </c>
+      <c r="D31" t="n">
+        <v>883.8093809418091</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.575758486538172</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.01751e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.803</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1908237995194199</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.080481267471709</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.037667587069403</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.606016578900993</v>
+      </c>
+      <c r="L31" t="n">
+        <v>35.15007195889579</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.81604736855897</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>26.2221933327917</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-12231.93795227585</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-365.2841907013815</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.658440801982039e-06</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.7879378883207873</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
